--- a/output5/【河洛話注音】桃花源記【文讀音】.xlsx
+++ b/output5/【河洛話注音】桃花源記【文讀音】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9978D1C5-2FBE-4878-98DB-57F60B101B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7935932A-2DCC-45BE-8350-8238931C9581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="797">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1391,1962 +1391,1967 @@
     <t>自</t>
   </si>
   <si>
+    <t>乃</t>
+  </si>
+  <si>
+    <t>驚</t>
+  </si>
+  <si>
+    <t>問</t>
+  </si>
+  <si>
+    <t>所</t>
+  </si>
+  <si>
+    <t>具</t>
+  </si>
+  <si>
+    <t>答</t>
+  </si>
+  <si>
+    <t>家</t>
+  </si>
+  <si>
+    <t>設</t>
+  </si>
+  <si>
+    <t>酒</t>
+  </si>
+  <si>
+    <t>此</t>
+  </si>
+  <si>
+    <t>咸</t>
+  </si>
+  <si>
+    <t>訊</t>
+  </si>
+  <si>
+    <t>云</t>
+  </si>
+  <si>
+    <t>：</t>
+  </si>
+  <si>
+    <t>「</t>
+  </si>
+  <si>
+    <t>先</t>
+  </si>
+  <si>
+    <t>世</t>
+  </si>
+  <si>
+    <t>秦</t>
+  </si>
+  <si>
+    <t>時</t>
+  </si>
+  <si>
+    <t>亂</t>
+  </si>
+  <si>
+    <t>率</t>
+  </si>
+  <si>
+    <t>妻</t>
+  </si>
+  <si>
+    <t>子</t>
+  </si>
+  <si>
+    <t>邑</t>
+  </si>
+  <si>
+    <t>絕</t>
+  </si>
+  <si>
+    <t>境</t>
+  </si>
+  <si>
+    <t>不</t>
+  </si>
+  <si>
+    <t>出</t>
+  </si>
+  <si>
+    <t>焉</t>
+  </si>
+  <si>
+    <t>遂</t>
+  </si>
+  <si>
+    <t>與</t>
+  </si>
+  <si>
+    <t>間</t>
+  </si>
+  <si>
+    <t>」</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>何</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>漢</t>
+  </si>
+  <si>
+    <t>論</t>
+  </si>
+  <si>
+    <t>魏</t>
+  </si>
+  <si>
+    <t>！</t>
+  </si>
+  <si>
+    <t>言</t>
+  </si>
+  <si>
+    <t>皆</t>
+  </si>
+  <si>
+    <t>惋</t>
+  </si>
+  <si>
+    <t>餘</t>
+  </si>
+  <si>
+    <t>延</t>
+  </si>
+  <si>
+    <t>至</t>
+  </si>
+  <si>
+    <t>停</t>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>辭</t>
+  </si>
+  <si>
+    <t>語</t>
+  </si>
+  <si>
+    <t>足</t>
+  </si>
+  <si>
+    <t>道</t>
+  </si>
+  <si>
+    <t>也</t>
+  </si>
+  <si>
+    <t>既</t>
+  </si>
+  <si>
+    <t>向</t>
+  </si>
+  <si>
+    <t>處</t>
+  </si>
+  <si>
+    <t>誌</t>
+  </si>
+  <si>
+    <t>及</t>
+  </si>
+  <si>
+    <t>郡</t>
+  </si>
+  <si>
+    <t>守</t>
+  </si>
+  <si>
+    <t>說</t>
+  </si>
+  <si>
+    <t>遣</t>
+  </si>
+  <si>
+    <t>隨</t>
+  </si>
+  <si>
+    <t>尋</t>
+  </si>
+  <si>
+    <t>迷</t>
+  </si>
+  <si>
+    <t>南</t>
+  </si>
+  <si>
+    <t>陽</t>
+  </si>
+  <si>
+    <t>劉</t>
+  </si>
+  <si>
+    <t>驥</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>尚</t>
+  </si>
+  <si>
+    <t>士</t>
+  </si>
+  <si>
+    <t>規</t>
+  </si>
+  <si>
+    <t>未</t>
+  </si>
+  <si>
+    <t>果</t>
+  </si>
+  <si>
+    <t>病</t>
+  </si>
+  <si>
+    <t>終</t>
+  </si>
+  <si>
+    <t>後</t>
+  </si>
+  <si>
+    <t>津</t>
+  </si>
+  <si>
+    <t>者</t>
+  </si>
+  <si>
+    <t>鮮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zap8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>種</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>著</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>髫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>並</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>見</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>問</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>還</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>殺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ke1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>避</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>歎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>詣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>便</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thai3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㄞ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆦ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giap8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄧㄚㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khe1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆦ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hut4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hua1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄚˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄚㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pian7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>it4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>san1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆲˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㆦˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bi2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ka1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄚˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khian2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄧㄢˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄞˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiau5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㄠˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nai2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄋㄞˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ham5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆰˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄣ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>un5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>se3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luan7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ip4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zuat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㄚㆵ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>king2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄥˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄜˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>han3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄞˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jit8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆵ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄨㄣ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ge7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㆤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kui1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄨㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆬˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bun7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨㄣ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>than3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ling5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lim5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆬˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gan7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆬ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>song1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄞ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iau3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄠ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kim1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆬˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>語音類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文讀音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花源記【文讀音】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄠˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kin7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄣ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>king1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ping7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄥ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tau5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄠˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄚㆴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sian3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄆㄧㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄨㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siau2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄠˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khio2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄧㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sia3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄚ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hap8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄞ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄞˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liam2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆰˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄇㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kau1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄠˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄋㆰˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ju7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆡㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ping2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄥˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thi3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gak8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄚㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hian7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ku7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄚㆴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sut4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lut7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨㆵ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ting5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tau2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄠˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄨ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khian3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄧㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>me5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄇㆤˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hio5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄜˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zau2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆲˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zut1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㆵˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ze3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zut4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄚㆵ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>樂</t>
-  </si>
-  <si>
-    <t>乃</t>
-  </si>
-  <si>
-    <t>驚</t>
-  </si>
-  <si>
-    <t>問</t>
-  </si>
-  <si>
-    <t>所</t>
-  </si>
-  <si>
-    <t>具</t>
-  </si>
-  <si>
-    <t>答</t>
-  </si>
-  <si>
-    <t>家</t>
-  </si>
-  <si>
-    <t>設</t>
-  </si>
-  <si>
-    <t>酒</t>
-  </si>
-  <si>
-    <t>此</t>
-  </si>
-  <si>
-    <t>咸</t>
-  </si>
-  <si>
-    <t>訊</t>
-  </si>
-  <si>
-    <t>云</t>
-  </si>
-  <si>
-    <t>：</t>
-  </si>
-  <si>
-    <t>「</t>
-  </si>
-  <si>
-    <t>先</t>
-  </si>
-  <si>
-    <t>世</t>
-  </si>
-  <si>
-    <t>秦</t>
-  </si>
-  <si>
-    <t>時</t>
-  </si>
-  <si>
-    <t>亂</t>
-  </si>
-  <si>
-    <t>率</t>
-  </si>
-  <si>
-    <t>妻</t>
-  </si>
-  <si>
-    <t>子</t>
-  </si>
-  <si>
-    <t>邑</t>
-  </si>
-  <si>
-    <t>絕</t>
-  </si>
-  <si>
-    <t>境</t>
-  </si>
-  <si>
-    <t>不</t>
-  </si>
-  <si>
-    <t>出</t>
-  </si>
-  <si>
-    <t>焉</t>
-  </si>
-  <si>
-    <t>遂</t>
-  </si>
-  <si>
-    <t>與</t>
-  </si>
-  <si>
-    <t>間</t>
-  </si>
-  <si>
-    <t>」</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>何</t>
-  </si>
-  <si>
-    <t>？</t>
-  </si>
-  <si>
-    <t>漢</t>
-  </si>
-  <si>
-    <t>論</t>
-  </si>
-  <si>
-    <t>魏</t>
-  </si>
-  <si>
-    <t>！</t>
-  </si>
-  <si>
-    <t>言</t>
-  </si>
-  <si>
-    <t>皆</t>
-  </si>
-  <si>
-    <t>惋</t>
-  </si>
-  <si>
-    <t>餘</t>
-  </si>
-  <si>
-    <t>延</t>
-  </si>
-  <si>
-    <t>至</t>
-  </si>
-  <si>
-    <t>停</t>
-  </si>
-  <si>
-    <t>日</t>
-  </si>
-  <si>
-    <t>辭</t>
-  </si>
-  <si>
-    <t>語</t>
-  </si>
-  <si>
-    <t>足</t>
-  </si>
-  <si>
-    <t>道</t>
-  </si>
-  <si>
-    <t>也</t>
-  </si>
-  <si>
-    <t>既</t>
-  </si>
-  <si>
-    <t>向</t>
-  </si>
-  <si>
-    <t>處</t>
-  </si>
-  <si>
-    <t>誌</t>
-  </si>
-  <si>
-    <t>及</t>
-  </si>
-  <si>
-    <t>郡</t>
-  </si>
-  <si>
-    <t>守</t>
-  </si>
-  <si>
-    <t>說</t>
-  </si>
-  <si>
-    <t>遣</t>
-  </si>
-  <si>
-    <t>隨</t>
-  </si>
-  <si>
-    <t>尋</t>
-  </si>
-  <si>
-    <t>迷</t>
-  </si>
-  <si>
-    <t>南</t>
-  </si>
-  <si>
-    <t>陽</t>
-  </si>
-  <si>
-    <t>劉</t>
-  </si>
-  <si>
-    <t>驥</t>
-  </si>
-  <si>
-    <t>高</t>
-  </si>
-  <si>
-    <t>尚</t>
-  </si>
-  <si>
-    <t>士</t>
-  </si>
-  <si>
-    <t>規</t>
-  </si>
-  <si>
-    <t>未</t>
-  </si>
-  <si>
-    <t>果</t>
-  </si>
-  <si>
-    <t>病</t>
-  </si>
-  <si>
-    <t>終</t>
-  </si>
-  <si>
-    <t>後</t>
-  </si>
-  <si>
-    <t>津</t>
-  </si>
-  <si>
-    <t>者</t>
-  </si>
-  <si>
-    <t>鮮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>落</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>甚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>窮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zap8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>豁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>竹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>種</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>著</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>悉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>髫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>並</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>佁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>見</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>漁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>問</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>還</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>殺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ke1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>食</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>村</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>避</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>隔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>今</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>知</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>歎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>詣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>守</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>便</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thai3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㄞ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>guan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>poo7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㆦ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>giap8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄧㄚㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khe1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㆤˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loo7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㆦ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hut4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hua1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㄚˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄚㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ing1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄥˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kiong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ki5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pian7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>it4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>san1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㆲˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thoo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㆦˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bi2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ka1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄚˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆤˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khian2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄧㄢˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lai5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄞˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㄚㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiau5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄠˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nai2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄋㄞˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄚㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ham5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㆰˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sin3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄣ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>un5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>se3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pi7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>luan7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ip4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zuat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㄚㆵ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>king2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄥˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kan1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ho5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄜˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>han3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gui7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄞˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jit8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㆵ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ki3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kun7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄨㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ge7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㆤ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kui1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄨㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ko2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄜˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sim5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆬˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bun7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>than3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ling5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㄥˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jin5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lim5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㆬˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gan7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sim7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆬ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>song1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tai7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄞ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iau3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄠ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄚㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kim1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆬˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ha7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄚ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>語音類型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文讀音</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花源記【文讀音】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>欣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄠˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kin7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>king1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄥˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ping7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄥ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>piong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tau5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄠˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kap4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄚㆴ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hiong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sian3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>phin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄆㄧㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pun1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄨㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄠˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khio2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄧㄜˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sia3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄚ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>suan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hap8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄚㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zai7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄞ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄞˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liam2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㆰˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄇㄧㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kau1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄠˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nam5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄋㆰˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sit4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ju7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆡㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ping2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄥˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thi3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gak8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄚㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hian7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ku7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tap4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄚㆴ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sut4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lut7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨㆵ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ting5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄥˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄠˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄨ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khian3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄧㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>me5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄇㆤˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bui7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hio5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄜˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ua</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zian1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iong2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆲˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zut1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㆵˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ze3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆴ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zut4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ian7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄚㆵ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆲˊ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3354,7 +3359,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="80">
+  <fonts count="81">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -3906,6 +3911,14 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFF0000"/>
+      <name val="吳守禮細明台語注音"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -4083,7 +4096,7 @@
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4367,7 +4380,10 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4386,6 +4402,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5576,7 +5595,7 @@
       </c>
     </row>
     <row r="11" spans="2:3">
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="99" t="s">
         <v>626</v>
       </c>
       <c r="C11" s="53" t="s">
@@ -5654,7 +5673,7 @@
       <c r="Q3" s="83"/>
       <c r="R3" s="83"/>
       <c r="T3" s="92"/>
-      <c r="V3" s="99" t="s">
+      <c r="V3" s="100" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5663,13 +5682,13 @@
       <c r="D4" s="84"/>
       <c r="E4" s="84"/>
       <c r="F4" s="84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G4" s="84" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H4" s="84" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I4" s="84" t="s">
         <v>644</v>
@@ -5678,19 +5697,19 @@
         <v>763</v>
       </c>
       <c r="K4" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L4" s="84" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M4" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N4" s="84" t="s">
         <v>762</v>
       </c>
       <c r="O4" s="84" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P4" s="84" t="s">
         <v>587</v>
@@ -5699,7 +5718,7 @@
         <v>766</v>
       </c>
       <c r="R4" s="84" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="S4" s="93" t="s">
         <v>764</v>
@@ -5707,7 +5726,7 @@
       <c r="T4" s="1">
         <v>8</v>
       </c>
-      <c r="V4" s="100"/>
+      <c r="V4" s="101"/>
     </row>
     <row r="5" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -5752,14 +5771,14 @@
       <c r="P5" s="80" t="s">
         <v>195</v>
       </c>
-      <c r="Q5" s="80" t="s">
+      <c r="Q5" s="98" t="s">
         <v>196</v>
       </c>
       <c r="R5" s="80" t="s">
         <v>197</v>
       </c>
       <c r="S5" s="94"/>
-      <c r="V5" s="100"/>
+      <c r="V5" s="101"/>
     </row>
     <row r="6" spans="2:29" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
@@ -5767,30 +5786,30 @@
       <c r="D6" s="85"/>
       <c r="E6" s="85"/>
       <c r="F6" s="85" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G6" s="85" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H6" s="85" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I6" s="85" t="s">
         <v>645</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L6" s="85" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M6" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="N6" s="85"/>
       <c r="O6" s="85" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P6" s="85" t="s">
         <v>588</v>
@@ -5799,10 +5818,10 @@
         <v>767</v>
       </c>
       <c r="R6" s="85" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="S6" s="95"/>
-      <c r="V6" s="100"/>
+      <c r="V6" s="101"/>
     </row>
     <row r="7" spans="2:29" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -5810,7 +5829,9 @@
       <c r="D7" s="83"/>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
+      <c r="G7" s="83" t="s">
+        <v>580</v>
+      </c>
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
       <c r="J7" s="83"/>
@@ -5823,7 +5844,7 @@
       <c r="Q7" s="83"/>
       <c r="R7" s="83"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="100"/>
+      <c r="V7" s="101"/>
     </row>
     <row r="8" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
@@ -5832,20 +5853,20 @@
         <v>768</v>
       </c>
       <c r="F8" s="84" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G8" s="84" t="s">
         <v>646</v>
       </c>
       <c r="H8" s="84"/>
       <c r="I8" s="84" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J8" s="84" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K8" s="84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L8" s="84" t="s">
         <v>768</v>
@@ -5857,7 +5878,7 @@
         <v>762</v>
       </c>
       <c r="O8" s="84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P8" s="84" t="s">
         <v>648</v>
@@ -5866,7 +5887,7 @@
         <v>650</v>
       </c>
       <c r="R8" s="84" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S8" s="93" t="s">
         <v>765</v>
@@ -5874,7 +5895,7 @@
       <c r="T8" s="1">
         <v>1</v>
       </c>
-      <c r="V8" s="100"/>
+      <c r="V8" s="101"/>
     </row>
     <row r="9" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -5890,7 +5911,7 @@
       <c r="F9" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="80" t="s">
+      <c r="G9" s="98" t="s">
         <v>200</v>
       </c>
       <c r="H9" s="80" t="s">
@@ -5917,10 +5938,10 @@
       <c r="O9" s="80" t="s">
         <v>207</v>
       </c>
-      <c r="P9" s="80" t="s">
+      <c r="P9" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="Q9" s="80" t="s">
+      <c r="Q9" s="98" t="s">
         <v>209</v>
       </c>
       <c r="R9" s="80" t="s">
@@ -5928,7 +5949,7 @@
       </c>
       <c r="S9" s="94"/>
       <c r="T9" s="92"/>
-      <c r="V9" s="100"/>
+      <c r="V9" s="101"/>
     </row>
     <row r="10" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
@@ -5937,20 +5958,20 @@
         <v>769</v>
       </c>
       <c r="F10" s="85" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G10" s="85" t="s">
         <v>647</v>
       </c>
       <c r="H10" s="85"/>
       <c r="I10" s="85" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J10" s="85" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K10" s="85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L10" s="85" t="s">
         <v>769</v>
@@ -5960,7 +5981,7 @@
       </c>
       <c r="N10" s="85"/>
       <c r="O10" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P10" s="85" t="s">
         <v>649</v>
@@ -5969,10 +5990,10 @@
         <v>651</v>
       </c>
       <c r="R10" s="85" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="S10" s="96"/>
-      <c r="V10" s="100"/>
+      <c r="V10" s="101"/>
     </row>
     <row r="11" spans="2:29" s="66" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="65"/>
@@ -5992,7 +6013,7 @@
       <c r="P11" s="83"/>
       <c r="Q11" s="83"/>
       <c r="R11" s="83"/>
-      <c r="V11" s="100"/>
+      <c r="V11" s="101"/>
     </row>
     <row r="12" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
@@ -6013,20 +6034,20 @@
         <v>585</v>
       </c>
       <c r="J12" s="84" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K12" s="84"/>
       <c r="L12" s="84" t="s">
         <v>644</v>
       </c>
       <c r="M12" s="84" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N12" s="84" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O12" s="84" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="P12" s="84"/>
       <c r="Q12" s="84" t="s">
@@ -6036,7 +6057,7 @@
         <v>770</v>
       </c>
       <c r="S12" s="93"/>
-      <c r="V12" s="100"/>
+      <c r="V12" s="101"/>
     </row>
     <row r="13" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -6049,7 +6070,7 @@
       <c r="E13" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="F13" s="80" t="s">
+      <c r="F13" s="98" t="s">
         <v>212</v>
       </c>
       <c r="G13" s="80" t="s">
@@ -6082,14 +6103,14 @@
       <c r="P13" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="Q13" s="80" t="s">
+      <c r="Q13" s="98" t="s">
         <v>220</v>
       </c>
-      <c r="R13" s="80" t="s">
+      <c r="R13" s="98" t="s">
         <v>221</v>
       </c>
       <c r="S13" s="94"/>
-      <c r="V13" s="100"/>
+      <c r="V13" s="101"/>
     </row>
     <row r="14" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
@@ -6110,20 +6131,20 @@
         <v>586</v>
       </c>
       <c r="J14" s="85" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K14" s="85"/>
       <c r="L14" s="85" t="s">
         <v>645</v>
       </c>
       <c r="M14" s="85" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N14" s="85" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O14" s="85" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P14" s="85"/>
       <c r="Q14" s="85" t="s">
@@ -6133,7 +6154,7 @@
         <v>630</v>
       </c>
       <c r="S14" s="96"/>
-      <c r="V14" s="100"/>
+      <c r="V14" s="101"/>
     </row>
     <row r="15" spans="2:29" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -6153,7 +6174,7 @@
       <c r="P15" s="83"/>
       <c r="Q15" s="83"/>
       <c r="R15" s="83"/>
-      <c r="V15" s="100"/>
+      <c r="V15" s="101"/>
       <c r="AC15" s="67" t="s">
         <v>184</v>
       </c>
@@ -6164,14 +6185,14 @@
         <v>658</v>
       </c>
       <c r="E16" s="84" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F16" s="84"/>
       <c r="G16" s="84" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H16" s="84" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I16" s="84" t="s">
         <v>660</v>
@@ -6184,23 +6205,23 @@
         <v>587</v>
       </c>
       <c r="M16" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N16" s="84" t="s">
         <v>589</v>
       </c>
       <c r="O16" s="84" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P16" s="84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q16" s="84"/>
       <c r="R16" s="84" t="s">
         <v>664</v>
       </c>
       <c r="S16" s="93"/>
-      <c r="V16" s="100"/>
+      <c r="V16" s="101"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -6208,7 +6229,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="80" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E17" s="80" t="s">
         <v>222</v>
@@ -6217,15 +6238,15 @@
         <v>190</v>
       </c>
       <c r="G17" s="80" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H17" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="I17" s="80" t="s">
+      <c r="I17" s="106" t="s">
         <v>224</v>
       </c>
-      <c r="J17" s="80" t="s">
+      <c r="J17" s="98" t="s">
         <v>225</v>
       </c>
       <c r="K17" s="80" t="s">
@@ -6238,7 +6259,7 @@
         <v>193</v>
       </c>
       <c r="N17" s="80" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O17" s="80" t="s">
         <v>227</v>
@@ -6249,11 +6270,11 @@
       <c r="Q17" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="R17" s="80" t="s">
+      <c r="R17" s="98" t="s">
         <v>229</v>
       </c>
       <c r="S17" s="94"/>
-      <c r="V17" s="100"/>
+      <c r="V17" s="101"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
@@ -6261,14 +6282,14 @@
         <v>659</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F18" s="85"/>
       <c r="G18" s="85" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H18" s="85" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I18" s="85" t="s">
         <v>661</v>
@@ -6281,23 +6302,23 @@
         <v>588</v>
       </c>
       <c r="M18" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="N18" s="85" t="s">
         <v>590</v>
       </c>
       <c r="O18" s="85" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P18" s="85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q18" s="85"/>
       <c r="R18" s="85" t="s">
         <v>665</v>
       </c>
       <c r="S18" s="96"/>
-      <c r="V18" s="100"/>
+      <c r="V18" s="101"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -6317,7 +6338,7 @@
       <c r="P19" s="83"/>
       <c r="Q19" s="83"/>
       <c r="R19" s="83"/>
-      <c r="V19" s="100"/>
+      <c r="V19" s="101"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
@@ -6332,10 +6353,10 @@
         <v>593</v>
       </c>
       <c r="H20" s="84" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I20" s="84" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J20" s="84" t="s">
         <v>581</v>
@@ -6349,7 +6370,7 @@
       <c r="Q20" s="84"/>
       <c r="R20" s="84"/>
       <c r="S20" s="93"/>
-      <c r="V20" s="100"/>
+      <c r="V20" s="101"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -6357,7 +6378,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="80" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E21" s="80" t="s">
         <v>200</v>
@@ -6369,7 +6390,7 @@
         <v>230</v>
       </c>
       <c r="H21" s="80" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I21" s="80" t="s">
         <v>231</v>
@@ -6388,7 +6409,7 @@
       <c r="Q21" s="80"/>
       <c r="R21" s="80"/>
       <c r="S21" s="94"/>
-      <c r="V21" s="100"/>
+      <c r="V21" s="101"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
@@ -6403,10 +6424,10 @@
         <v>594</v>
       </c>
       <c r="H22" s="85" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I22" s="85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J22" s="85" t="s">
         <v>582</v>
@@ -6420,7 +6441,7 @@
       <c r="Q22" s="85"/>
       <c r="R22" s="85"/>
       <c r="S22" s="96"/>
-      <c r="V22" s="101"/>
+      <c r="V22" s="102"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -6547,24 +6568,24 @@
         <v>668</v>
       </c>
       <c r="I28" s="84" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J28" s="84"/>
       <c r="K28" s="84" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L28" s="84" t="s">
         <v>642</v>
       </c>
       <c r="M28" s="84" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N28" s="84" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O28" s="84"/>
       <c r="P28" s="84" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q28" s="84" t="s">
         <v>595</v>
@@ -6650,24 +6671,24 @@
         <v>669</v>
       </c>
       <c r="I30" s="85" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J30" s="85"/>
       <c r="K30" s="85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L30" s="85" t="s">
         <v>643</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N30" s="85" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O30" s="85"/>
       <c r="P30" s="85" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q30" s="85" t="s">
         <v>596</v>
@@ -6716,7 +6737,7 @@
         <v>674</v>
       </c>
       <c r="G32" s="84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H32" s="84" t="s">
         <v>597</v>
@@ -6729,7 +6750,7 @@
       </c>
       <c r="K32" s="84"/>
       <c r="L32" s="84" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M32" s="84" t="s">
         <v>678</v>
@@ -6745,7 +6766,7 @@
         <v>672</v>
       </c>
       <c r="R32" s="84" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="S32" s="93"/>
       <c r="U32" s="67" t="str">
@@ -6759,13 +6780,13 @@
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="80" t="s">
+      <c r="D33" s="98" t="s">
         <v>241</v>
       </c>
       <c r="E33" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="F33" s="80" t="s">
+      <c r="F33" s="98" t="s">
         <v>242</v>
       </c>
       <c r="G33" s="80" t="s">
@@ -6789,7 +6810,7 @@
       <c r="M33" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="N33" s="80" t="s">
+      <c r="N33" s="106" t="s">
         <v>247</v>
       </c>
       <c r="O33" s="80" t="s">
@@ -6817,7 +6838,7 @@
         <v>675</v>
       </c>
       <c r="G34" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H34" s="85" t="s">
         <v>598</v>
@@ -6830,7 +6851,7 @@
       </c>
       <c r="K34" s="85"/>
       <c r="L34" s="85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M34" s="85" t="s">
         <v>679</v>
@@ -6878,7 +6899,7 @@
         <v>771</v>
       </c>
       <c r="F36" s="84" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G36" s="84" t="s">
         <v>685</v>
@@ -6891,7 +6912,7 @@
         <v>635</v>
       </c>
       <c r="K36" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L36" s="84"/>
       <c r="M36" s="84" t="s">
@@ -6907,7 +6928,7 @@
         <v>599</v>
       </c>
       <c r="Q36" s="84" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="R36" s="84"/>
       <c r="S36" s="93"/>
@@ -6921,7 +6942,7 @@
       <c r="D37" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="E37" s="80" t="s">
+      <c r="E37" s="98" t="s">
         <v>250</v>
       </c>
       <c r="F37" s="80" t="s">
@@ -6973,7 +6994,7 @@
         <v>772</v>
       </c>
       <c r="F38" s="85" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G38" s="85" t="s">
         <v>686</v>
@@ -6986,7 +7007,7 @@
         <v>636</v>
       </c>
       <c r="K38" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L38" s="85"/>
       <c r="M38" s="85" t="s">
@@ -7002,7 +7023,7 @@
         <v>689</v>
       </c>
       <c r="Q38" s="85" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="R38" s="85"/>
       <c r="S38" s="96"/>
@@ -7031,20 +7052,20 @@
     <row r="40" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="56"/>
       <c r="D40" s="84" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E40" s="84" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F40" s="84" t="s">
         <v>690</v>
       </c>
       <c r="G40" s="84" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H40" s="84"/>
       <c r="I40" s="84" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J40" s="84" t="s">
         <v>692</v>
@@ -7053,11 +7074,11 @@
         <v>694</v>
       </c>
       <c r="L40" s="84" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M40" s="84"/>
       <c r="N40" s="84" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="O40" s="84" t="s">
         <v>678</v>
@@ -7066,7 +7087,7 @@
         <v>696</v>
       </c>
       <c r="Q40" s="84" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="R40" s="84"/>
       <c r="S40" s="93"/>
@@ -7077,8 +7098,8 @@
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="80" t="s">
-        <v>373</v>
+      <c r="D41" s="98" t="s">
+        <v>372</v>
       </c>
       <c r="E41" s="80" t="s">
         <v>256</v>
@@ -7098,7 +7119,7 @@
       <c r="J41" s="80" t="s">
         <v>260</v>
       </c>
-      <c r="K41" s="80" t="s">
+      <c r="K41" s="106" t="s">
         <v>261</v>
       </c>
       <c r="L41" s="80" t="s">
@@ -7113,7 +7134,7 @@
       <c r="O41" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="P41" s="80" t="s">
+      <c r="P41" s="106" t="s">
         <v>264</v>
       </c>
       <c r="Q41" s="80" t="s">
@@ -7128,20 +7149,20 @@
     <row r="42" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="58"/>
       <c r="D42" s="85" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E42" s="85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F42" s="85" t="s">
         <v>691</v>
       </c>
       <c r="G42" s="85" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H42" s="85"/>
       <c r="I42" s="85" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J42" s="85" t="s">
         <v>693</v>
@@ -7150,11 +7171,11 @@
         <v>695</v>
       </c>
       <c r="L42" s="85" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M42" s="85"/>
       <c r="N42" s="85" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O42" s="85" t="s">
         <v>679</v>
@@ -7163,7 +7184,7 @@
         <v>697</v>
       </c>
       <c r="Q42" s="85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R42" s="85"/>
       <c r="S42" s="96"/>
@@ -7202,10 +7223,10 @@
       </c>
       <c r="G44" s="84"/>
       <c r="H44" s="84" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I44" s="84" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J44" s="84"/>
       <c r="K44" s="84" t="s">
@@ -7213,13 +7234,13 @@
       </c>
       <c r="L44" s="84"/>
       <c r="M44" s="84" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N44" s="84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O44" s="84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P44" s="84"/>
       <c r="Q44" s="84" t="s">
@@ -7258,28 +7279,28 @@
         <v>267</v>
       </c>
       <c r="K45" s="80" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L45" s="80" t="s">
         <v>267</v>
       </c>
       <c r="M45" s="80" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N45" s="80" t="s">
         <v>203</v>
       </c>
       <c r="O45" s="80" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P45" s="80" t="s">
         <v>190</v>
       </c>
       <c r="Q45" s="80" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R45" s="80" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S45" s="94"/>
       <c r="V45" s="60"/>
@@ -7297,10 +7318,10 @@
       </c>
       <c r="G46" s="85"/>
       <c r="H46" s="85" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I46" s="85" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J46" s="85"/>
       <c r="K46" s="85" t="s">
@@ -7308,13 +7329,13 @@
       </c>
       <c r="L46" s="85"/>
       <c r="M46" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N46" s="85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O46" s="85" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="P46" s="85"/>
       <c r="Q46" s="85" t="s">
@@ -7356,20 +7377,20 @@
       </c>
       <c r="F48" s="84"/>
       <c r="G48" s="84" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H48" s="84" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I48" s="84" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J48" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K48" s="84"/>
       <c r="L48" s="84" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M48" s="84" t="s">
         <v>644</v>
@@ -7378,13 +7399,13 @@
         <v>774</v>
       </c>
       <c r="O48" s="84" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P48" s="84" t="s">
         <v>602</v>
       </c>
       <c r="Q48" s="84" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="R48" s="84"/>
       <c r="S48" s="93"/>
@@ -7405,7 +7426,7 @@
         <v>190</v>
       </c>
       <c r="G49" s="80" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H49" s="80" t="s">
         <v>271</v>
@@ -7425,14 +7446,14 @@
       <c r="M49" s="80" t="s">
         <v>189</v>
       </c>
-      <c r="N49" s="80" t="s">
+      <c r="N49" s="106" t="s">
         <v>274</v>
       </c>
       <c r="O49" s="80" t="s">
         <v>275</v>
       </c>
       <c r="P49" s="80" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q49" s="80" t="s">
         <v>276</v>
@@ -7453,20 +7474,20 @@
       </c>
       <c r="F50" s="85"/>
       <c r="G50" s="85" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H50" s="85" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I50" s="85" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J50" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K50" s="85"/>
       <c r="L50" s="85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M50" s="85" t="s">
         <v>645</v>
@@ -7475,13 +7496,13 @@
         <v>775</v>
       </c>
       <c r="O50" s="85" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P50" s="85" t="s">
         <v>603</v>
       </c>
       <c r="Q50" s="85" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R50" s="85"/>
       <c r="S50" s="96"/>
@@ -7529,23 +7550,23 @@
         <v>712</v>
       </c>
       <c r="K52" s="84" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L52" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M52" s="84"/>
       <c r="N52" s="84" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O52" s="84" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P52" s="84" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q52" s="84" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="R52" s="84"/>
       <c r="S52" s="93"/>
@@ -7566,13 +7587,13 @@
         <v>279</v>
       </c>
       <c r="G53" s="81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H53" s="81" t="s">
         <v>190</v>
       </c>
       <c r="I53" s="80" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J53" s="80" t="s">
         <v>280</v>
@@ -7596,7 +7617,7 @@
         <v>284</v>
       </c>
       <c r="Q53" s="80" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R53" s="80" t="s">
         <v>190</v>
@@ -7626,23 +7647,23 @@
         <v>713</v>
       </c>
       <c r="K54" s="85" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L54" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M54" s="85"/>
       <c r="N54" s="85" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="O54" s="85" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="P54" s="85" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q54" s="85" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="R54" s="85"/>
       <c r="S54" s="96"/>
@@ -7677,7 +7698,7 @@
         <v>716</v>
       </c>
       <c r="F56" s="84" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G56" s="84" t="s">
         <v>718</v>
@@ -7693,11 +7714,11 @@
         <v>587</v>
       </c>
       <c r="L56" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M56" s="84"/>
       <c r="N56" s="84" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O56" s="84" t="s">
         <v>606</v>
@@ -7707,7 +7728,7 @@
       </c>
       <c r="Q56" s="84"/>
       <c r="R56" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="S56" s="93"/>
       <c r="V56" s="60"/>
@@ -7718,28 +7739,28 @@
         <v>14</v>
       </c>
       <c r="D57" s="80" t="s">
+        <v>383</v>
+      </c>
+      <c r="E57" s="106" t="s">
         <v>384</v>
-      </c>
-      <c r="E57" s="80" t="s">
-        <v>385</v>
       </c>
       <c r="F57" s="80" t="s">
         <v>256</v>
       </c>
       <c r="G57" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="H57" s="80" t="s">
-        <v>286</v>
+        <v>385</v>
+      </c>
+      <c r="H57" s="81" t="s">
+        <v>796</v>
       </c>
       <c r="I57" s="80" t="s">
         <v>228</v>
       </c>
       <c r="J57" s="80" t="s">
+        <v>387</v>
+      </c>
+      <c r="K57" s="80" t="s">
         <v>388</v>
-      </c>
-      <c r="K57" s="80" t="s">
-        <v>389</v>
       </c>
       <c r="L57" s="80" t="s">
         <v>193</v>
@@ -7748,19 +7769,19 @@
         <v>190</v>
       </c>
       <c r="N57" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="O57" s="80" t="s">
+        <v>389</v>
+      </c>
+      <c r="P57" s="80" t="s">
         <v>287</v>
-      </c>
-      <c r="O57" s="80" t="s">
-        <v>390</v>
-      </c>
-      <c r="P57" s="80" t="s">
-        <v>288</v>
       </c>
       <c r="Q57" s="80" t="s">
         <v>190</v>
       </c>
       <c r="R57" s="80" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="S57" s="94"/>
       <c r="V57" s="60"/>
@@ -7774,7 +7795,7 @@
         <v>717</v>
       </c>
       <c r="F58" s="85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G58" s="85" t="s">
         <v>719</v>
@@ -7790,11 +7811,11 @@
         <v>588</v>
       </c>
       <c r="L58" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M58" s="85"/>
       <c r="N58" s="85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="O58" s="85" t="s">
         <v>607</v>
@@ -7804,7 +7825,7 @@
       </c>
       <c r="Q58" s="85"/>
       <c r="R58" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="S58" s="96"/>
       <c r="V58" s="60"/>
@@ -7838,7 +7859,7 @@
         <v>682</v>
       </c>
       <c r="F60" s="84" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G60" s="84"/>
       <c r="H60" s="84" t="s">
@@ -7848,27 +7869,27 @@
         <v>728</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K60" s="84"/>
       <c r="L60" s="84" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M60" s="84" t="s">
         <v>608</v>
       </c>
       <c r="N60" s="84" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="O60" s="84" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P60" s="84"/>
       <c r="Q60" s="84" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="R60" s="84" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="S60" s="93"/>
       <c r="V60" s="60"/>
@@ -7878,8 +7899,8 @@
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="80" t="s">
-        <v>290</v>
+      <c r="D61" s="106" t="s">
+        <v>289</v>
       </c>
       <c r="E61" s="80" t="s">
         <v>248</v>
@@ -7891,10 +7912,10 @@
         <v>206</v>
       </c>
       <c r="H61" s="80" t="s">
+        <v>290</v>
+      </c>
+      <c r="I61" s="80" t="s">
         <v>291</v>
-      </c>
-      <c r="I61" s="80" t="s">
-        <v>292</v>
       </c>
       <c r="J61" s="80" t="s">
         <v>203</v>
@@ -7906,22 +7927,22 @@
         <v>235</v>
       </c>
       <c r="M61" s="80" t="s">
+        <v>391</v>
+      </c>
+      <c r="N61" s="80" t="s">
         <v>392</v>
       </c>
-      <c r="N61" s="80" t="s">
-        <v>393</v>
-      </c>
       <c r="O61" s="80" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P61" s="80" t="s">
         <v>190</v>
       </c>
       <c r="Q61" s="80" t="s">
+        <v>293</v>
+      </c>
+      <c r="R61" s="80" t="s">
         <v>294</v>
-      </c>
-      <c r="R61" s="80" t="s">
-        <v>295</v>
       </c>
       <c r="S61" s="94"/>
       <c r="V61" s="60"/>
@@ -7935,7 +7956,7 @@
         <v>683</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G62" s="85"/>
       <c r="H62" s="85" t="s">
@@ -7945,27 +7966,27 @@
         <v>729</v>
       </c>
       <c r="J62" s="85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K62" s="85"/>
       <c r="L62" s="85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M62" s="85" t="s">
         <v>609</v>
       </c>
       <c r="N62" s="85" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O62" s="85" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P62" s="85"/>
       <c r="Q62" s="85" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="R62" s="85" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="S62" s="96"/>
       <c r="V62" s="60"/>
@@ -7997,11 +8018,11 @@
         <v>610</v>
       </c>
       <c r="F64" s="84" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G64" s="84"/>
       <c r="H64" s="84" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I64" s="84" t="s">
         <v>730</v>
@@ -8014,7 +8035,7 @@
         <v>644</v>
       </c>
       <c r="M64" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="N64" s="84" t="s">
         <v>595</v>
@@ -8023,11 +8044,11 @@
         <v>734</v>
       </c>
       <c r="P64" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q64" s="84"/>
       <c r="R64" s="84" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="S64" s="93"/>
       <c r="V64" s="60"/>
@@ -8041,7 +8062,7 @@
         <v>267</v>
       </c>
       <c r="E65" s="80" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F65" s="80" t="s">
         <v>270</v>
@@ -8053,13 +8074,13 @@
         <v>276</v>
       </c>
       <c r="I65" s="80" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J65" s="80" t="s">
         <v>228</v>
       </c>
       <c r="K65" s="80" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L65" s="80" t="s">
         <v>189</v>
@@ -8071,7 +8092,7 @@
         <v>239</v>
       </c>
       <c r="O65" s="80" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P65" s="80" t="s">
         <v>193</v>
@@ -8080,7 +8101,7 @@
         <v>190</v>
       </c>
       <c r="R65" s="80" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S65" s="94"/>
       <c r="V65" s="60"/>
@@ -8092,11 +8113,11 @@
         <v>611</v>
       </c>
       <c r="F66" s="85" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G66" s="85"/>
       <c r="H66" s="85" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I66" s="85" t="s">
         <v>731</v>
@@ -8109,7 +8130,7 @@
         <v>645</v>
       </c>
       <c r="M66" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N66" s="85" t="s">
         <v>596</v>
@@ -8118,11 +8139,11 @@
         <v>735</v>
       </c>
       <c r="P66" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q66" s="85"/>
       <c r="R66" s="85" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="S66" s="96"/>
       <c r="V66" s="60"/>
@@ -8150,20 +8171,20 @@
     <row r="68" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="56"/>
       <c r="D68" s="84" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E68" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F68" s="84" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G68" s="84"/>
       <c r="H68" s="84" t="s">
         <v>718</v>
       </c>
       <c r="I68" s="84" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J68" s="84"/>
       <c r="K68" s="84"/>
@@ -8171,19 +8192,19 @@
         <v>658</v>
       </c>
       <c r="M68" s="84" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N68" s="84" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="O68" s="84" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="P68" s="84" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q68" s="84" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R68" s="84"/>
       <c r="S68" s="93"/>
@@ -8198,10 +8219,10 @@
         <v>275</v>
       </c>
       <c r="E69" s="80" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F69" s="80" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G69" s="81" t="s">
         <v>228</v>
@@ -8210,31 +8231,31 @@
         <v>285</v>
       </c>
       <c r="I69" s="80" t="s">
+        <v>298</v>
+      </c>
+      <c r="J69" s="80" t="s">
         <v>299</v>
       </c>
-      <c r="J69" s="80" t="s">
+      <c r="K69" s="80" t="s">
         <v>300</v>
       </c>
-      <c r="K69" s="80" t="s">
+      <c r="L69" s="80" t="s">
         <v>301</v>
       </c>
-      <c r="L69" s="80" t="s">
+      <c r="M69" s="80" t="s">
         <v>302</v>
       </c>
-      <c r="M69" s="80" t="s">
+      <c r="N69" s="80" t="s">
+        <v>397</v>
+      </c>
+      <c r="O69" s="80" t="s">
         <v>303</v>
       </c>
-      <c r="N69" s="80" t="s">
-        <v>398</v>
-      </c>
-      <c r="O69" s="80" t="s">
+      <c r="P69" s="80" t="s">
         <v>304</v>
       </c>
-      <c r="P69" s="80" t="s">
+      <c r="Q69" s="80" t="s">
         <v>305</v>
-      </c>
-      <c r="Q69" s="80" t="s">
-        <v>306</v>
       </c>
       <c r="R69" s="80" t="s">
         <v>190</v>
@@ -8245,20 +8266,20 @@
     <row r="70" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="58"/>
       <c r="D70" s="85" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E70" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F70" s="85" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G70" s="85"/>
       <c r="H70" s="85" t="s">
         <v>719</v>
       </c>
       <c r="I70" s="85" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J70" s="85"/>
       <c r="K70" s="85"/>
@@ -8266,19 +8287,19 @@
         <v>659</v>
       </c>
       <c r="M70" s="85" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N70" s="85" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="O70" s="85" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P70" s="85" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="Q70" s="85" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="R70" s="85"/>
       <c r="S70" s="96"/>
@@ -8316,26 +8337,26 @@
         <v>734</v>
       </c>
       <c r="G72" s="84" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H72" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I72" s="84" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J72" s="84" t="s">
         <v>734</v>
       </c>
       <c r="K72" s="84" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L72" s="84" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M72" s="84"/>
       <c r="N72" s="84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O72" s="84" t="s">
         <v>664</v>
@@ -8344,7 +8365,7 @@
         <v>783</v>
       </c>
       <c r="Q72" s="84" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="R72" s="84"/>
       <c r="S72" s="93"/>
@@ -8356,16 +8377,16 @@
         <v>18</v>
       </c>
       <c r="D73" s="80" t="s">
+        <v>306</v>
+      </c>
+      <c r="E73" s="80" t="s">
         <v>307</v>
       </c>
-      <c r="E73" s="80" t="s">
+      <c r="F73" s="80" t="s">
         <v>308</v>
       </c>
-      <c r="F73" s="80" t="s">
+      <c r="G73" s="81" t="s">
         <v>309</v>
-      </c>
-      <c r="G73" s="81" t="s">
-        <v>310</v>
       </c>
       <c r="H73" s="80" t="s">
         <v>193</v>
@@ -8374,28 +8395,28 @@
         <v>275</v>
       </c>
       <c r="J73" s="80" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K73" s="80" t="s">
+        <v>310</v>
+      </c>
+      <c r="L73" s="80" t="s">
         <v>311</v>
-      </c>
-      <c r="L73" s="80" t="s">
-        <v>312</v>
       </c>
       <c r="M73" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="N73" s="80" t="s">
-        <v>313</v>
+      <c r="N73" s="106" t="s">
+        <v>312</v>
       </c>
       <c r="O73" s="80" t="s">
         <v>229</v>
       </c>
       <c r="P73" s="80" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q73" s="80" t="s">
         <v>314</v>
-      </c>
-      <c r="Q73" s="80" t="s">
-        <v>315</v>
       </c>
       <c r="R73" s="80" t="s">
         <v>206</v>
@@ -8418,23 +8439,23 @@
         <v>782</v>
       </c>
       <c r="H74" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I74" s="85" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J74" s="85" t="s">
         <v>735</v>
       </c>
       <c r="K74" s="85" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L74" s="85" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M74" s="85"/>
       <c r="N74" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O74" s="85" t="s">
         <v>665</v>
@@ -8443,7 +8464,7 @@
         <v>632</v>
       </c>
       <c r="Q74" s="85" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="R74" s="85"/>
       <c r="S74" s="96"/>
@@ -8472,19 +8493,19 @@
     <row r="76" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="56"/>
       <c r="D76" s="84" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E76" s="84" t="s">
         <v>784</v>
       </c>
       <c r="F76" s="84" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G76" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H76" s="84" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I76" s="84" t="s">
         <v>612</v>
@@ -8492,7 +8513,7 @@
       <c r="J76" s="84"/>
       <c r="K76" s="84"/>
       <c r="L76" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M76" s="84"/>
       <c r="N76" s="84" t="s">
@@ -8502,10 +8523,10 @@
         <v>736</v>
       </c>
       <c r="P76" s="84" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q76" s="84" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="R76" s="84"/>
       <c r="S76" s="93"/>
@@ -8517,10 +8538,10 @@
         <v>19</v>
       </c>
       <c r="D77" s="80" t="s">
+        <v>315</v>
+      </c>
+      <c r="E77" s="80" t="s">
         <v>316</v>
-      </c>
-      <c r="E77" s="80" t="s">
-        <v>317</v>
       </c>
       <c r="F77" s="80" t="s">
         <v>281</v>
@@ -8529,37 +8550,37 @@
         <v>193</v>
       </c>
       <c r="H77" s="80" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I77" s="80" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J77" s="80" t="s">
         <v>228</v>
       </c>
       <c r="K77" s="80" t="s">
+        <v>318</v>
+      </c>
+      <c r="L77" s="80" t="s">
+        <v>288</v>
+      </c>
+      <c r="M77" s="80" t="s">
+        <v>300</v>
+      </c>
+      <c r="N77" s="80" t="s">
+        <v>399</v>
+      </c>
+      <c r="O77" s="80" t="s">
         <v>319</v>
       </c>
-      <c r="L77" s="80" t="s">
-        <v>289</v>
-      </c>
-      <c r="M77" s="80" t="s">
-        <v>301</v>
-      </c>
-      <c r="N77" s="80" t="s">
-        <v>400</v>
-      </c>
-      <c r="O77" s="80" t="s">
+      <c r="P77" s="80" t="s">
         <v>320</v>
       </c>
-      <c r="P77" s="80" t="s">
+      <c r="Q77" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="R77" s="80" t="s">
         <v>321</v>
-      </c>
-      <c r="Q77" s="80" t="s">
-        <v>303</v>
-      </c>
-      <c r="R77" s="80" t="s">
-        <v>322</v>
       </c>
       <c r="S77" s="94"/>
       <c r="V77" s="60"/>
@@ -8567,19 +8588,19 @@
     <row r="78" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="58"/>
       <c r="D78" s="85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E78" s="85" t="s">
         <v>785</v>
       </c>
       <c r="F78" s="85" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G78" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H78" s="85" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I78" s="85" t="s">
         <v>613</v>
@@ -8587,20 +8608,20 @@
       <c r="J78" s="85"/>
       <c r="K78" s="85"/>
       <c r="L78" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M78" s="85"/>
       <c r="N78" s="85" t="s">
         <v>615</v>
       </c>
       <c r="O78" s="85" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P78" s="85" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q78" s="85" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="R78" s="85"/>
       <c r="S78" s="96"/>
@@ -8630,10 +8651,10 @@
       <c r="B80" s="56"/>
       <c r="D80" s="84"/>
       <c r="E80" s="84" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F80" s="84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G80" s="84" t="s">
         <v>616</v>
@@ -8642,28 +8663,28 @@
         <v>595</v>
       </c>
       <c r="I80" s="84" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="J80" s="84"/>
       <c r="K80" s="84" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L80" s="84" t="s">
         <v>737</v>
       </c>
       <c r="M80" s="84" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N80" s="84"/>
       <c r="O80" s="84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P80" s="84"/>
       <c r="Q80" s="84" t="s">
         <v>734</v>
       </c>
       <c r="R80" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="S80" s="93"/>
       <c r="V80" s="60"/>
@@ -8674,22 +8695,22 @@
         <v>20</v>
       </c>
       <c r="D81" s="80" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E81" s="80" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F81" s="80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G81" s="80" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H81" s="80" t="s">
         <v>239</v>
       </c>
       <c r="I81" s="80" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J81" s="80" t="s">
         <v>190</v>
@@ -8698,10 +8719,10 @@
         <v>217</v>
       </c>
       <c r="L81" s="80" t="s">
+        <v>323</v>
+      </c>
+      <c r="M81" s="80" t="s">
         <v>324</v>
-      </c>
-      <c r="M81" s="80" t="s">
-        <v>325</v>
       </c>
       <c r="N81" s="80" t="s">
         <v>267</v>
@@ -8710,10 +8731,10 @@
         <v>186</v>
       </c>
       <c r="P81" s="80" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q81" s="80" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R81" s="80" t="s">
         <v>193</v>
@@ -8725,10 +8746,10 @@
       <c r="B82" s="58"/>
       <c r="D82" s="85"/>
       <c r="E82" s="85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F82" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G82" s="85" t="s">
         <v>617</v>
@@ -8737,28 +8758,28 @@
         <v>596</v>
       </c>
       <c r="I82" s="85" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J82" s="85"/>
       <c r="K82" s="85" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L82" s="85" t="s">
         <v>738</v>
       </c>
       <c r="M82" s="85" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N82" s="85"/>
       <c r="O82" s="85" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P82" s="85"/>
       <c r="Q82" s="85" t="s">
         <v>735</v>
       </c>
       <c r="R82" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="S82" s="96"/>
       <c r="V82" s="60"/>
@@ -8786,10 +8807,10 @@
     <row r="84" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="56"/>
       <c r="D84" s="84" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E84" s="84" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F84" s="84" t="s">
         <v>766</v>
@@ -8798,30 +8819,30 @@
         <v>726</v>
       </c>
       <c r="H84" s="84" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I84" s="84" t="s">
         <v>724</v>
       </c>
       <c r="J84" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K84" s="84"/>
       <c r="L84" s="84" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="M84" s="84" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="N84" s="84" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O84" s="84"/>
       <c r="P84" s="84" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q84" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="R84" s="84" t="s">
         <v>618</v>
@@ -8835,7 +8856,7 @@
         <v>21</v>
       </c>
       <c r="D85" s="80" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E85" s="80" t="s">
         <v>237</v>
@@ -8844,13 +8865,13 @@
         <v>196</v>
       </c>
       <c r="G85" s="81" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H85" s="80" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I85" s="80" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J85" s="80" t="s">
         <v>273</v>
@@ -8859,25 +8880,25 @@
         <v>190</v>
       </c>
       <c r="L85" s="80" t="s">
+        <v>327</v>
+      </c>
+      <c r="M85" s="80" t="s">
+        <v>402</v>
+      </c>
+      <c r="N85" s="80" t="s">
         <v>328</v>
-      </c>
-      <c r="M85" s="80" t="s">
-        <v>403</v>
-      </c>
-      <c r="N85" s="80" t="s">
-        <v>329</v>
       </c>
       <c r="O85" s="80" t="s">
         <v>228</v>
       </c>
       <c r="P85" s="80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q85" s="80" t="s">
         <v>193</v>
       </c>
       <c r="R85" s="80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S85" s="94"/>
       <c r="V85" s="60"/>
@@ -8885,10 +8906,10 @@
     <row r="86" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="58"/>
       <c r="D86" s="85" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E86" s="85" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F86" s="85" t="s">
         <v>767</v>
@@ -8897,30 +8918,30 @@
         <v>727</v>
       </c>
       <c r="H86" s="85" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I86" s="85" t="s">
         <v>725</v>
       </c>
       <c r="J86" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K86" s="85"/>
       <c r="L86" s="85" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M86" s="85" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="N86" s="85" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O86" s="85"/>
       <c r="P86" s="85" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="Q86" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R86" s="85" t="s">
         <v>619</v>
@@ -8957,23 +8978,23 @@
         <v>786</v>
       </c>
       <c r="F88" s="84" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G88" s="84" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H88" s="84" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I88" s="84"/>
       <c r="J88" s="84" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K88" s="84" t="s">
         <v>783</v>
       </c>
       <c r="L88" s="84" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="M88" s="84" t="s">
         <v>730</v>
@@ -8986,7 +9007,7 @@
         <v>654</v>
       </c>
       <c r="Q88" s="84" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="R88" s="84"/>
       <c r="S88" s="93"/>
@@ -9001,43 +9022,43 @@
         <v>229</v>
       </c>
       <c r="E89" s="80" t="s">
+        <v>330</v>
+      </c>
+      <c r="F89" s="80" t="s">
         <v>331</v>
-      </c>
-      <c r="F89" s="80" t="s">
-        <v>332</v>
       </c>
       <c r="G89" s="80" t="s">
         <v>231</v>
       </c>
       <c r="H89" s="80" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I89" s="80" t="s">
         <v>190</v>
       </c>
       <c r="J89" s="80" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K89" s="80" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L89" s="80" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M89" s="80" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N89" s="80" t="s">
         <v>228</v>
       </c>
       <c r="O89" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P89" s="80" t="s">
         <v>214</v>
       </c>
       <c r="Q89" s="80" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R89" s="80" t="s">
         <v>190</v>
@@ -9054,23 +9075,23 @@
         <v>787</v>
       </c>
       <c r="F90" s="85" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G90" s="85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H90" s="85" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I90" s="85"/>
       <c r="J90" s="85" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K90" s="85" t="s">
         <v>632</v>
       </c>
       <c r="L90" s="85" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M90" s="85" t="s">
         <v>731</v>
@@ -9083,7 +9104,7 @@
         <v>655</v>
       </c>
       <c r="Q90" s="85" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R90" s="85"/>
       <c r="S90" s="96"/>
@@ -9112,7 +9133,7 @@
     <row r="92" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="56"/>
       <c r="D92" s="84" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E92" s="84" t="s">
         <v>726</v>
@@ -9125,30 +9146,30 @@
         <v>644</v>
       </c>
       <c r="I92" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J92" s="84" t="s">
         <v>741</v>
       </c>
       <c r="K92" s="84" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L92" s="84"/>
       <c r="M92" s="84"/>
       <c r="N92" s="84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O92" s="84" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P92" s="84" t="s">
         <v>766</v>
       </c>
       <c r="Q92" s="84" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="R92" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="S92" s="93"/>
       <c r="V92" s="60"/>
@@ -9159,16 +9180,16 @@
         <v>23</v>
       </c>
       <c r="D93" s="80" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E93" s="80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F93" s="80" t="s">
         <v>228</v>
       </c>
       <c r="G93" s="81" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H93" s="80" t="s">
         <v>189</v>
@@ -9177,22 +9198,22 @@
         <v>193</v>
       </c>
       <c r="J93" s="80" t="s">
+        <v>335</v>
+      </c>
+      <c r="K93" s="80" t="s">
+        <v>298</v>
+      </c>
+      <c r="L93" s="80" t="s">
+        <v>299</v>
+      </c>
+      <c r="M93" s="80" t="s">
+        <v>300</v>
+      </c>
+      <c r="N93" s="80" t="s">
+        <v>312</v>
+      </c>
+      <c r="O93" s="80" t="s">
         <v>336</v>
-      </c>
-      <c r="K93" s="80" t="s">
-        <v>299</v>
-      </c>
-      <c r="L93" s="80" t="s">
-        <v>300</v>
-      </c>
-      <c r="M93" s="80" t="s">
-        <v>301</v>
-      </c>
-      <c r="N93" s="80" t="s">
-        <v>313</v>
-      </c>
-      <c r="O93" s="80" t="s">
-        <v>337</v>
       </c>
       <c r="P93" s="80" t="s">
         <v>196</v>
@@ -9209,7 +9230,7 @@
     <row r="94" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="58"/>
       <c r="D94" s="85" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E94" s="85" t="s">
         <v>727</v>
@@ -9222,30 +9243,30 @@
         <v>645</v>
       </c>
       <c r="I94" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J94" s="85" t="s">
         <v>742</v>
       </c>
       <c r="K94" s="85" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L94" s="85"/>
       <c r="M94" s="85"/>
       <c r="N94" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O94" s="85" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P94" s="85" t="s">
         <v>767</v>
       </c>
       <c r="Q94" s="85" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="R94" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="S94" s="96"/>
       <c r="V94" s="60"/>
@@ -9300,16 +9321,16 @@
         <v>24</v>
       </c>
       <c r="D97" s="80" t="s">
+        <v>337</v>
+      </c>
+      <c r="E97" s="80" t="s">
         <v>338</v>
-      </c>
-      <c r="E97" s="80" t="s">
-        <v>339</v>
       </c>
       <c r="F97" s="80" t="s">
         <v>228</v>
       </c>
       <c r="G97" s="81" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H97" s="80"/>
       <c r="I97" s="80"/>
@@ -9457,7 +9478,7 @@
       <c r="D104" s="84"/>
       <c r="E104" s="84"/>
       <c r="F104" s="84" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G104" s="84" t="s">
         <v>783</v>
@@ -9467,23 +9488,23 @@
         <v>642</v>
       </c>
       <c r="J104" s="84" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K104" s="84" t="s">
         <v>680</v>
       </c>
       <c r="L104" s="84"/>
       <c r="M104" s="84" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N104" s="84" t="s">
         <v>620</v>
       </c>
       <c r="O104" s="84" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P104" s="84" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q104" s="84"/>
       <c r="R104" s="84" t="s">
@@ -9504,10 +9525,10 @@
         <v>185</v>
       </c>
       <c r="F105" s="80" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G105" s="81" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H105" s="80" t="s">
         <v>190</v>
@@ -9525,13 +9546,13 @@
         <v>190</v>
       </c>
       <c r="M105" s="80" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N105" s="80" t="s">
+        <v>405</v>
+      </c>
+      <c r="O105" s="80" t="s">
         <v>406</v>
-      </c>
-      <c r="O105" s="80" t="s">
-        <v>407</v>
       </c>
       <c r="P105" s="80" t="s">
         <v>202</v>
@@ -9540,7 +9561,7 @@
         <v>190</v>
       </c>
       <c r="R105" s="80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S105" s="94"/>
       <c r="V105" s="60"/>
@@ -9550,7 +9571,7 @@
       <c r="D106" s="85"/>
       <c r="E106" s="85"/>
       <c r="F106" s="85" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G106" s="85" t="s">
         <v>632</v>
@@ -9560,23 +9581,23 @@
         <v>643</v>
       </c>
       <c r="J106" s="85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K106" s="85" t="s">
         <v>681</v>
       </c>
       <c r="L106" s="85"/>
       <c r="M106" s="85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N106" s="85" t="s">
         <v>621</v>
       </c>
       <c r="O106" s="85" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="P106" s="85" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q106" s="85"/>
       <c r="R106" s="85" t="s">
@@ -9611,27 +9632,27 @@
         <v>790</v>
       </c>
       <c r="E108" s="84" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F108" s="84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G108" s="84"/>
       <c r="H108" s="84" t="s">
+        <v>549</v>
+      </c>
+      <c r="I108" s="84" t="s">
         <v>550</v>
-      </c>
-      <c r="I108" s="84" t="s">
-        <v>551</v>
       </c>
       <c r="J108" s="84" t="s">
         <v>622</v>
       </c>
       <c r="K108" s="84"/>
       <c r="L108" s="84" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M108" s="84" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N108" s="84" t="s">
         <v>746</v>
@@ -9655,10 +9676,10 @@
         <v>27</v>
       </c>
       <c r="D109" s="80" t="s">
+        <v>341</v>
+      </c>
+      <c r="E109" s="80" t="s">
         <v>342</v>
-      </c>
-      <c r="E109" s="80" t="s">
-        <v>343</v>
       </c>
       <c r="F109" s="80" t="s">
         <v>203</v>
@@ -9667,37 +9688,37 @@
         <v>228</v>
       </c>
       <c r="H109" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="I109" s="80" t="s">
         <v>344</v>
       </c>
-      <c r="I109" s="80" t="s">
-        <v>345</v>
-      </c>
       <c r="J109" s="80" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K109" s="80" t="s">
         <v>190</v>
       </c>
       <c r="L109" s="80" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M109" s="80" t="s">
         <v>187</v>
       </c>
       <c r="N109" s="80" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O109" s="80" t="s">
         <v>190</v>
       </c>
       <c r="P109" s="80" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q109" s="80" t="s">
         <v>280</v>
       </c>
       <c r="R109" s="80" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S109" s="94"/>
       <c r="V109" s="60"/>
@@ -9708,27 +9729,27 @@
         <v>791</v>
       </c>
       <c r="E110" s="85" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F110" s="85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G110" s="85"/>
       <c r="H110" s="85" t="s">
         <v>745</v>
       </c>
       <c r="I110" s="85" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J110" s="85" t="s">
         <v>623</v>
       </c>
       <c r="K110" s="85"/>
       <c r="L110" s="85" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M110" s="85" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N110" s="85" t="s">
         <v>747</v>
@@ -9770,7 +9791,7 @@
       <c r="B112" s="56"/>
       <c r="D112" s="84"/>
       <c r="E112" s="84" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F112" s="84" t="s">
         <v>746</v>
@@ -9782,29 +9803,29 @@
         <v>748</v>
       </c>
       <c r="I112" s="84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J112" s="84" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K112" s="84" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L112" s="84" t="s">
         <v>774</v>
       </c>
       <c r="M112" s="84"/>
       <c r="N112" s="84" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="O112" s="84" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P112" s="84" t="s">
         <v>724</v>
       </c>
       <c r="Q112" s="84" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="R112" s="84"/>
       <c r="S112" s="93"/>
@@ -9822,19 +9843,19 @@
         <v>187</v>
       </c>
       <c r="F113" s="80" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G113" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H113" s="80" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I113" s="80" t="s">
         <v>193</v>
       </c>
       <c r="J113" s="80" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K113" s="80" t="s">
         <v>231</v>
@@ -9846,16 +9867,16 @@
         <v>190</v>
       </c>
       <c r="N113" s="80" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O113" s="80" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P113" s="80" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q113" s="80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R113" s="80" t="s">
         <v>190</v>
@@ -9867,7 +9888,7 @@
       <c r="B114" s="58"/>
       <c r="D114" s="85"/>
       <c r="E114" s="85" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F114" s="85" t="s">
         <v>747</v>
@@ -9879,29 +9900,29 @@
         <v>749</v>
       </c>
       <c r="I114" s="85" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J114" s="85" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K114" s="85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L114" s="85" t="s">
         <v>775</v>
       </c>
       <c r="M114" s="85"/>
       <c r="N114" s="85" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="O114" s="85" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="P114" s="85" t="s">
         <v>725</v>
       </c>
       <c r="Q114" s="85" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="R114" s="85"/>
       <c r="S114" s="96"/>
@@ -9930,13 +9951,13 @@
     <row r="116" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B116" s="56"/>
       <c r="D116" s="84" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E116" s="84" t="s">
         <v>750</v>
       </c>
       <c r="F116" s="84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G116" s="84" t="s">
         <v>664</v>
@@ -9945,7 +9966,7 @@
         <v>642</v>
       </c>
       <c r="I116" s="84" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J116" s="84"/>
       <c r="K116" s="84"/>
@@ -9965,13 +9986,13 @@
         <v>29</v>
       </c>
       <c r="D117" s="80" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E117" s="80" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F117" s="80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G117" s="81" t="s">
         <v>229</v>
@@ -9999,13 +10020,13 @@
     <row r="118" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="58"/>
       <c r="D118" s="85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E118" s="85" t="s">
         <v>751</v>
       </c>
       <c r="F118" s="85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G118" s="85" t="s">
         <v>665</v>
@@ -10014,7 +10035,7 @@
         <v>643</v>
       </c>
       <c r="I118" s="85" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J118" s="85"/>
       <c r="K118" s="85"/>
@@ -10148,14 +10169,14 @@
         <v>734</v>
       </c>
       <c r="J124" s="84" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K124" s="84"/>
       <c r="L124" s="84" t="s">
         <v>704</v>
       </c>
       <c r="M124" s="84" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N124" s="84" t="s">
         <v>734</v>
@@ -10165,10 +10186,10 @@
       </c>
       <c r="P124" s="84"/>
       <c r="Q124" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R124" s="84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S124" s="93"/>
       <c r="V124" s="60"/>
@@ -10185,34 +10206,34 @@
         <v>185</v>
       </c>
       <c r="F125" s="80" t="s">
+        <v>351</v>
+      </c>
+      <c r="G125" s="81" t="s">
         <v>352</v>
       </c>
-      <c r="G125" s="81" t="s">
+      <c r="H125" s="80" t="s">
         <v>353</v>
       </c>
-      <c r="H125" s="80" t="s">
+      <c r="I125" s="80" t="s">
+        <v>308</v>
+      </c>
+      <c r="J125" s="80" t="s">
         <v>354</v>
-      </c>
-      <c r="I125" s="80" t="s">
-        <v>309</v>
-      </c>
-      <c r="J125" s="80" t="s">
-        <v>355</v>
       </c>
       <c r="K125" s="80" t="s">
         <v>190</v>
       </c>
       <c r="L125" s="80" t="s">
+        <v>355</v>
+      </c>
+      <c r="M125" s="80" t="s">
         <v>356</v>
       </c>
-      <c r="M125" s="80" t="s">
+      <c r="N125" s="80" t="s">
         <v>357</v>
       </c>
-      <c r="N125" s="80" t="s">
-        <v>358</v>
-      </c>
       <c r="O125" s="80" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P125" s="80" t="s">
         <v>190</v>
@@ -10243,14 +10264,14 @@
         <v>735</v>
       </c>
       <c r="J126" s="85" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K126" s="85"/>
       <c r="L126" s="85" t="s">
         <v>705</v>
       </c>
       <c r="M126" s="85" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N126" s="85" t="s">
         <v>735</v>
@@ -10260,10 +10281,10 @@
       </c>
       <c r="P126" s="85"/>
       <c r="Q126" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="R126" s="85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S126" s="96"/>
       <c r="V126" s="60"/>
@@ -10295,10 +10316,10 @@
         <v>754</v>
       </c>
       <c r="F128" s="84" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G128" s="84" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H128" s="84" t="s">
         <v>774</v>
@@ -10308,24 +10329,24 @@
         <v>756</v>
       </c>
       <c r="K128" s="84" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L128" s="84"/>
       <c r="M128" s="84" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N128" s="84" t="s">
         <v>639</v>
       </c>
       <c r="O128" s="84" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="P128" s="84"/>
       <c r="Q128" s="84" t="s">
         <v>758</v>
       </c>
       <c r="R128" s="84" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="S128" s="93"/>
       <c r="V128" s="60"/>
@@ -10338,14 +10359,14 @@
       <c r="D129" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="E129" s="80" t="s">
+      <c r="E129" s="106" t="s">
         <v>629</v>
       </c>
       <c r="F129" s="80" t="s">
         <v>256</v>
       </c>
       <c r="G129" s="81" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H129" s="80" t="s">
         <v>274</v>
@@ -10354,31 +10375,31 @@
         <v>190</v>
       </c>
       <c r="J129" s="80" t="s">
+        <v>359</v>
+      </c>
+      <c r="K129" s="80" t="s">
         <v>360</v>
-      </c>
-      <c r="K129" s="80" t="s">
-        <v>361</v>
       </c>
       <c r="L129" s="80" t="s">
         <v>190</v>
       </c>
       <c r="M129" s="80" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N129" s="80" t="s">
+        <v>361</v>
+      </c>
+      <c r="O129" s="80" t="s">
         <v>362</v>
-      </c>
-      <c r="O129" s="80" t="s">
-        <v>363</v>
       </c>
       <c r="P129" s="80" t="s">
         <v>228</v>
       </c>
       <c r="Q129" s="80" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="R129" s="80" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S129" s="94"/>
       <c r="V129" s="60"/>
@@ -10390,10 +10411,10 @@
         <v>755</v>
       </c>
       <c r="F130" s="85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G130" s="85" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H130" s="85" t="s">
         <v>775</v>
@@ -10403,24 +10424,24 @@
         <v>757</v>
       </c>
       <c r="K130" s="85" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L130" s="85"/>
       <c r="M130" s="85" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="N130" s="85" t="s">
         <v>640</v>
       </c>
       <c r="O130" s="85" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="P130" s="85"/>
       <c r="Q130" s="85" t="s">
         <v>759</v>
       </c>
       <c r="R130" s="85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="S130" s="96"/>
       <c r="V130" s="60"/>
@@ -10448,16 +10469,16 @@
     <row r="132" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B132" s="56"/>
       <c r="D132" s="84" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E132" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F132" s="84" t="s">
         <v>760</v>
       </c>
       <c r="G132" s="84" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H132" s="84"/>
       <c r="I132" s="84"/>
@@ -10482,13 +10503,13 @@
         <v>217</v>
       </c>
       <c r="E133" s="80" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F133" s="80" t="s">
+        <v>364</v>
+      </c>
+      <c r="G133" s="81" t="s">
         <v>365</v>
-      </c>
-      <c r="G133" s="81" t="s">
-        <v>366</v>
       </c>
       <c r="H133" s="80" t="s">
         <v>228</v>
@@ -10509,16 +10530,16 @@
     <row r="134" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="58"/>
       <c r="D134" s="85" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E134" s="85" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F134" s="85" t="s">
         <v>761</v>
       </c>
       <c r="G134" s="85" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H134" s="85"/>
       <c r="I134" s="85"/>
@@ -12713,27 +12734,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:R7">
-    <cfRule type="expression" dxfId="45" priority="38">
+    <cfRule type="expression" dxfId="45" priority="37">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="38">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="37">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
-    <cfRule type="expression" dxfId="43" priority="36">
+    <cfRule type="expression" dxfId="43" priority="35">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="36">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="35">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="41" priority="34">
+    <cfRule type="expression" dxfId="41" priority="33">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="34">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="33">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
@@ -12745,27 +12766,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23:R23 D39:R39 D87:R87 D91:R91 D95:R95 D99:R99 D103:R103 D111:R111 D115:R115 D119:R119 D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="37" priority="46">
+    <cfRule type="expression" dxfId="37" priority="45">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="46">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="45">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="35" priority="30">
+    <cfRule type="expression" dxfId="35" priority="29">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="30">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="29">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
-    <cfRule type="expression" dxfId="33" priority="28">
+    <cfRule type="expression" dxfId="33" priority="27">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="28">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="27">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
@@ -12777,19 +12798,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="29" priority="24">
+    <cfRule type="expression" dxfId="29" priority="23">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="24">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="23">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
-    <cfRule type="expression" dxfId="27" priority="22">
+    <cfRule type="expression" dxfId="27" priority="21">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="22">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="21">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
@@ -12801,19 +12822,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:R55">
-    <cfRule type="expression" dxfId="23" priority="18">
+    <cfRule type="expression" dxfId="23" priority="17">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="18">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="17">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:R59">
-    <cfRule type="expression" dxfId="21" priority="16">
+    <cfRule type="expression" dxfId="21" priority="15">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="16">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="15">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
@@ -12825,11 +12846,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
-    <cfRule type="expression" dxfId="17" priority="12">
+    <cfRule type="expression" dxfId="17" priority="11">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="12">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="11">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D71:R71">
@@ -12841,11 +12862,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="7">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
@@ -12865,11 +12886,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
@@ -12953,7 +12974,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="103" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -12971,7 +12992,7 @@
       <c r="G5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="102" t="s">
+      <c r="I5" s="103" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -12996,7 +13017,7 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B6" s="103"/>
+      <c r="B6" s="104"/>
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
@@ -13016,7 +13037,7 @@
         <f>$B5 &amp; G$4</f>
         <v>陰入</v>
       </c>
-      <c r="I6" s="103"/>
+      <c r="I6" s="104"/>
       <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
@@ -13038,7 +13059,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B7" s="103"/>
+      <c r="B7" s="104"/>
       <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
@@ -13054,7 +13075,7 @@
       <c r="G7" s="16">
         <v>30</v>
       </c>
-      <c r="I7" s="103"/>
+      <c r="I7" s="104"/>
       <c r="J7" s="15" t="s">
         <v>22</v>
       </c>
@@ -13076,7 +13097,7 @@
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B8" s="103"/>
+      <c r="B8" s="104"/>
       <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
@@ -13092,7 +13113,7 @@
       <c r="G8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="103"/>
+      <c r="I8" s="104"/>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
@@ -13114,7 +13135,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B9" s="103"/>
+      <c r="B9" s="104"/>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
@@ -13130,7 +13151,7 @@
       <c r="G9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="103"/>
+      <c r="I9" s="104"/>
       <c r="J9" s="11" t="s">
         <v>33</v>
       </c>
@@ -13152,7 +13173,7 @@
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B10" s="104"/>
+      <c r="B10" s="105"/>
       <c r="C10" s="11" t="s">
         <v>38</v>
       </c>
@@ -13168,7 +13189,7 @@
       <c r="G10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="104"/>
+      <c r="I10" s="105"/>
       <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
@@ -13191,7 +13212,7 @@
       <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="103" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -13209,7 +13230,7 @@
       <c r="G11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="102" t="s">
+      <c r="I11" s="103" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -13233,7 +13254,7 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B12" s="103"/>
+      <c r="B12" s="104"/>
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
@@ -13253,7 +13274,7 @@
         <f>$B11 &amp; G$4</f>
         <v>陽入</v>
       </c>
-      <c r="I12" s="103"/>
+      <c r="I12" s="104"/>
       <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
@@ -13273,7 +13294,7 @@
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B13" s="103"/>
+      <c r="B13" s="104"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
@@ -13287,7 +13308,7 @@
       <c r="G13" s="16">
         <v>50</v>
       </c>
-      <c r="I13" s="103"/>
+      <c r="I13" s="104"/>
       <c r="J13" s="15" t="s">
         <v>22</v>
       </c>
@@ -13307,7 +13328,7 @@
       <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B14" s="103"/>
+      <c r="B14" s="104"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -13321,7 +13342,7 @@
       <c r="G14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="103"/>
+      <c r="I14" s="104"/>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
@@ -13341,7 +13362,7 @@
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B15" s="103"/>
+      <c r="B15" s="104"/>
       <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
@@ -13355,7 +13376,7 @@
       <c r="G15" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="103"/>
+      <c r="I15" s="104"/>
       <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
@@ -13375,7 +13396,7 @@
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B16" s="104"/>
+      <c r="B16" s="105"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
       </c>
@@ -13389,7 +13410,7 @@
       <c r="G16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="104"/>
+      <c r="I16" s="105"/>
       <c r="J16" s="11" t="s">
         <v>43</v>
       </c>

--- a/output5/【河洛話注音】桃花源記【文讀音】.xlsx
+++ b/output5/【河洛話注音】桃花源記【文讀音】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7935932A-2DCC-45BE-8350-8238931C9581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{679082E1-F881-4FC8-80FC-1AF497F08CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="794">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1883,14 +1883,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>loo7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1967,14 +1959,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pian7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>it4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2103,14 +2087,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>zok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>huat4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2391,22 +2367,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>siong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>kui1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2455,14 +2415,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>siok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>than3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2523,14 +2475,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sim7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆬ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zian5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2555,14 +2499,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>jiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sip8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2575,22 +2511,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ziong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tai7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2599,22 +2519,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>iau3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄠ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄚㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>kik4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2655,14 +2559,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ha7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄚ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zik4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2695,18 +2591,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㄗㄨㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kin7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>thong1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2743,22 +2627,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tiong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>piong5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2783,14 +2651,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hiong1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2799,14 +2659,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sian3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>phin1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2823,14 +2675,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zin2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2871,22 +2715,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>kong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sia3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄚ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>suan5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2895,14 +2723,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ziong7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㆢㄧㆴ˙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2915,14 +2735,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>zai7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄞ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㄒㄧㆴ˙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2999,14 +2811,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sit4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3015,14 +2819,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ju7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆡㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ping2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3031,14 +2827,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>thi3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zi7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3047,22 +2835,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gak8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄚㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hian7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>su2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3087,22 +2859,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sut4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zi2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3115,14 +2871,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lut7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨㆵ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ting5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3131,14 +2879,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tau2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3151,22 +2891,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>siu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄨ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khian3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄧㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>me5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3199,14 +2923,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hio5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄜˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zin1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3239,14 +2955,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>uan7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zau2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3271,14 +2979,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>i3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zut1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3287,38 +2987,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ze3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㄧㆴ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>zut4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ian7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ia2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3335,14 +3007,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>uat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄚㆵ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>iong5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3352,6 +3016,330 @@
   </si>
   <si>
     <t>樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄣˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆬˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jia5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㄚˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄞˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bun5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㆦ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ju5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆡㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gau7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄠ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kian3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iau1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄠˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sai3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄞ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ze1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>piu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zui3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lun5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sue3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hio2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄜˋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4386,6 +4374,9 @@
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="62" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -4402,9 +4393,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5543,7 +5531,7 @@
         <v>165</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -5559,7 +5547,7 @@
         <v>181</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>641</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -5596,10 +5584,10 @@
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="99" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -5673,7 +5661,7 @@
       <c r="Q3" s="83"/>
       <c r="R3" s="83"/>
       <c r="T3" s="92"/>
-      <c r="V3" s="100" t="s">
+      <c r="V3" s="101" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5691,42 +5679,42 @@
         <v>417</v>
       </c>
       <c r="I4" s="84" t="s">
-        <v>644</v>
+        <v>713</v>
       </c>
       <c r="J4" s="84" t="s">
-        <v>763</v>
+        <v>692</v>
       </c>
       <c r="K4" s="84" t="s">
         <v>419</v>
       </c>
       <c r="L4" s="84" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="M4" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="N4" s="84" t="s">
-        <v>762</v>
+        <v>691</v>
       </c>
       <c r="O4" s="84" t="s">
         <v>421</v>
       </c>
       <c r="P4" s="84" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="Q4" s="84" t="s">
-        <v>766</v>
+        <v>695</v>
       </c>
       <c r="R4" s="84" t="s">
         <v>423</v>
       </c>
       <c r="S4" s="93" t="s">
-        <v>764</v>
+        <v>693</v>
       </c>
       <c r="T4" s="1">
         <v>8</v>
       </c>
-      <c r="V4" s="101"/>
+      <c r="V4" s="102"/>
     </row>
     <row r="5" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -5778,7 +5766,7 @@
         <v>197</v>
       </c>
       <c r="S5" s="94"/>
-      <c r="V5" s="101"/>
+      <c r="V5" s="102"/>
     </row>
     <row r="6" spans="2:29" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
@@ -5795,33 +5783,33 @@
         <v>418</v>
       </c>
       <c r="I6" s="85" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85" t="s">
         <v>420</v>
       </c>
       <c r="L6" s="85" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="M6" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="N6" s="85"/>
       <c r="O6" s="85" t="s">
         <v>422</v>
       </c>
       <c r="P6" s="85" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="Q6" s="85" t="s">
-        <v>767</v>
+        <v>696</v>
       </c>
       <c r="R6" s="85" t="s">
         <v>424</v>
       </c>
       <c r="S6" s="95"/>
-      <c r="V6" s="101"/>
+      <c r="V6" s="102"/>
     </row>
     <row r="7" spans="2:29" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -5830,7 +5818,7 @@
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
       <c r="G7" s="83" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
@@ -5844,58 +5832,58 @@
       <c r="Q7" s="83"/>
       <c r="R7" s="83"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="101"/>
+      <c r="V7" s="102"/>
     </row>
     <row r="8" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
       <c r="D8" s="84"/>
       <c r="E8" s="84" t="s">
-        <v>768</v>
+        <v>715</v>
       </c>
       <c r="F8" s="84" t="s">
         <v>427</v>
       </c>
       <c r="G8" s="84" t="s">
-        <v>646</v>
+        <v>568</v>
       </c>
       <c r="H8" s="84"/>
       <c r="I8" s="84" t="s">
+        <v>718</v>
+      </c>
+      <c r="J8" s="84" t="s">
         <v>429</v>
       </c>
-      <c r="J8" s="84" t="s">
+      <c r="K8" s="84" t="s">
         <v>431</v>
       </c>
-      <c r="K8" s="84" t="s">
+      <c r="L8" s="84" t="s">
+        <v>720</v>
+      </c>
+      <c r="M8" s="84" t="s">
+        <v>722</v>
+      </c>
+      <c r="N8" s="84" t="s">
+        <v>691</v>
+      </c>
+      <c r="O8" s="84" t="s">
         <v>433</v>
       </c>
-      <c r="L8" s="84" t="s">
-        <v>768</v>
-      </c>
-      <c r="M8" s="84" t="s">
-        <v>633</v>
-      </c>
-      <c r="N8" s="84" t="s">
-        <v>762</v>
-      </c>
-      <c r="O8" s="84" t="s">
-        <v>435</v>
-      </c>
       <c r="P8" s="84" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
       <c r="Q8" s="84" t="s">
-        <v>650</v>
+        <v>617</v>
       </c>
       <c r="R8" s="84" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="S8" s="93" t="s">
-        <v>765</v>
+        <v>694</v>
       </c>
       <c r="T8" s="1">
         <v>1</v>
       </c>
-      <c r="V8" s="101"/>
+      <c r="V8" s="102"/>
     </row>
     <row r="9" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -5938,7 +5926,7 @@
       <c r="O9" s="80" t="s">
         <v>207</v>
       </c>
-      <c r="P9" s="106" t="s">
+      <c r="P9" s="100" t="s">
         <v>208</v>
       </c>
       <c r="Q9" s="98" t="s">
@@ -5949,51 +5937,51 @@
       </c>
       <c r="S9" s="94"/>
       <c r="T9" s="92"/>
-      <c r="V9" s="101"/>
+      <c r="V9" s="102"/>
     </row>
     <row r="10" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
       <c r="D10" s="85"/>
       <c r="E10" s="85" t="s">
-        <v>769</v>
+        <v>716</v>
       </c>
       <c r="F10" s="85" t="s">
         <v>428</v>
       </c>
       <c r="G10" s="85" t="s">
-        <v>647</v>
+        <v>717</v>
       </c>
       <c r="H10" s="85"/>
       <c r="I10" s="85" t="s">
+        <v>719</v>
+      </c>
+      <c r="J10" s="85" t="s">
         <v>430</v>
       </c>
-      <c r="J10" s="85" t="s">
+      <c r="K10" s="85" t="s">
         <v>432</v>
       </c>
-      <c r="K10" s="85" t="s">
-        <v>434</v>
-      </c>
       <c r="L10" s="85" t="s">
-        <v>769</v>
+        <v>721</v>
       </c>
       <c r="M10" s="85" t="s">
-        <v>634</v>
+        <v>723</v>
       </c>
       <c r="N10" s="85"/>
       <c r="O10" s="85" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P10" s="85" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="Q10" s="85" t="s">
-        <v>651</v>
+        <v>618</v>
       </c>
       <c r="R10" s="85" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="S10" s="96"/>
-      <c r="V10" s="101"/>
+      <c r="V10" s="102"/>
     </row>
     <row r="11" spans="2:29" s="66" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="65"/>
@@ -6013,51 +6001,51 @@
       <c r="P11" s="83"/>
       <c r="Q11" s="83"/>
       <c r="R11" s="83"/>
-      <c r="V11" s="101"/>
+      <c r="V11" s="102"/>
     </row>
     <row r="12" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
       <c r="D12" s="84" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="E12" s="84"/>
       <c r="F12" s="84" t="s">
-        <v>652</v>
+        <v>619</v>
       </c>
       <c r="G12" s="84" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="H12" s="84" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="I12" s="84" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="J12" s="84" t="s">
         <v>421</v>
       </c>
       <c r="K12" s="84"/>
       <c r="L12" s="84" t="s">
-        <v>644</v>
+        <v>713</v>
       </c>
       <c r="M12" s="84" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="N12" s="84" t="s">
         <v>371</v>
       </c>
       <c r="O12" s="84" t="s">
-        <v>558</v>
+        <v>667</v>
       </c>
       <c r="P12" s="84"/>
       <c r="Q12" s="84" t="s">
-        <v>656</v>
+        <v>621</v>
       </c>
       <c r="R12" s="84" t="s">
-        <v>770</v>
+        <v>697</v>
       </c>
       <c r="S12" s="93"/>
-      <c r="V12" s="101"/>
+      <c r="V12" s="102"/>
     </row>
     <row r="13" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -6110,51 +6098,51 @@
         <v>221</v>
       </c>
       <c r="S13" s="94"/>
-      <c r="V13" s="101"/>
+      <c r="V13" s="102"/>
     </row>
     <row r="14" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
       <c r="D14" s="85" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="E14" s="85"/>
       <c r="F14" s="85" t="s">
-        <v>653</v>
+        <v>620</v>
       </c>
       <c r="G14" s="85" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="H14" s="85" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="I14" s="85" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="J14" s="85" t="s">
         <v>422</v>
       </c>
       <c r="K14" s="85"/>
       <c r="L14" s="85" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="M14" s="85" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="N14" s="85" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="O14" s="85" t="s">
-        <v>559</v>
+        <v>668</v>
       </c>
       <c r="P14" s="85"/>
       <c r="Q14" s="85" t="s">
-        <v>657</v>
+        <v>622</v>
       </c>
       <c r="R14" s="85" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="S14" s="96"/>
-      <c r="V14" s="101"/>
+      <c r="V14" s="102"/>
     </row>
     <row r="15" spans="2:29" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -6174,7 +6162,7 @@
       <c r="P15" s="83"/>
       <c r="Q15" s="83"/>
       <c r="R15" s="83"/>
-      <c r="V15" s="101"/>
+      <c r="V15" s="102"/>
       <c r="AC15" s="67" t="s">
         <v>184</v>
       </c>
@@ -6182,46 +6170,46 @@
     <row r="16" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="56"/>
       <c r="D16" s="84" t="s">
-        <v>658</v>
+        <v>724</v>
       </c>
       <c r="E16" s="84" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F16" s="84"/>
       <c r="G16" s="84" t="s">
         <v>386</v>
       </c>
       <c r="H16" s="84" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I16" s="84" t="s">
-        <v>660</v>
+        <v>623</v>
       </c>
       <c r="J16" s="84" t="s">
-        <v>662</v>
+        <v>625</v>
       </c>
       <c r="K16" s="84"/>
       <c r="L16" s="84" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="M16" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="N16" s="84" t="s">
-        <v>589</v>
+        <v>726</v>
       </c>
       <c r="O16" s="84" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P16" s="84" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q16" s="84"/>
       <c r="R16" s="84" t="s">
-        <v>664</v>
+        <v>728</v>
       </c>
       <c r="S16" s="93"/>
-      <c r="V16" s="101"/>
+      <c r="V16" s="102"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -6243,7 +6231,7 @@
       <c r="H17" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="I17" s="106" t="s">
+      <c r="I17" s="100" t="s">
         <v>224</v>
       </c>
       <c r="J17" s="98" t="s">
@@ -6274,51 +6262,51 @@
         <v>229</v>
       </c>
       <c r="S17" s="94"/>
-      <c r="V17" s="101"/>
+      <c r="V17" s="102"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
       <c r="D18" s="85" t="s">
-        <v>659</v>
+        <v>725</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F18" s="85"/>
       <c r="G18" s="85" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="H18" s="85" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I18" s="85" t="s">
-        <v>661</v>
+        <v>624</v>
       </c>
       <c r="J18" s="85" t="s">
-        <v>663</v>
+        <v>626</v>
       </c>
       <c r="K18" s="85"/>
       <c r="L18" s="85" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="M18" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="N18" s="85" t="s">
-        <v>590</v>
+        <v>727</v>
       </c>
       <c r="O18" s="85" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="P18" s="85" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q18" s="85"/>
       <c r="R18" s="85" t="s">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="S18" s="96"/>
-      <c r="V18" s="101"/>
+      <c r="V18" s="102"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -6338,28 +6326,28 @@
       <c r="P19" s="83"/>
       <c r="Q19" s="83"/>
       <c r="R19" s="83"/>
-      <c r="V19" s="101"/>
+      <c r="V19" s="102"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
       <c r="D20" s="84" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="E20" s="84" t="s">
-        <v>646</v>
+        <v>435</v>
       </c>
       <c r="F20" s="84"/>
       <c r="G20" s="84" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="H20" s="84" t="s">
+        <v>444</v>
+      </c>
+      <c r="I20" s="84" t="s">
         <v>446</v>
       </c>
-      <c r="I20" s="84" t="s">
-        <v>448</v>
-      </c>
       <c r="J20" s="84" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="K20" s="84"/>
       <c r="L20" s="84"/>
@@ -6370,7 +6358,7 @@
       <c r="Q20" s="84"/>
       <c r="R20" s="84"/>
       <c r="S20" s="93"/>
-      <c r="V20" s="101"/>
+      <c r="V20" s="102"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -6409,28 +6397,28 @@
       <c r="Q21" s="80"/>
       <c r="R21" s="80"/>
       <c r="S21" s="94"/>
-      <c r="V21" s="101"/>
+      <c r="V21" s="102"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
       <c r="D22" s="85" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="E22" s="85" t="s">
-        <v>647</v>
+        <v>436</v>
       </c>
       <c r="F22" s="85"/>
       <c r="G22" s="85" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H22" s="85" t="s">
+        <v>445</v>
+      </c>
+      <c r="I22" s="85" t="s">
         <v>447</v>
       </c>
-      <c r="I22" s="85" t="s">
-        <v>449</v>
-      </c>
       <c r="J22" s="85" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="K22" s="85"/>
       <c r="L22" s="85"/>
@@ -6441,7 +6429,7 @@
       <c r="Q22" s="85"/>
       <c r="R22" s="85"/>
       <c r="S22" s="96"/>
-      <c r="V22" s="102"/>
+      <c r="V22" s="103"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -6559,39 +6547,39 @@
       <c r="D28" s="84"/>
       <c r="E28" s="84"/>
       <c r="F28" s="84" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="G28" s="84" t="s">
-        <v>666</v>
+        <v>627</v>
       </c>
       <c r="H28" s="84" t="s">
-        <v>668</v>
+        <v>629</v>
       </c>
       <c r="I28" s="84" t="s">
         <v>417</v>
       </c>
       <c r="J28" s="84"/>
       <c r="K28" s="84" t="s">
+        <v>647</v>
+      </c>
+      <c r="L28" s="84" t="s">
+        <v>613</v>
+      </c>
+      <c r="M28" s="84" t="s">
+        <v>448</v>
+      </c>
+      <c r="N28" s="84" t="s">
         <v>450</v>
-      </c>
-      <c r="L28" s="84" t="s">
-        <v>642</v>
-      </c>
-      <c r="M28" s="84" t="s">
-        <v>452</v>
-      </c>
-      <c r="N28" s="84" t="s">
-        <v>454</v>
       </c>
       <c r="O28" s="84"/>
       <c r="P28" s="84" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Q28" s="84" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="R28" s="84" t="s">
-        <v>670</v>
+        <v>631</v>
       </c>
       <c r="S28" s="93"/>
       <c r="U28" s="67" t="str">
@@ -6662,39 +6650,39 @@
       <c r="D30" s="85"/>
       <c r="E30" s="85"/>
       <c r="F30" s="85" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="G30" s="85" t="s">
-        <v>667</v>
+        <v>628</v>
       </c>
       <c r="H30" s="85" t="s">
-        <v>669</v>
+        <v>630</v>
       </c>
       <c r="I30" s="85" t="s">
         <v>418</v>
       </c>
       <c r="J30" s="85"/>
       <c r="K30" s="85" t="s">
+        <v>648</v>
+      </c>
+      <c r="L30" s="85" t="s">
+        <v>614</v>
+      </c>
+      <c r="M30" s="85" t="s">
+        <v>449</v>
+      </c>
+      <c r="N30" s="85" t="s">
         <v>451</v>
-      </c>
-      <c r="L30" s="85" t="s">
-        <v>643</v>
-      </c>
-      <c r="M30" s="85" t="s">
-        <v>453</v>
-      </c>
-      <c r="N30" s="85" t="s">
-        <v>455</v>
       </c>
       <c r="O30" s="85"/>
       <c r="P30" s="85" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="Q30" s="85" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="R30" s="85" t="s">
-        <v>671</v>
+        <v>632</v>
       </c>
       <c r="S30" s="96"/>
       <c r="U30" s="67" t="str">
@@ -6730,43 +6718,43 @@
     <row r="32" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="56"/>
       <c r="D32" s="84" t="s">
-        <v>672</v>
+        <v>633</v>
       </c>
       <c r="E32" s="84"/>
       <c r="F32" s="84" t="s">
-        <v>674</v>
+        <v>635</v>
       </c>
       <c r="G32" s="84" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H32" s="84" t="s">
-        <v>597</v>
+        <v>730</v>
       </c>
       <c r="I32" s="84" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="J32" s="84" t="s">
-        <v>676</v>
+        <v>732</v>
       </c>
       <c r="K32" s="84"/>
       <c r="L32" s="84" t="s">
-        <v>450</v>
+        <v>647</v>
       </c>
       <c r="M32" s="84" t="s">
-        <v>678</v>
+        <v>734</v>
       </c>
       <c r="N32" s="84" t="s">
-        <v>680</v>
+        <v>637</v>
       </c>
       <c r="O32" s="84"/>
       <c r="P32" s="84" t="s">
-        <v>682</v>
+        <v>736</v>
       </c>
       <c r="Q32" s="84" t="s">
-        <v>672</v>
+        <v>633</v>
       </c>
       <c r="R32" s="84" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="S32" s="93"/>
       <c r="U32" s="67" t="str">
@@ -6810,7 +6798,7 @@
       <c r="M33" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="N33" s="106" t="s">
+      <c r="N33" s="100" t="s">
         <v>247</v>
       </c>
       <c r="O33" s="80" t="s">
@@ -6831,43 +6819,43 @@
     <row r="34" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="58"/>
       <c r="D34" s="85" t="s">
-        <v>673</v>
+        <v>634</v>
       </c>
       <c r="E34" s="85"/>
       <c r="F34" s="85" t="s">
-        <v>675</v>
+        <v>636</v>
       </c>
       <c r="G34" s="85" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H34" s="85" t="s">
-        <v>598</v>
+        <v>731</v>
       </c>
       <c r="I34" s="85" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="J34" s="85" t="s">
-        <v>677</v>
+        <v>733</v>
       </c>
       <c r="K34" s="85"/>
       <c r="L34" s="85" t="s">
-        <v>451</v>
+        <v>648</v>
       </c>
       <c r="M34" s="85" t="s">
-        <v>679</v>
+        <v>735</v>
       </c>
       <c r="N34" s="85" t="s">
-        <v>681</v>
+        <v>638</v>
       </c>
       <c r="O34" s="85"/>
       <c r="P34" s="85" t="s">
-        <v>683</v>
+        <v>737</v>
       </c>
       <c r="Q34" s="85" t="s">
-        <v>673</v>
+        <v>634</v>
       </c>
       <c r="R34" s="85" t="s">
-        <v>684</v>
+        <v>639</v>
       </c>
       <c r="S34" s="96"/>
       <c r="V34" s="60"/>
@@ -6896,36 +6884,36 @@
       <c r="B36" s="56"/>
       <c r="D36" s="84"/>
       <c r="E36" s="84" t="s">
-        <v>771</v>
+        <v>698</v>
       </c>
       <c r="F36" s="84" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G36" s="84" t="s">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="H36" s="84"/>
       <c r="I36" s="84" t="s">
-        <v>687</v>
+        <v>738</v>
       </c>
       <c r="J36" s="84" t="s">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="K36" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="L36" s="84"/>
       <c r="M36" s="84" t="s">
-        <v>664</v>
+        <v>728</v>
       </c>
       <c r="N36" s="84" t="s">
-        <v>646</v>
+        <v>435</v>
       </c>
       <c r="O36" s="84" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="P36" s="84" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="Q36" s="84" t="s">
         <v>421</v>
@@ -6991,36 +6979,36 @@
       <c r="B38" s="58"/>
       <c r="D38" s="85"/>
       <c r="E38" s="85" t="s">
-        <v>772</v>
+        <v>699</v>
       </c>
       <c r="F38" s="85" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G38" s="85" t="s">
-        <v>686</v>
+        <v>641</v>
       </c>
       <c r="H38" s="85"/>
       <c r="I38" s="85" t="s">
-        <v>688</v>
+        <v>739</v>
       </c>
       <c r="J38" s="85" t="s">
-        <v>636</v>
+        <v>607</v>
       </c>
       <c r="K38" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="L38" s="85"/>
       <c r="M38" s="85" t="s">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="N38" s="85" t="s">
-        <v>647</v>
+        <v>436</v>
       </c>
       <c r="O38" s="85" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="P38" s="85" t="s">
-        <v>689</v>
+        <v>642</v>
       </c>
       <c r="Q38" s="85" t="s">
         <v>422</v>
@@ -7052,42 +7040,42 @@
     <row r="40" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="56"/>
       <c r="D40" s="84" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="E40" s="84" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F40" s="84" t="s">
-        <v>690</v>
+        <v>643</v>
       </c>
       <c r="G40" s="84" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H40" s="84"/>
       <c r="I40" s="84" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J40" s="84" t="s">
-        <v>692</v>
+        <v>645</v>
       </c>
       <c r="K40" s="84" t="s">
-        <v>694</v>
+        <v>647</v>
       </c>
       <c r="L40" s="84" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="M40" s="84"/>
       <c r="N40" s="84" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="O40" s="84" t="s">
-        <v>678</v>
+        <v>734</v>
       </c>
       <c r="P40" s="84" t="s">
-        <v>696</v>
+        <v>649</v>
       </c>
       <c r="Q40" s="84" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="R40" s="84"/>
       <c r="S40" s="93"/>
@@ -7119,7 +7107,7 @@
       <c r="J41" s="80" t="s">
         <v>260</v>
       </c>
-      <c r="K41" s="106" t="s">
+      <c r="K41" s="100" t="s">
         <v>261</v>
       </c>
       <c r="L41" s="80" t="s">
@@ -7134,7 +7122,7 @@
       <c r="O41" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="P41" s="106" t="s">
+      <c r="P41" s="100" t="s">
         <v>264</v>
       </c>
       <c r="Q41" s="80" t="s">
@@ -7149,42 +7137,42 @@
     <row r="42" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="58"/>
       <c r="D42" s="85" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E42" s="85" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F42" s="85" t="s">
-        <v>691</v>
+        <v>644</v>
       </c>
       <c r="G42" s="85" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H42" s="85"/>
       <c r="I42" s="85" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J42" s="85" t="s">
-        <v>693</v>
+        <v>646</v>
       </c>
       <c r="K42" s="85" t="s">
-        <v>695</v>
+        <v>648</v>
       </c>
       <c r="L42" s="85" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="M42" s="85"/>
       <c r="N42" s="85" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="O42" s="85" t="s">
-        <v>679</v>
+        <v>735</v>
       </c>
       <c r="P42" s="85" t="s">
-        <v>697</v>
+        <v>650</v>
       </c>
       <c r="Q42" s="85" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="R42" s="85"/>
       <c r="S42" s="96"/>
@@ -7213,41 +7201,41 @@
     <row r="44" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="56"/>
       <c r="D44" s="84" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="E44" s="84" t="s">
-        <v>698</v>
+        <v>651</v>
       </c>
       <c r="F44" s="84" t="s">
-        <v>700</v>
+        <v>653</v>
       </c>
       <c r="G44" s="84"/>
       <c r="H44" s="84" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I44" s="84" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J44" s="84"/>
       <c r="K44" s="84" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="L44" s="84"/>
       <c r="M44" s="84" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N44" s="84" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="O44" s="84" t="s">
-        <v>572</v>
+        <v>539</v>
       </c>
       <c r="P44" s="84"/>
       <c r="Q44" s="84" t="s">
-        <v>773</v>
+        <v>700</v>
       </c>
       <c r="R44" s="84" t="s">
-        <v>702</v>
+        <v>655</v>
       </c>
       <c r="S44" s="93"/>
       <c r="V44" s="60"/>
@@ -7308,41 +7296,41 @@
     <row r="46" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="58"/>
       <c r="D46" s="85" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="E46" s="85" t="s">
-        <v>699</v>
+        <v>652</v>
       </c>
       <c r="F46" s="85" t="s">
-        <v>701</v>
+        <v>654</v>
       </c>
       <c r="G46" s="85"/>
       <c r="H46" s="85" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="I46" s="85" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="J46" s="85"/>
       <c r="K46" s="85" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="L46" s="85"/>
       <c r="M46" s="85" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="N46" s="85" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="O46" s="85" t="s">
-        <v>573</v>
+        <v>540</v>
       </c>
       <c r="P46" s="85"/>
       <c r="Q46" s="85" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="R46" s="85" t="s">
-        <v>703</v>
+        <v>656</v>
       </c>
       <c r="S46" s="96"/>
       <c r="V46" s="60"/>
@@ -7370,42 +7358,42 @@
     <row r="48" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="56"/>
       <c r="D48" s="84" t="s">
-        <v>704</v>
+        <v>657</v>
       </c>
       <c r="E48" s="84" t="s">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="F48" s="84"/>
       <c r="G48" s="84" t="s">
         <v>394</v>
       </c>
       <c r="H48" s="84" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="I48" s="84" t="s">
-        <v>480</v>
+        <v>740</v>
       </c>
       <c r="J48" s="84" t="s">
-        <v>568</v>
+        <v>742</v>
       </c>
       <c r="K48" s="84"/>
       <c r="L48" s="84" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M48" s="84" t="s">
-        <v>644</v>
+        <v>713</v>
       </c>
       <c r="N48" s="84" t="s">
-        <v>774</v>
+        <v>701</v>
       </c>
       <c r="O48" s="84" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="P48" s="84" t="s">
-        <v>602</v>
+        <v>744</v>
       </c>
       <c r="Q48" s="84" t="s">
-        <v>484</v>
+        <v>746</v>
       </c>
       <c r="R48" s="84"/>
       <c r="S48" s="93"/>
@@ -7446,7 +7434,7 @@
       <c r="M49" s="80" t="s">
         <v>189</v>
       </c>
-      <c r="N49" s="106" t="s">
+      <c r="N49" s="100" t="s">
         <v>274</v>
       </c>
       <c r="O49" s="80" t="s">
@@ -7467,42 +7455,42 @@
     <row r="50" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="58"/>
       <c r="D50" s="85" t="s">
-        <v>705</v>
+        <v>658</v>
       </c>
       <c r="E50" s="85" t="s">
-        <v>636</v>
+        <v>607</v>
       </c>
       <c r="F50" s="85"/>
       <c r="G50" s="85" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H50" s="85" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I50" s="85" t="s">
-        <v>481</v>
+        <v>741</v>
       </c>
       <c r="J50" s="85" t="s">
-        <v>569</v>
+        <v>743</v>
       </c>
       <c r="K50" s="85"/>
       <c r="L50" s="85" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M50" s="85" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="N50" s="85" t="s">
-        <v>775</v>
+        <v>702</v>
       </c>
       <c r="O50" s="85" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="P50" s="85" t="s">
-        <v>603</v>
+        <v>745</v>
       </c>
       <c r="Q50" s="85" t="s">
-        <v>485</v>
+        <v>747</v>
       </c>
       <c r="R50" s="85"/>
       <c r="S50" s="96"/>
@@ -7531,42 +7519,42 @@
     <row r="52" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="56"/>
       <c r="D52" s="84" t="s">
-        <v>706</v>
+        <v>659</v>
       </c>
       <c r="E52" s="84" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
       <c r="F52" s="84" t="s">
-        <v>776</v>
+        <v>750</v>
       </c>
       <c r="G52" s="84" t="s">
-        <v>604</v>
+        <v>752</v>
       </c>
       <c r="H52" s="84"/>
       <c r="I52" s="84" t="s">
-        <v>710</v>
+        <v>661</v>
       </c>
       <c r="J52" s="84" t="s">
-        <v>712</v>
+        <v>754</v>
       </c>
       <c r="K52" s="84" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="L52" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="M52" s="84"/>
       <c r="N52" s="84" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="O52" s="84" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="P52" s="84" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="Q52" s="84" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="R52" s="84"/>
       <c r="S52" s="93"/>
@@ -7628,42 +7616,42 @@
     <row r="54" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="58"/>
       <c r="D54" s="85" t="s">
-        <v>707</v>
+        <v>660</v>
       </c>
       <c r="E54" s="85" t="s">
-        <v>709</v>
+        <v>749</v>
       </c>
       <c r="F54" s="85" t="s">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="G54" s="85" t="s">
-        <v>605</v>
+        <v>753</v>
       </c>
       <c r="H54" s="85"/>
       <c r="I54" s="85" t="s">
-        <v>711</v>
+        <v>662</v>
       </c>
       <c r="J54" s="85" t="s">
-        <v>713</v>
+        <v>755</v>
       </c>
       <c r="K54" s="85" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="L54" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="M54" s="85"/>
       <c r="N54" s="85" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="O54" s="85" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="P54" s="85" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="Q54" s="85" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="R54" s="85"/>
       <c r="S54" s="96"/>
@@ -7692,43 +7680,43 @@
     <row r="56" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="56"/>
       <c r="D56" s="84" t="s">
-        <v>714</v>
+        <v>663</v>
       </c>
       <c r="E56" s="84" t="s">
-        <v>716</v>
+        <v>756</v>
       </c>
       <c r="F56" s="84" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G56" s="84" t="s">
-        <v>718</v>
+        <v>665</v>
       </c>
       <c r="H56" s="84" t="s">
-        <v>720</v>
+        <v>758</v>
       </c>
       <c r="I56" s="84"/>
       <c r="J56" s="84" t="s">
-        <v>722</v>
+        <v>760</v>
       </c>
       <c r="K56" s="84" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="L56" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="M56" s="84"/>
       <c r="N56" s="84" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="O56" s="84" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="P56" s="84" t="s">
-        <v>637</v>
+        <v>608</v>
       </c>
       <c r="Q56" s="84"/>
       <c r="R56" s="84" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="S56" s="93"/>
       <c r="V56" s="60"/>
@@ -7741,7 +7729,7 @@
       <c r="D57" s="80" t="s">
         <v>383</v>
       </c>
-      <c r="E57" s="106" t="s">
+      <c r="E57" s="100" t="s">
         <v>384</v>
       </c>
       <c r="F57" s="80" t="s">
@@ -7751,7 +7739,7 @@
         <v>385</v>
       </c>
       <c r="H57" s="81" t="s">
-        <v>796</v>
+        <v>712</v>
       </c>
       <c r="I57" s="80" t="s">
         <v>228</v>
@@ -7789,43 +7777,43 @@
     <row r="58" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="58"/>
       <c r="D58" s="85" t="s">
-        <v>715</v>
+        <v>664</v>
       </c>
       <c r="E58" s="85" t="s">
-        <v>717</v>
+        <v>757</v>
       </c>
       <c r="F58" s="85" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G58" s="85" t="s">
-        <v>719</v>
+        <v>666</v>
       </c>
       <c r="H58" s="85" t="s">
-        <v>721</v>
+        <v>759</v>
       </c>
       <c r="I58" s="85"/>
       <c r="J58" s="85" t="s">
-        <v>723</v>
+        <v>761</v>
       </c>
       <c r="K58" s="85" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="L58" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="M58" s="85"/>
       <c r="N58" s="85" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="O58" s="85" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="P58" s="85" t="s">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="Q58" s="85"/>
       <c r="R58" s="85" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="S58" s="96"/>
       <c r="V58" s="60"/>
@@ -7853,43 +7841,43 @@
     <row r="60" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="56"/>
       <c r="D60" s="84" t="s">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="E60" s="84" t="s">
-        <v>682</v>
+        <v>736</v>
       </c>
       <c r="F60" s="84" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G60" s="84"/>
       <c r="H60" s="84" t="s">
-        <v>726</v>
+        <v>669</v>
       </c>
       <c r="I60" s="84" t="s">
-        <v>728</v>
+        <v>671</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K60" s="84"/>
       <c r="L60" s="84" t="s">
-        <v>450</v>
+        <v>647</v>
       </c>
       <c r="M60" s="84" t="s">
-        <v>608</v>
+        <v>762</v>
       </c>
       <c r="N60" s="84" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="O60" s="84" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="P60" s="84"/>
       <c r="Q60" s="84" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="R60" s="84" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="S60" s="93"/>
       <c r="V60" s="60"/>
@@ -7899,7 +7887,7 @@
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="106" t="s">
+      <c r="D61" s="100" t="s">
         <v>289</v>
       </c>
       <c r="E61" s="80" t="s">
@@ -7950,43 +7938,43 @@
     <row r="62" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="58"/>
       <c r="D62" s="85" t="s">
-        <v>725</v>
+        <v>668</v>
       </c>
       <c r="E62" s="85" t="s">
-        <v>683</v>
+        <v>737</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="G62" s="85"/>
       <c r="H62" s="85" t="s">
-        <v>727</v>
+        <v>670</v>
       </c>
       <c r="I62" s="85" t="s">
-        <v>729</v>
+        <v>672</v>
       </c>
       <c r="J62" s="85" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K62" s="85"/>
       <c r="L62" s="85" t="s">
-        <v>451</v>
+        <v>648</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>609</v>
+        <v>763</v>
       </c>
       <c r="N62" s="85" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="O62" s="85" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="P62" s="85"/>
       <c r="Q62" s="85" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="R62" s="85" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="S62" s="96"/>
       <c r="V62" s="60"/>
@@ -8015,40 +8003,40 @@
       <c r="B64" s="56"/>
       <c r="D64" s="84"/>
       <c r="E64" s="84" t="s">
-        <v>610</v>
+        <v>764</v>
       </c>
       <c r="F64" s="84" t="s">
         <v>394</v>
       </c>
       <c r="G64" s="84"/>
       <c r="H64" s="84" t="s">
-        <v>484</v>
+        <v>746</v>
       </c>
       <c r="I64" s="84" t="s">
-        <v>730</v>
+        <v>442</v>
       </c>
       <c r="J64" s="84"/>
       <c r="K64" s="84" t="s">
-        <v>778</v>
+        <v>703</v>
       </c>
       <c r="L64" s="84" t="s">
-        <v>644</v>
+        <v>713</v>
       </c>
       <c r="M64" s="84" t="s">
-        <v>568</v>
+        <v>742</v>
       </c>
       <c r="N64" s="84" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="O64" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="P64" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="Q64" s="84"/>
       <c r="R64" s="84" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="S64" s="93"/>
       <c r="V64" s="60"/>
@@ -8110,40 +8098,40 @@
       <c r="B66" s="58"/>
       <c r="D66" s="85"/>
       <c r="E66" s="85" t="s">
-        <v>611</v>
+        <v>765</v>
       </c>
       <c r="F66" s="85" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G66" s="85"/>
       <c r="H66" s="85" t="s">
-        <v>485</v>
+        <v>747</v>
       </c>
       <c r="I66" s="85" t="s">
-        <v>731</v>
+        <v>443</v>
       </c>
       <c r="J66" s="85"/>
       <c r="K66" s="85" t="s">
-        <v>779</v>
+        <v>704</v>
       </c>
       <c r="L66" s="85" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="M66" s="85" t="s">
-        <v>569</v>
+        <v>743</v>
       </c>
       <c r="N66" s="85" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="O66" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="P66" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="Q66" s="85"/>
       <c r="R66" s="85" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="S66" s="96"/>
       <c r="V66" s="60"/>
@@ -8171,40 +8159,40 @@
     <row r="68" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="56"/>
       <c r="D68" s="84" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E68" s="84" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="F68" s="84" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="G68" s="84"/>
       <c r="H68" s="84" t="s">
-        <v>718</v>
+        <v>665</v>
       </c>
       <c r="I68" s="84" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="J68" s="84"/>
       <c r="K68" s="84"/>
       <c r="L68" s="84" t="s">
-        <v>658</v>
+        <v>724</v>
       </c>
       <c r="M68" s="84" t="s">
+        <v>499</v>
+      </c>
+      <c r="N68" s="84" t="s">
+        <v>501</v>
+      </c>
+      <c r="O68" s="84" t="s">
+        <v>503</v>
+      </c>
+      <c r="P68" s="84" t="s">
         <v>505</v>
       </c>
-      <c r="N68" s="84" t="s">
+      <c r="Q68" s="84" t="s">
         <v>507</v>
-      </c>
-      <c r="O68" s="84" t="s">
-        <v>509</v>
-      </c>
-      <c r="P68" s="84" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q68" s="84" t="s">
-        <v>513</v>
       </c>
       <c r="R68" s="84"/>
       <c r="S68" s="93"/>
@@ -8266,40 +8254,40 @@
     <row r="70" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="58"/>
       <c r="D70" s="85" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E70" s="85" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="F70" s="85" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="G70" s="85"/>
       <c r="H70" s="85" t="s">
-        <v>719</v>
+        <v>666</v>
       </c>
       <c r="I70" s="85" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="J70" s="85"/>
       <c r="K70" s="85"/>
       <c r="L70" s="85" t="s">
-        <v>659</v>
+        <v>725</v>
       </c>
       <c r="M70" s="85" t="s">
+        <v>500</v>
+      </c>
+      <c r="N70" s="85" t="s">
+        <v>502</v>
+      </c>
+      <c r="O70" s="85" t="s">
+        <v>504</v>
+      </c>
+      <c r="P70" s="85" t="s">
         <v>506</v>
       </c>
-      <c r="N70" s="85" t="s">
+      <c r="Q70" s="85" t="s">
         <v>508</v>
-      </c>
-      <c r="O70" s="85" t="s">
-        <v>510</v>
-      </c>
-      <c r="P70" s="85" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q70" s="85" t="s">
-        <v>514</v>
       </c>
       <c r="R70" s="85"/>
       <c r="S70" s="96"/>
@@ -8328,44 +8316,44 @@
     <row r="72" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="56"/>
       <c r="D72" s="84" t="s">
-        <v>732</v>
+        <v>766</v>
       </c>
       <c r="E72" s="84" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="F72" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="G72" s="84" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="H72" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="I72" s="84" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J72" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="K72" s="84" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="L72" s="84" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="M72" s="84"/>
       <c r="N72" s="84" t="s">
-        <v>435</v>
+        <v>770</v>
       </c>
       <c r="O72" s="84" t="s">
-        <v>664</v>
+        <v>728</v>
       </c>
       <c r="P72" s="84" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="Q72" s="84" t="s">
-        <v>425</v>
+        <v>774</v>
       </c>
       <c r="R72" s="84"/>
       <c r="S72" s="93"/>
@@ -8385,7 +8373,7 @@
       <c r="F73" s="80" t="s">
         <v>308</v>
       </c>
-      <c r="G73" s="81" t="s">
+      <c r="G73" s="80" t="s">
         <v>309</v>
       </c>
       <c r="H73" s="80" t="s">
@@ -8406,7 +8394,7 @@
       <c r="M73" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="N73" s="106" t="s">
+      <c r="N73" s="100" t="s">
         <v>312</v>
       </c>
       <c r="O73" s="80" t="s">
@@ -8427,44 +8415,44 @@
     <row r="74" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="58"/>
       <c r="D74" s="85" t="s">
-        <v>733</v>
+        <v>767</v>
       </c>
       <c r="E74" s="85" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="F74" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="G74" s="85" t="s">
-        <v>782</v>
+        <v>705</v>
       </c>
       <c r="H74" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="I74" s="85" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="J74" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="K74" s="85" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="L74" s="85" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="M74" s="85"/>
       <c r="N74" s="85" t="s">
-        <v>436</v>
+        <v>771</v>
       </c>
       <c r="O74" s="85" t="s">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="P74" s="85" t="s">
-        <v>632</v>
+        <v>773</v>
       </c>
       <c r="Q74" s="85" t="s">
-        <v>426</v>
+        <v>775</v>
       </c>
       <c r="R74" s="85"/>
       <c r="S74" s="96"/>
@@ -8493,40 +8481,40 @@
     <row r="76" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="56"/>
       <c r="D76" s="84" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E76" s="84" t="s">
-        <v>784</v>
+        <v>533</v>
       </c>
       <c r="F76" s="84" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G76" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="H76" s="84" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="I76" s="84" t="s">
-        <v>612</v>
+        <v>588</v>
       </c>
       <c r="J76" s="84"/>
       <c r="K76" s="84"/>
       <c r="L76" s="84" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="M76" s="84"/>
       <c r="N76" s="84" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="O76" s="84" t="s">
-        <v>736</v>
+        <v>675</v>
       </c>
       <c r="P76" s="84" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="Q76" s="84" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="R76" s="84"/>
       <c r="S76" s="93"/>
@@ -8588,40 +8576,40 @@
     <row r="78" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="58"/>
       <c r="D78" s="85" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E78" s="85" t="s">
-        <v>785</v>
+        <v>534</v>
       </c>
       <c r="F78" s="85" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="G78" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="H78" s="85" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="I78" s="85" t="s">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="J78" s="85"/>
       <c r="K78" s="85"/>
       <c r="L78" s="85" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="M78" s="85"/>
       <c r="N78" s="85" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="O78" s="85" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="P78" s="85" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="Q78" s="85" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="R78" s="85"/>
       <c r="S78" s="96"/>
@@ -8651,29 +8639,29 @@
       <c r="B80" s="56"/>
       <c r="D80" s="84"/>
       <c r="E80" s="84" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F80" s="84" t="s">
-        <v>435</v>
+        <v>770</v>
       </c>
       <c r="G80" s="84" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="H80" s="84" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="I80" s="84" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="J80" s="84"/>
       <c r="K80" s="84" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="L80" s="84" t="s">
-        <v>737</v>
+        <v>776</v>
       </c>
       <c r="M80" s="84" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="N80" s="84"/>
       <c r="O80" s="84" t="s">
@@ -8681,10 +8669,10 @@
       </c>
       <c r="P80" s="84"/>
       <c r="Q80" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="R80" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="S80" s="93"/>
       <c r="V80" s="60"/>
@@ -8746,29 +8734,29 @@
       <c r="B82" s="58"/>
       <c r="D82" s="85"/>
       <c r="E82" s="85" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F82" s="85" t="s">
-        <v>436</v>
+        <v>771</v>
       </c>
       <c r="G82" s="85" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="H82" s="85" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="I82" s="85" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="J82" s="85"/>
       <c r="K82" s="85" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="L82" s="85" t="s">
-        <v>738</v>
+        <v>777</v>
       </c>
       <c r="M82" s="85" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="N82" s="85"/>
       <c r="O82" s="85" t="s">
@@ -8776,10 +8764,10 @@
       </c>
       <c r="P82" s="85"/>
       <c r="Q82" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="R82" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="S82" s="96"/>
       <c r="V82" s="60"/>
@@ -8807,45 +8795,45 @@
     <row r="84" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="56"/>
       <c r="D84" s="84" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E84" s="84" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F84" s="84" t="s">
-        <v>766</v>
+        <v>695</v>
       </c>
       <c r="G84" s="84" t="s">
-        <v>726</v>
+        <v>669</v>
       </c>
       <c r="H84" s="84" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="I84" s="84" t="s">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="J84" s="84" t="s">
-        <v>568</v>
+        <v>742</v>
       </c>
       <c r="K84" s="84"/>
       <c r="L84" s="84" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="M84" s="84" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="N84" s="84" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="O84" s="84"/>
       <c r="P84" s="84" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="Q84" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="R84" s="84" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="S84" s="93"/>
       <c r="V84" s="60"/>
@@ -8906,45 +8894,45 @@
     <row r="86" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="58"/>
       <c r="D86" s="85" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E86" s="85" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F86" s="85" t="s">
-        <v>767</v>
+        <v>696</v>
       </c>
       <c r="G86" s="85" t="s">
-        <v>727</v>
+        <v>670</v>
       </c>
       <c r="H86" s="85" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="I86" s="85" t="s">
-        <v>725</v>
+        <v>668</v>
       </c>
       <c r="J86" s="85" t="s">
-        <v>569</v>
+        <v>743</v>
       </c>
       <c r="K86" s="85"/>
       <c r="L86" s="85" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M86" s="85" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="N86" s="85" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="O86" s="85"/>
       <c r="P86" s="85" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="Q86" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="R86" s="85" t="s">
-        <v>619</v>
+        <v>595</v>
       </c>
       <c r="S86" s="96"/>
       <c r="V86" s="60"/>
@@ -8972,42 +8960,42 @@
     <row r="88" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B88" s="56"/>
       <c r="D88" s="84" t="s">
-        <v>664</v>
+        <v>728</v>
       </c>
       <c r="E88" s="84" t="s">
-        <v>786</v>
+        <v>425</v>
       </c>
       <c r="F88" s="84" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G88" s="84" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H88" s="84" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I88" s="84"/>
       <c r="J88" s="84" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="K88" s="84" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="L88" s="84" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="M88" s="84" t="s">
-        <v>730</v>
+        <v>442</v>
       </c>
       <c r="N88" s="84"/>
       <c r="O88" s="84" t="s">
-        <v>739</v>
+        <v>676</v>
       </c>
       <c r="P88" s="84" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="Q88" s="84" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="R88" s="84"/>
       <c r="S88" s="93"/>
@@ -9069,42 +9057,42 @@
     <row r="90" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="58"/>
       <c r="D90" s="85" t="s">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="E90" s="85" t="s">
-        <v>787</v>
+        <v>426</v>
       </c>
       <c r="F90" s="85" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G90" s="85" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H90" s="85" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I90" s="85"/>
       <c r="J90" s="85" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="K90" s="85" t="s">
-        <v>632</v>
+        <v>773</v>
       </c>
       <c r="L90" s="85" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M90" s="85" t="s">
-        <v>731</v>
+        <v>443</v>
       </c>
       <c r="N90" s="85"/>
       <c r="O90" s="85" t="s">
-        <v>740</v>
+        <v>677</v>
       </c>
       <c r="P90" s="85" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="Q90" s="85" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="R90" s="85"/>
       <c r="S90" s="96"/>
@@ -9133,43 +9121,43 @@
     <row r="92" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="56"/>
       <c r="D92" s="84" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E92" s="84" t="s">
-        <v>726</v>
+        <v>778</v>
       </c>
       <c r="F92" s="84"/>
       <c r="G92" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="H92" s="84" t="s">
-        <v>644</v>
+        <v>713</v>
       </c>
       <c r="I92" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="J92" s="84" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
       <c r="K92" s="84" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="L92" s="84"/>
       <c r="M92" s="84"/>
       <c r="N92" s="84" t="s">
-        <v>435</v>
+        <v>770</v>
       </c>
       <c r="O92" s="84" t="s">
-        <v>545</v>
+        <v>708</v>
       </c>
       <c r="P92" s="84" t="s">
-        <v>766</v>
+        <v>695</v>
       </c>
       <c r="Q92" s="84" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="R92" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="S92" s="93"/>
       <c r="V92" s="60"/>
@@ -9230,43 +9218,43 @@
     <row r="94" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="58"/>
       <c r="D94" s="85" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E94" s="85" t="s">
-        <v>727</v>
+        <v>779</v>
       </c>
       <c r="F94" s="85"/>
       <c r="G94" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="H94" s="85" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="I94" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="J94" s="85" t="s">
-        <v>742</v>
+        <v>781</v>
       </c>
       <c r="K94" s="85" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="L94" s="85"/>
       <c r="M94" s="85"/>
       <c r="N94" s="85" t="s">
-        <v>436</v>
+        <v>771</v>
       </c>
       <c r="O94" s="85" t="s">
-        <v>546</v>
+        <v>709</v>
       </c>
       <c r="P94" s="85" t="s">
-        <v>767</v>
+        <v>696</v>
       </c>
       <c r="Q94" s="85" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="R94" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="S94" s="96"/>
       <c r="V94" s="60"/>
@@ -9294,10 +9282,10 @@
     <row r="96" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="56"/>
       <c r="D96" s="84" t="s">
-        <v>743</v>
+        <v>678</v>
       </c>
       <c r="E96" s="84" t="s">
-        <v>788</v>
+        <v>706</v>
       </c>
       <c r="F96" s="84"/>
       <c r="G96" s="84"/>
@@ -9349,10 +9337,10 @@
     <row r="98" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="58"/>
       <c r="D98" s="85" t="s">
-        <v>744</v>
+        <v>679</v>
       </c>
       <c r="E98" s="85" t="s">
-        <v>789</v>
+        <v>707</v>
       </c>
       <c r="F98" s="85"/>
       <c r="G98" s="85"/>
@@ -9478,37 +9466,37 @@
       <c r="D104" s="84"/>
       <c r="E104" s="84"/>
       <c r="F104" s="84" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="G104" s="84" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="H104" s="84"/>
       <c r="I104" s="84" t="s">
-        <v>642</v>
+        <v>613</v>
       </c>
       <c r="J104" s="84" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K104" s="84" t="s">
-        <v>680</v>
+        <v>637</v>
       </c>
       <c r="L104" s="84"/>
       <c r="M104" s="84" t="s">
-        <v>450</v>
+        <v>647</v>
       </c>
       <c r="N104" s="84" t="s">
-        <v>620</v>
+        <v>596</v>
       </c>
       <c r="O104" s="84" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P104" s="84" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q104" s="84"/>
       <c r="R104" s="84" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="S104" s="93"/>
       <c r="V104" s="60"/>
@@ -9571,37 +9559,37 @@
       <c r="D106" s="85"/>
       <c r="E106" s="85"/>
       <c r="F106" s="85" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="G106" s="85" t="s">
-        <v>632</v>
+        <v>773</v>
       </c>
       <c r="H106" s="85"/>
       <c r="I106" s="85" t="s">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="J106" s="85" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K106" s="85" t="s">
-        <v>681</v>
+        <v>638</v>
       </c>
       <c r="L106" s="85"/>
       <c r="M106" s="85" t="s">
-        <v>451</v>
+        <v>648</v>
       </c>
       <c r="N106" s="85" t="s">
-        <v>621</v>
+        <v>597</v>
       </c>
       <c r="O106" s="85" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="P106" s="85" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q106" s="85"/>
       <c r="R106" s="85" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="S106" s="96"/>
       <c r="V106" s="60"/>
@@ -9629,43 +9617,43 @@
     <row r="108" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B108" s="56"/>
       <c r="D108" s="84" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E108" s="84" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="F108" s="84" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G108" s="84"/>
       <c r="H108" s="84" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="I108" s="84" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="J108" s="84" t="s">
-        <v>622</v>
+        <v>784</v>
       </c>
       <c r="K108" s="84"/>
       <c r="L108" s="84" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="M108" s="84" t="s">
         <v>415</v>
       </c>
       <c r="N108" s="84" t="s">
-        <v>746</v>
+        <v>786</v>
       </c>
       <c r="O108" s="84"/>
       <c r="P108" s="84" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="Q108" s="84" t="s">
-        <v>712</v>
+        <v>754</v>
       </c>
       <c r="R108" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="S108" s="93"/>
       <c r="V108" s="60"/>
@@ -9726,43 +9714,43 @@
     <row r="110" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="58"/>
       <c r="D110" s="85" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="E110" s="85" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="F110" s="85" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G110" s="85"/>
       <c r="H110" s="85" t="s">
-        <v>745</v>
+        <v>680</v>
       </c>
       <c r="I110" s="85" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="J110" s="85" t="s">
-        <v>623</v>
+        <v>785</v>
       </c>
       <c r="K110" s="85"/>
       <c r="L110" s="85" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="M110" s="85" t="s">
         <v>416</v>
       </c>
       <c r="N110" s="85" t="s">
-        <v>747</v>
+        <v>787</v>
       </c>
       <c r="O110" s="85"/>
       <c r="P110" s="85" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="Q110" s="85" t="s">
-        <v>713</v>
+        <v>755</v>
       </c>
       <c r="R110" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="S110" s="96"/>
       <c r="V110" s="60"/>
@@ -9794,38 +9782,38 @@
         <v>415</v>
       </c>
       <c r="F112" s="84" t="s">
-        <v>746</v>
+        <v>786</v>
       </c>
       <c r="G112" s="84" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="H112" s="84" t="s">
-        <v>748</v>
+        <v>474</v>
       </c>
       <c r="I112" s="84" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="J112" s="84" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="K112" s="84" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L112" s="84" t="s">
-        <v>774</v>
+        <v>701</v>
       </c>
       <c r="M112" s="84"/>
       <c r="N112" s="84" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="O112" s="84" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P112" s="84" t="s">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="Q112" s="84" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="R112" s="84"/>
       <c r="S112" s="93"/>
@@ -9891,38 +9879,38 @@
         <v>416</v>
       </c>
       <c r="F114" s="85" t="s">
-        <v>747</v>
+        <v>787</v>
       </c>
       <c r="G114" s="85" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="H114" s="85" t="s">
-        <v>749</v>
+        <v>475</v>
       </c>
       <c r="I114" s="85" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="J114" s="85" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="K114" s="85" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L114" s="85" t="s">
-        <v>775</v>
+        <v>702</v>
       </c>
       <c r="M114" s="85"/>
       <c r="N114" s="85" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="O114" s="85" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="P114" s="85" t="s">
-        <v>725</v>
+        <v>668</v>
       </c>
       <c r="Q114" s="85" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="R114" s="85"/>
       <c r="S114" s="96"/>
@@ -9951,22 +9939,22 @@
     <row r="116" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B116" s="56"/>
       <c r="D116" s="84" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E116" s="84" t="s">
-        <v>750</v>
+        <v>681</v>
       </c>
       <c r="F116" s="84" t="s">
-        <v>435</v>
+        <v>770</v>
       </c>
       <c r="G116" s="84" t="s">
-        <v>664</v>
+        <v>728</v>
       </c>
       <c r="H116" s="84" t="s">
-        <v>642</v>
+        <v>613</v>
       </c>
       <c r="I116" s="84" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J116" s="84"/>
       <c r="K116" s="84"/>
@@ -10020,22 +10008,22 @@
     <row r="118" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="58"/>
       <c r="D118" s="85" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E118" s="85" t="s">
-        <v>751</v>
+        <v>682</v>
       </c>
       <c r="F118" s="85" t="s">
-        <v>436</v>
+        <v>771</v>
       </c>
       <c r="G118" s="85" t="s">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="H118" s="85" t="s">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="I118" s="85" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J118" s="85"/>
       <c r="K118" s="85"/>
@@ -10157,39 +10145,39 @@
       <c r="D124" s="84"/>
       <c r="E124" s="84"/>
       <c r="F124" s="84" t="s">
-        <v>706</v>
+        <v>659</v>
       </c>
       <c r="G124" s="84" t="s">
-        <v>794</v>
+        <v>710</v>
       </c>
       <c r="H124" s="84" t="s">
-        <v>752</v>
+        <v>683</v>
       </c>
       <c r="I124" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="J124" s="84" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="K124" s="84"/>
       <c r="L124" s="84" t="s">
-        <v>704</v>
+        <v>657</v>
       </c>
       <c r="M124" s="84" t="s">
-        <v>556</v>
+        <v>790</v>
       </c>
       <c r="N124" s="84" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="O124" s="84" t="s">
-        <v>788</v>
+        <v>706</v>
       </c>
       <c r="P124" s="84"/>
       <c r="Q124" s="84" t="s">
-        <v>568</v>
+        <v>742</v>
       </c>
       <c r="R124" s="84" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="S124" s="93"/>
       <c r="V124" s="60"/>
@@ -10252,39 +10240,39 @@
       <c r="D126" s="85"/>
       <c r="E126" s="85"/>
       <c r="F126" s="85" t="s">
-        <v>707</v>
+        <v>660</v>
       </c>
       <c r="G126" s="85" t="s">
-        <v>795</v>
+        <v>711</v>
       </c>
       <c r="H126" s="85" t="s">
-        <v>753</v>
+        <v>684</v>
       </c>
       <c r="I126" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="J126" s="85" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="K126" s="85"/>
       <c r="L126" s="85" t="s">
-        <v>705</v>
+        <v>658</v>
       </c>
       <c r="M126" s="85" t="s">
-        <v>557</v>
+        <v>791</v>
       </c>
       <c r="N126" s="85" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="O126" s="85" t="s">
-        <v>789</v>
+        <v>707</v>
       </c>
       <c r="P126" s="85"/>
       <c r="Q126" s="85" t="s">
-        <v>569</v>
+        <v>743</v>
       </c>
       <c r="R126" s="85" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="S126" s="96"/>
       <c r="V126" s="60"/>
@@ -10313,40 +10301,40 @@
       <c r="B128" s="56"/>
       <c r="D128" s="84"/>
       <c r="E128" s="84" t="s">
-        <v>754</v>
+        <v>685</v>
       </c>
       <c r="F128" s="84" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G128" s="84" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="H128" s="84" t="s">
-        <v>774</v>
+        <v>701</v>
       </c>
       <c r="I128" s="84"/>
       <c r="J128" s="84" t="s">
-        <v>756</v>
+        <v>687</v>
       </c>
       <c r="K128" s="84" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="L128" s="84"/>
       <c r="M128" s="84" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="N128" s="84" t="s">
-        <v>639</v>
+        <v>610</v>
       </c>
       <c r="O128" s="84" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="P128" s="84"/>
       <c r="Q128" s="84" t="s">
-        <v>758</v>
+        <v>792</v>
       </c>
       <c r="R128" s="84" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="S128" s="93"/>
       <c r="V128" s="60"/>
@@ -10359,13 +10347,13 @@
       <c r="D129" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="E129" s="106" t="s">
-        <v>629</v>
+      <c r="E129" s="100" t="s">
+        <v>603</v>
       </c>
       <c r="F129" s="80" t="s">
         <v>256</v>
       </c>
-      <c r="G129" s="81" t="s">
+      <c r="G129" s="80" t="s">
         <v>358</v>
       </c>
       <c r="H129" s="80" t="s">
@@ -10408,40 +10396,40 @@
       <c r="B130" s="58"/>
       <c r="D130" s="85"/>
       <c r="E130" s="85" t="s">
-        <v>755</v>
+        <v>686</v>
       </c>
       <c r="F130" s="85" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G130" s="85" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="H130" s="85" t="s">
-        <v>775</v>
+        <v>702</v>
       </c>
       <c r="I130" s="85"/>
       <c r="J130" s="85" t="s">
-        <v>757</v>
+        <v>688</v>
       </c>
       <c r="K130" s="85" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="L130" s="85"/>
       <c r="M130" s="85" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="N130" s="85" t="s">
-        <v>640</v>
+        <v>611</v>
       </c>
       <c r="O130" s="85" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="P130" s="85"/>
       <c r="Q130" s="85" t="s">
-        <v>759</v>
+        <v>793</v>
       </c>
       <c r="R130" s="85" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="S130" s="96"/>
       <c r="V130" s="60"/>
@@ -10469,16 +10457,16 @@
     <row r="132" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B132" s="56"/>
       <c r="D132" s="84" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E132" s="84" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="F132" s="84" t="s">
-        <v>760</v>
+        <v>689</v>
       </c>
       <c r="G132" s="84" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="H132" s="84"/>
       <c r="I132" s="84"/>
@@ -10530,16 +10518,16 @@
     <row r="134" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="58"/>
       <c r="D134" s="85" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E134" s="85" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="F134" s="85" t="s">
-        <v>761</v>
+        <v>690</v>
       </c>
       <c r="G134" s="85" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="H134" s="85"/>
       <c r="I134" s="85"/>
@@ -12734,27 +12722,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:R7">
-    <cfRule type="expression" dxfId="45" priority="37">
+    <cfRule type="expression" dxfId="45" priority="38">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="37">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="38">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
-    <cfRule type="expression" dxfId="43" priority="35">
+    <cfRule type="expression" dxfId="43" priority="36">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="35">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="36">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="41" priority="33">
+    <cfRule type="expression" dxfId="41" priority="34">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="33">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="34">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
@@ -12766,27 +12754,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23:R23 D39:R39 D87:R87 D91:R91 D95:R95 D99:R99 D103:R103 D111:R111 D115:R115 D119:R119 D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="37" priority="45">
+    <cfRule type="expression" dxfId="37" priority="46">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="45">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="46">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="35" priority="29">
+    <cfRule type="expression" dxfId="35" priority="30">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="29">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="30">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
-    <cfRule type="expression" dxfId="33" priority="27">
+    <cfRule type="expression" dxfId="33" priority="28">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="27">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="28">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
@@ -12798,19 +12786,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="29" priority="23">
+    <cfRule type="expression" dxfId="29" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
-    <cfRule type="expression" dxfId="27" priority="21">
+    <cfRule type="expression" dxfId="27" priority="22">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="21">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="22">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
@@ -12822,19 +12810,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:R55">
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="23" priority="18">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="17">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:R59">
-    <cfRule type="expression" dxfId="21" priority="15">
+    <cfRule type="expression" dxfId="21" priority="16">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="15">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="16">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
@@ -12846,11 +12834,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
-    <cfRule type="expression" dxfId="17" priority="11">
+    <cfRule type="expression" dxfId="17" priority="12">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="11">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D71:R71">
@@ -12862,11 +12850,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="13" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
@@ -12886,11 +12874,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
@@ -12974,7 +12962,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="104" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -12992,7 +12980,7 @@
       <c r="G5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="103" t="s">
+      <c r="I5" s="104" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -13017,7 +13005,7 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B6" s="104"/>
+      <c r="B6" s="105"/>
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
@@ -13037,7 +13025,7 @@
         <f>$B5 &amp; G$4</f>
         <v>陰入</v>
       </c>
-      <c r="I6" s="104"/>
+      <c r="I6" s="105"/>
       <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
@@ -13059,7 +13047,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B7" s="104"/>
+      <c r="B7" s="105"/>
       <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
@@ -13075,7 +13063,7 @@
       <c r="G7" s="16">
         <v>30</v>
       </c>
-      <c r="I7" s="104"/>
+      <c r="I7" s="105"/>
       <c r="J7" s="15" t="s">
         <v>22</v>
       </c>
@@ -13097,7 +13085,7 @@
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B8" s="104"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
@@ -13113,7 +13101,7 @@
       <c r="G8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="104"/>
+      <c r="I8" s="105"/>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
@@ -13135,7 +13123,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B9" s="104"/>
+      <c r="B9" s="105"/>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
@@ -13151,7 +13139,7 @@
       <c r="G9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="104"/>
+      <c r="I9" s="105"/>
       <c r="J9" s="11" t="s">
         <v>33</v>
       </c>
@@ -13173,7 +13161,7 @@
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B10" s="105"/>
+      <c r="B10" s="106"/>
       <c r="C10" s="11" t="s">
         <v>38</v>
       </c>
@@ -13189,7 +13177,7 @@
       <c r="G10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="105"/>
+      <c r="I10" s="106"/>
       <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
@@ -13212,7 +13200,7 @@
       <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="104" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -13230,7 +13218,7 @@
       <c r="G11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="103" t="s">
+      <c r="I11" s="104" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -13254,7 +13242,7 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B12" s="104"/>
+      <c r="B12" s="105"/>
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
@@ -13274,7 +13262,7 @@
         <f>$B11 &amp; G$4</f>
         <v>陽入</v>
       </c>
-      <c r="I12" s="104"/>
+      <c r="I12" s="105"/>
       <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
@@ -13294,7 +13282,7 @@
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B13" s="104"/>
+      <c r="B13" s="105"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
@@ -13308,7 +13296,7 @@
       <c r="G13" s="16">
         <v>50</v>
       </c>
-      <c r="I13" s="104"/>
+      <c r="I13" s="105"/>
       <c r="J13" s="15" t="s">
         <v>22</v>
       </c>
@@ -13328,7 +13316,7 @@
       <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B14" s="104"/>
+      <c r="B14" s="105"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -13342,7 +13330,7 @@
       <c r="G14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="104"/>
+      <c r="I14" s="105"/>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
@@ -13362,7 +13350,7 @@
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B15" s="104"/>
+      <c r="B15" s="105"/>
       <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
@@ -13376,7 +13364,7 @@
       <c r="G15" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="104"/>
+      <c r="I15" s="105"/>
       <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
@@ -13396,7 +13384,7 @@
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B16" s="105"/>
+      <c r="B16" s="106"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
       </c>
@@ -13410,7 +13398,7 @@
       <c r="G16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="105"/>
+      <c r="I16" s="106"/>
       <c r="J16" s="11" t="s">
         <v>43</v>
       </c>

--- a/output5/【河洛話注音】桃花源記【文讀音】.xlsx
+++ b/output5/【河洛話注音】桃花源記【文讀音】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{679082E1-F881-4FC8-80FC-1AF497F08CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{565644C9-0D6C-449D-A507-3B034A2281CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="800">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1481,1865 +1481,1895 @@
     <t>遂</t>
   </si>
   <si>
+    <t>間</t>
+  </si>
+  <si>
+    <t>」</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>何</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>漢</t>
+  </si>
+  <si>
+    <t>魏</t>
+  </si>
+  <si>
+    <t>！</t>
+  </si>
+  <si>
+    <t>言</t>
+  </si>
+  <si>
+    <t>皆</t>
+  </si>
+  <si>
+    <t>惋</t>
+  </si>
+  <si>
+    <t>餘</t>
+  </si>
+  <si>
+    <t>延</t>
+  </si>
+  <si>
+    <t>至</t>
+  </si>
+  <si>
+    <t>停</t>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>辭</t>
+  </si>
+  <si>
+    <t>語</t>
+  </si>
+  <si>
+    <t>道</t>
+  </si>
+  <si>
+    <t>也</t>
+  </si>
+  <si>
+    <t>既</t>
+  </si>
+  <si>
+    <t>處</t>
+  </si>
+  <si>
+    <t>誌</t>
+  </si>
+  <si>
+    <t>及</t>
+  </si>
+  <si>
+    <t>郡</t>
+  </si>
+  <si>
+    <t>守</t>
+  </si>
+  <si>
+    <t>說</t>
+  </si>
+  <si>
+    <t>遣</t>
+  </si>
+  <si>
+    <t>隨</t>
+  </si>
+  <si>
+    <t>尋</t>
+  </si>
+  <si>
+    <t>迷</t>
+  </si>
+  <si>
+    <t>南</t>
+  </si>
+  <si>
+    <t>陽</t>
+  </si>
+  <si>
+    <t>劉</t>
+  </si>
+  <si>
+    <t>驥</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>規</t>
+  </si>
+  <si>
+    <t>未</t>
+  </si>
+  <si>
+    <t>果</t>
+  </si>
+  <si>
+    <t>病</t>
+  </si>
+  <si>
+    <t>終</t>
+  </si>
+  <si>
+    <t>後</t>
+  </si>
+  <si>
+    <t>津</t>
+  </si>
+  <si>
+    <t>者</t>
+  </si>
+  <si>
+    <t>鮮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zap8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>種</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>著</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>髫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>並</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>見</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>問</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>還</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>殺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ke1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>避</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>歎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>詣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>便</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thai3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㄞ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆦ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giap8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄧㄚㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khe1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆦ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hut4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hua1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄚˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄚㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pian7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>it4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>san1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆲˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thoo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㆦˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㆲ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bi2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ka1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄚˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khian2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄧㄢˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄞˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiau5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㄠˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nai2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄋㄞˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ham5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㆰˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄣ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>un5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>se3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luan7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ip4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zuat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄨㄚㆵ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>king2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄥˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄜˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>han3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄞˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jit8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆵ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄨㄣ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ge7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㆤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kui1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄨㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆬˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bun7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨㄣ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>than3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ling5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lim5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆬˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gan7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄢ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>song1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆦㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄞ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄚㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kim1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆬˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆦㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>語音類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文讀音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花源記【文讀音】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>king1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄥˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ping7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄥ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆻ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄚㆴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄆㄧㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siau2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄠˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khio2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄧㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hap8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄞˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄇㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kau1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄠˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄋㆰˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ping2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅㄧㄥˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ku7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄚㆴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆻ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ting5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㆴ˙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>me5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄇㆤˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄧㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄥˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄢˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄣˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆬˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jia5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆢㄧㄚˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㄞˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㆲˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bun5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐㄧㆲˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗㆦ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ju5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆡㄨˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kian3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄧㄢ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iau1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄠˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sui3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㄧ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄧㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lun5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌㄨㄣˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄚˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒㄧㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sue3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙㄨㆤ˪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hio2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨㄧ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㆲˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄜˊ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄨㄣˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giam2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄧㆰˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆲˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gue7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣㄨㆤ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍㄜˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄨ˫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>co2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄨˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄑㄧㄢˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cut1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄨㆵˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ci2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄑㄧˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ce1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㆤˉ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>與</t>
-  </si>
-  <si>
-    <t>間</t>
-  </si>
-  <si>
-    <t>」</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>何</t>
-  </si>
-  <si>
-    <t>？</t>
-  </si>
-  <si>
-    <t>漢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>論</t>
-  </si>
-  <si>
-    <t>魏</t>
-  </si>
-  <si>
-    <t>！</t>
-  </si>
-  <si>
-    <t>言</t>
-  </si>
-  <si>
-    <t>皆</t>
-  </si>
-  <si>
-    <t>惋</t>
-  </si>
-  <si>
-    <t>餘</t>
-  </si>
-  <si>
-    <t>延</t>
-  </si>
-  <si>
-    <t>至</t>
-  </si>
-  <si>
-    <t>停</t>
-  </si>
-  <si>
-    <t>日</t>
-  </si>
-  <si>
-    <t>辭</t>
-  </si>
-  <si>
-    <t>語</t>
-  </si>
-  <si>
-    <t>足</t>
-  </si>
-  <si>
-    <t>道</t>
-  </si>
-  <si>
-    <t>也</t>
-  </si>
-  <si>
-    <t>既</t>
-  </si>
-  <si>
-    <t>向</t>
-  </si>
-  <si>
-    <t>處</t>
-  </si>
-  <si>
-    <t>誌</t>
-  </si>
-  <si>
-    <t>及</t>
-  </si>
-  <si>
-    <t>郡</t>
-  </si>
-  <si>
-    <t>守</t>
-  </si>
-  <si>
-    <t>說</t>
-  </si>
-  <si>
-    <t>遣</t>
-  </si>
-  <si>
-    <t>隨</t>
-  </si>
-  <si>
-    <t>尋</t>
-  </si>
-  <si>
-    <t>迷</t>
-  </si>
-  <si>
-    <t>南</t>
-  </si>
-  <si>
-    <t>陽</t>
-  </si>
-  <si>
-    <t>劉</t>
-  </si>
-  <si>
-    <t>驥</t>
-  </si>
-  <si>
-    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>尚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>士</t>
-  </si>
-  <si>
-    <t>規</t>
-  </si>
-  <si>
-    <t>未</t>
-  </si>
-  <si>
-    <t>果</t>
-  </si>
-  <si>
-    <t>病</t>
-  </si>
-  <si>
-    <t>終</t>
-  </si>
-  <si>
-    <t>後</t>
-  </si>
-  <si>
-    <t>津</t>
-  </si>
-  <si>
-    <t>者</t>
-  </si>
-  <si>
-    <t>鮮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>落</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>甚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>窮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zap8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>豁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>竹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>種</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>著</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>悉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>髫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>並</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>佁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>見</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>漁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>問</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>還</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>殺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ke1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>食</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>村</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>避</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>隔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>今</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>知</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>歎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>詣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>守</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>便</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thai3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㄞ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>guan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>poo7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㆦ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>giap8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄧㄚㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khe1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㆤˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loo7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㆦ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hut4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hua1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㄚˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄚㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ing1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄥˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kiong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ki5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>it4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>san1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㆲˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thoo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㆦˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bi2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ka1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄚˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆤˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khian2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄧㄢˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆲ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lai5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄞˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㄚㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiau5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄠˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nai2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄋㄞˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄚㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ham5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㆰˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sin3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄣ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>un5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>se3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pi7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>luan7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ip4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zuat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㄚㆵ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>king2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄥˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kan1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ho5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄜˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>han3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gui7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄞˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jit8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㆵ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ki3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kun7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄨㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ge7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㆤ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kui1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄨㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ko2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄜˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sim5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆬˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bun7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨㄣ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>than3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ling5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㄥˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jin5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hing5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lim5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㆬˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gan7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄢ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆦㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>song1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tai7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄞ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kim1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆬˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆦㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>語音類型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文讀音</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花源記【文讀音】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>欣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄠˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄊㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>king1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄥˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ping7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄥ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>piong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tau5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄠˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kap4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄚㆴ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hiong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>phin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄆㄧㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pun1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄨㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄠˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khio2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄧㄜˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>suan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hap8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄚㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄞˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liam2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㆰˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄇㄧㆻ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kau1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄠˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nam5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄋㆰˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sit4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆵ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ping2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄥˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ku7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tap4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄚㆴ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ting5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㄥˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄠˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㆴ˙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>me5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄇㆤˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄧㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bui7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨㄧ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㄣˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ua</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zian1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iong2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆲˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zut1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㆵˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆴ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>樂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄧㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄢˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄥˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>biong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄨㄢˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄣˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sian1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sim2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆬˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>piu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄨ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jia5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆢㄧㄚˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zai5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄞˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆲˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bun5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆠㄨㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziong2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄐㄧㆲˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zoo3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㆦ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄉㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ju5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆡㄨˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gau7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄠ˫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kian3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄍㄧㄢ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iau1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄠˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sai3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄞ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sui3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ze1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㆤˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>piu1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄅㄧㄨˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zui3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨㄧ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ian1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄧㄢˉ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lun5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄌㄨㄣˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄎㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㆣㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄗㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ha2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄚˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㄨˋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sue3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄙㄨㆤ˪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄒㄧㆲˊ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hio2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄏㄧㄜˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cut4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘㄨㆵ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄨˋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏㄧㆲ˪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3347,7 +3377,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="81">
+  <fonts count="83">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -3913,6 +3943,21 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFF0000"/>
+      <name val="吳守禮細明台語破音01"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFF0000"/>
+      <name val="吳守禮細明台語注音"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -4084,7 +4129,7 @@
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4393,6 +4438,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5547,7 +5601,7 @@
         <v>181</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -5670,46 +5724,46 @@
       <c r="D4" s="84"/>
       <c r="E4" s="84"/>
       <c r="F4" s="84" t="s">
+        <v>407</v>
+      </c>
+      <c r="G4" s="84" t="s">
+        <v>409</v>
+      </c>
+      <c r="H4" s="84" t="s">
+        <v>411</v>
+      </c>
+      <c r="I4" s="84" t="s">
+        <v>691</v>
+      </c>
+      <c r="J4" s="84" t="s">
+        <v>682</v>
+      </c>
+      <c r="K4" s="84" t="s">
         <v>413</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="L4" s="84" t="s">
+        <v>560</v>
+      </c>
+      <c r="M4" s="84" t="s">
+        <v>562</v>
+      </c>
+      <c r="N4" s="84" t="s">
+        <v>681</v>
+      </c>
+      <c r="O4" s="84" t="s">
         <v>415</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="P4" s="84" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q4" s="84" t="s">
+        <v>754</v>
+      </c>
+      <c r="R4" s="84" t="s">
         <v>417</v>
       </c>
-      <c r="I4" s="84" t="s">
-        <v>713</v>
-      </c>
-      <c r="J4" s="84" t="s">
-        <v>692</v>
-      </c>
-      <c r="K4" s="84" t="s">
-        <v>419</v>
-      </c>
-      <c r="L4" s="84" t="s">
-        <v>564</v>
-      </c>
-      <c r="M4" s="84" t="s">
-        <v>566</v>
-      </c>
-      <c r="N4" s="84" t="s">
-        <v>691</v>
-      </c>
-      <c r="O4" s="84" t="s">
-        <v>421</v>
-      </c>
-      <c r="P4" s="84" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q4" s="84" t="s">
-        <v>695</v>
-      </c>
-      <c r="R4" s="84" t="s">
-        <v>423</v>
-      </c>
       <c r="S4" s="93" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="T4" s="1">
         <v>8</v>
@@ -5774,39 +5828,39 @@
       <c r="D6" s="85"/>
       <c r="E6" s="85"/>
       <c r="F6" s="85" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="G6" s="85" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="H6" s="85" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="I6" s="85" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="L6" s="85" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="M6" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="N6" s="85"/>
       <c r="O6" s="85" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="P6" s="85" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="Q6" s="85" t="s">
-        <v>696</v>
+        <v>755</v>
       </c>
       <c r="R6" s="85" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="S6" s="95"/>
       <c r="V6" s="102"/>
@@ -5818,7 +5872,7 @@
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
       <c r="G7" s="83" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
@@ -5838,47 +5892,47 @@
       <c r="B8" s="56"/>
       <c r="D8" s="84"/>
       <c r="E8" s="84" t="s">
-        <v>715</v>
+        <v>693</v>
       </c>
       <c r="F8" s="84" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G8" s="84" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="H8" s="84"/>
       <c r="I8" s="84" t="s">
-        <v>718</v>
+        <v>696</v>
       </c>
       <c r="J8" s="84" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="K8" s="84" t="s">
+        <v>425</v>
+      </c>
+      <c r="L8" s="84" t="s">
+        <v>698</v>
+      </c>
+      <c r="M8" s="84" t="s">
+        <v>700</v>
+      </c>
+      <c r="N8" s="84" t="s">
+        <v>681</v>
+      </c>
+      <c r="O8" s="84" t="s">
+        <v>427</v>
+      </c>
+      <c r="P8" s="84" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q8" s="84" t="s">
+        <v>758</v>
+      </c>
+      <c r="R8" s="84" t="s">
         <v>431</v>
       </c>
-      <c r="L8" s="84" t="s">
-        <v>720</v>
-      </c>
-      <c r="M8" s="84" t="s">
-        <v>722</v>
-      </c>
-      <c r="N8" s="84" t="s">
-        <v>691</v>
-      </c>
-      <c r="O8" s="84" t="s">
-        <v>433</v>
-      </c>
-      <c r="P8" s="84" t="s">
-        <v>615</v>
-      </c>
-      <c r="Q8" s="84" t="s">
-        <v>617</v>
-      </c>
-      <c r="R8" s="84" t="s">
-        <v>437</v>
-      </c>
       <c r="S8" s="93" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="T8" s="1">
         <v>1</v>
@@ -5943,42 +5997,42 @@
       <c r="B10" s="58"/>
       <c r="D10" s="85"/>
       <c r="E10" s="85" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
       <c r="F10" s="85" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="G10" s="85" t="s">
-        <v>717</v>
+        <v>695</v>
       </c>
       <c r="H10" s="85"/>
       <c r="I10" s="85" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="J10" s="85" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="K10" s="85" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="L10" s="85" t="s">
-        <v>721</v>
+        <v>699</v>
       </c>
       <c r="M10" s="85" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
       <c r="N10" s="85"/>
       <c r="O10" s="85" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="P10" s="85" t="s">
-        <v>616</v>
+        <v>757</v>
       </c>
       <c r="Q10" s="85" t="s">
-        <v>618</v>
+        <v>759</v>
       </c>
       <c r="R10" s="85" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="S10" s="96"/>
       <c r="V10" s="102"/>
@@ -6006,43 +6060,43 @@
     <row r="12" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
       <c r="D12" s="84" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E12" s="84"/>
       <c r="F12" s="84" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="G12" s="84" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="H12" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I12" s="84" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="J12" s="84" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="K12" s="84"/>
       <c r="L12" s="84" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="M12" s="84" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="N12" s="84" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="O12" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="P12" s="84"/>
       <c r="Q12" s="84" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="R12" s="84" t="s">
-        <v>697</v>
+        <v>776</v>
       </c>
       <c r="S12" s="93"/>
       <c r="V12" s="102"/>
@@ -6094,7 +6148,7 @@
       <c r="Q13" s="98" t="s">
         <v>220</v>
       </c>
-      <c r="R13" s="98" t="s">
+      <c r="R13" s="100" t="s">
         <v>221</v>
       </c>
       <c r="S13" s="94"/>
@@ -6103,43 +6157,43 @@
     <row r="14" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
       <c r="D14" s="85" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E14" s="85"/>
       <c r="F14" s="85" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="G14" s="85" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H14" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="I14" s="85" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="J14" s="85" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K14" s="85"/>
       <c r="L14" s="85" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="M14" s="85" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="N14" s="85" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="O14" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="P14" s="85"/>
       <c r="Q14" s="85" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="R14" s="85" t="s">
-        <v>604</v>
+        <v>777</v>
       </c>
       <c r="S14" s="96"/>
       <c r="V14" s="102"/>
@@ -6170,43 +6224,43 @@
     <row r="16" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="56"/>
       <c r="D16" s="84" t="s">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="E16" s="84" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F16" s="84"/>
       <c r="G16" s="84" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H16" s="84" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="I16" s="84" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="J16" s="84" t="s">
-        <v>625</v>
+        <v>760</v>
       </c>
       <c r="K16" s="84"/>
       <c r="L16" s="84" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="M16" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="N16" s="84" t="s">
-        <v>726</v>
+        <v>704</v>
       </c>
       <c r="O16" s="84" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="P16" s="84" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="Q16" s="84"/>
       <c r="R16" s="84" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="S16" s="93"/>
       <c r="V16" s="102"/>
@@ -6217,7 +6271,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="80" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E17" s="80" t="s">
         <v>222</v>
@@ -6226,7 +6280,7 @@
         <v>190</v>
       </c>
       <c r="G17" s="80" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="H17" s="80" t="s">
         <v>223</v>
@@ -6247,7 +6301,7 @@
         <v>193</v>
       </c>
       <c r="N17" s="80" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O17" s="80" t="s">
         <v>227</v>
@@ -6267,43 +6321,43 @@
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
       <c r="D18" s="85" t="s">
-        <v>725</v>
+        <v>703</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F18" s="85"/>
       <c r="G18" s="85" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="H18" s="85" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="I18" s="85" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="J18" s="85" t="s">
-        <v>626</v>
+        <v>761</v>
       </c>
       <c r="K18" s="85"/>
       <c r="L18" s="85" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M18" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="N18" s="85" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
       <c r="O18" s="85" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="P18" s="85" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="Q18" s="85"/>
       <c r="R18" s="85" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="S18" s="96"/>
       <c r="V18" s="102"/>
@@ -6331,23 +6385,23 @@
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
       <c r="D20" s="84" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E20" s="84" t="s">
-        <v>435</v>
+        <v>564</v>
       </c>
       <c r="F20" s="84"/>
       <c r="G20" s="84" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="H20" s="84" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="I20" s="84" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="J20" s="84" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="K20" s="84"/>
       <c r="L20" s="84"/>
@@ -6366,9 +6420,9 @@
         <v>5</v>
       </c>
       <c r="D21" s="80" t="s">
-        <v>369</v>
-      </c>
-      <c r="E21" s="80" t="s">
+        <v>363</v>
+      </c>
+      <c r="E21" s="98" t="s">
         <v>200</v>
       </c>
       <c r="F21" s="80" t="s">
@@ -6378,7 +6432,7 @@
         <v>230</v>
       </c>
       <c r="H21" s="80" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="I21" s="80" t="s">
         <v>231</v>
@@ -6402,23 +6456,23 @@
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
       <c r="D22" s="85" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E22" s="85" t="s">
-        <v>436</v>
+        <v>695</v>
       </c>
       <c r="F22" s="85"/>
       <c r="G22" s="85" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="H22" s="85" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="I22" s="85" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="J22" s="85" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="K22" s="85"/>
       <c r="L22" s="85"/>
@@ -6547,39 +6601,39 @@
       <c r="D28" s="84"/>
       <c r="E28" s="84"/>
       <c r="F28" s="84" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="G28" s="84" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="H28" s="84" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="I28" s="84" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="J28" s="84"/>
       <c r="K28" s="84" t="s">
-        <v>647</v>
+        <v>442</v>
       </c>
       <c r="L28" s="84" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="M28" s="84" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N28" s="84" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="O28" s="84"/>
       <c r="P28" s="84" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="Q28" s="84" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="R28" s="84" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="S28" s="93"/>
       <c r="U28" s="67" t="str">
@@ -6650,39 +6704,39 @@
       <c r="D30" s="85"/>
       <c r="E30" s="85"/>
       <c r="F30" s="85" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="G30" s="85" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="H30" s="85" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I30" s="85" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="J30" s="85"/>
       <c r="K30" s="85" t="s">
-        <v>648</v>
+        <v>443</v>
       </c>
       <c r="L30" s="85" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="N30" s="85" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="O30" s="85"/>
       <c r="P30" s="85" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q30" s="85" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="R30" s="85" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S30" s="96"/>
       <c r="U30" s="67" t="str">
@@ -6718,43 +6772,43 @@
     <row r="32" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="56"/>
       <c r="D32" s="84" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E32" s="84"/>
       <c r="F32" s="84" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="G32" s="84" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="H32" s="84" t="s">
-        <v>730</v>
+        <v>706</v>
       </c>
       <c r="I32" s="84" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J32" s="84" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
       <c r="K32" s="84"/>
       <c r="L32" s="84" t="s">
-        <v>647</v>
+        <v>442</v>
       </c>
       <c r="M32" s="84" t="s">
-        <v>734</v>
+        <v>710</v>
       </c>
       <c r="N32" s="84" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="O32" s="84"/>
       <c r="P32" s="84" t="s">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="Q32" s="84" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="R32" s="84" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="S32" s="93"/>
       <c r="U32" s="67" t="str">
@@ -6792,7 +6846,7 @@
       <c r="K33" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="L33" s="80" t="s">
+      <c r="L33" s="98" t="s">
         <v>235</v>
       </c>
       <c r="M33" s="80" t="s">
@@ -6819,43 +6873,43 @@
     <row r="34" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="58"/>
       <c r="D34" s="85" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E34" s="85"/>
       <c r="F34" s="85" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="G34" s="85" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H34" s="85" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="I34" s="85" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J34" s="85" t="s">
-        <v>733</v>
+        <v>709</v>
       </c>
       <c r="K34" s="85"/>
       <c r="L34" s="85" t="s">
-        <v>648</v>
+        <v>443</v>
       </c>
       <c r="M34" s="85" t="s">
-        <v>735</v>
+        <v>711</v>
       </c>
       <c r="N34" s="85" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="O34" s="85"/>
       <c r="P34" s="85" t="s">
-        <v>737</v>
+        <v>713</v>
       </c>
       <c r="Q34" s="85" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="R34" s="85" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="S34" s="96"/>
       <c r="V34" s="60"/>
@@ -6884,39 +6938,39 @@
       <c r="B36" s="56"/>
       <c r="D36" s="84"/>
       <c r="E36" s="84" t="s">
-        <v>698</v>
+        <v>778</v>
       </c>
       <c r="F36" s="84" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G36" s="84" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="H36" s="84"/>
       <c r="I36" s="84" t="s">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="J36" s="84" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="K36" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="L36" s="84"/>
       <c r="M36" s="84" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="N36" s="84" t="s">
-        <v>435</v>
+        <v>564</v>
       </c>
       <c r="O36" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="P36" s="84" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="Q36" s="84" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="R36" s="84"/>
       <c r="S36" s="93"/>
@@ -6979,39 +7033,39 @@
       <c r="B38" s="58"/>
       <c r="D38" s="85"/>
       <c r="E38" s="85" t="s">
-        <v>699</v>
+        <v>779</v>
       </c>
       <c r="F38" s="85" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G38" s="85" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="H38" s="85"/>
       <c r="I38" s="85" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
       <c r="J38" s="85" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="K38" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="L38" s="85"/>
       <c r="M38" s="85" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="N38" s="85" t="s">
-        <v>436</v>
+        <v>695</v>
       </c>
       <c r="O38" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="P38" s="85" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="Q38" s="85" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="R38" s="85"/>
       <c r="S38" s="96"/>
@@ -7040,42 +7094,42 @@
     <row r="40" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="56"/>
       <c r="D40" s="84" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E40" s="84" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F40" s="84" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="G40" s="84" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H40" s="84"/>
       <c r="I40" s="84" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J40" s="84" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="K40" s="84" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="L40" s="84" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="M40" s="84"/>
       <c r="N40" s="84" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="O40" s="84" t="s">
-        <v>734</v>
+        <v>710</v>
       </c>
       <c r="P40" s="84" t="s">
-        <v>649</v>
+        <v>762</v>
       </c>
       <c r="Q40" s="84" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="R40" s="84"/>
       <c r="S40" s="93"/>
@@ -7087,7 +7141,7 @@
         <v>10</v>
       </c>
       <c r="D41" s="98" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E41" s="80" t="s">
         <v>256</v>
@@ -7137,42 +7191,42 @@
     <row r="42" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="58"/>
       <c r="D42" s="85" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E42" s="85" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F42" s="85" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="G42" s="85" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H42" s="85"/>
       <c r="I42" s="85" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J42" s="85" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="K42" s="85" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="L42" s="85" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="M42" s="85"/>
       <c r="N42" s="85" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="O42" s="85" t="s">
-        <v>735</v>
+        <v>711</v>
       </c>
       <c r="P42" s="85" t="s">
-        <v>650</v>
+        <v>763</v>
       </c>
       <c r="Q42" s="85" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="R42" s="85"/>
       <c r="S42" s="96"/>
@@ -7201,41 +7255,41 @@
     <row r="44" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="56"/>
       <c r="D44" s="84" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E44" s="84" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="F44" s="84" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="G44" s="84"/>
       <c r="H44" s="84" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="I44" s="84" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J44" s="84"/>
       <c r="K44" s="84" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="L44" s="84"/>
       <c r="M44" s="84" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N44" s="84" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="O44" s="84" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="P44" s="84"/>
       <c r="Q44" s="84" t="s">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="R44" s="84" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="S44" s="93"/>
       <c r="V44" s="60"/>
@@ -7267,28 +7321,28 @@
         <v>267</v>
       </c>
       <c r="K45" s="80" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="L45" s="80" t="s">
         <v>267</v>
       </c>
       <c r="M45" s="80" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="N45" s="80" t="s">
         <v>203</v>
       </c>
       <c r="O45" s="80" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="P45" s="80" t="s">
         <v>190</v>
       </c>
       <c r="Q45" s="80" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="R45" s="80" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="S45" s="94"/>
       <c r="V45" s="60"/>
@@ -7296,41 +7350,41 @@
     <row r="46" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="58"/>
       <c r="D46" s="85" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E46" s="85" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="F46" s="85" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G46" s="85"/>
       <c r="H46" s="85" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="I46" s="85" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J46" s="85"/>
       <c r="K46" s="85" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="L46" s="85"/>
       <c r="M46" s="85" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N46" s="85" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="O46" s="85" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="P46" s="85"/>
       <c r="Q46" s="85" t="s">
-        <v>605</v>
+        <v>781</v>
       </c>
       <c r="R46" s="85" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="S46" s="96"/>
       <c r="V46" s="60"/>
@@ -7358,42 +7412,42 @@
     <row r="48" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="56"/>
       <c r="D48" s="84" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="E48" s="84" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F48" s="84"/>
       <c r="G48" s="84" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H48" s="84" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I48" s="84" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="J48" s="84" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="K48" s="84"/>
       <c r="L48" s="84" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M48" s="84" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="N48" s="84" t="s">
-        <v>701</v>
+        <v>764</v>
       </c>
       <c r="O48" s="84" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="P48" s="84" t="s">
-        <v>744</v>
+        <v>720</v>
       </c>
       <c r="Q48" s="84" t="s">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="R48" s="84"/>
       <c r="S48" s="93"/>
@@ -7414,7 +7468,7 @@
         <v>190</v>
       </c>
       <c r="G49" s="80" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="H49" s="80" t="s">
         <v>271</v>
@@ -7440,8 +7494,8 @@
       <c r="O49" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="P49" s="80" t="s">
-        <v>379</v>
+      <c r="P49" s="100" t="s">
+        <v>373</v>
       </c>
       <c r="Q49" s="80" t="s">
         <v>276</v>
@@ -7455,42 +7509,42 @@
     <row r="50" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="58"/>
       <c r="D50" s="85" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="E50" s="85" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F50" s="85"/>
       <c r="G50" s="85" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H50" s="85" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I50" s="85" t="s">
-        <v>741</v>
+        <v>717</v>
       </c>
       <c r="J50" s="85" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="K50" s="85"/>
       <c r="L50" s="85" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="M50" s="85" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="N50" s="85" t="s">
-        <v>702</v>
+        <v>765</v>
       </c>
       <c r="O50" s="85" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="P50" s="85" t="s">
-        <v>745</v>
+        <v>721</v>
       </c>
       <c r="Q50" s="85" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="R50" s="85"/>
       <c r="S50" s="96"/>
@@ -7519,42 +7573,42 @@
     <row r="52" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="56"/>
       <c r="D52" s="84" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="E52" s="84" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="F52" s="84" t="s">
-        <v>750</v>
+        <v>726</v>
       </c>
       <c r="G52" s="84" t="s">
-        <v>752</v>
+        <v>582</v>
       </c>
       <c r="H52" s="84"/>
       <c r="I52" s="84" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="J52" s="84" t="s">
-        <v>754</v>
+        <v>728</v>
       </c>
       <c r="K52" s="84" t="s">
-        <v>525</v>
+        <v>766</v>
       </c>
       <c r="L52" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M52" s="84"/>
       <c r="N52" s="84" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="O52" s="84" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="P52" s="84" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="Q52" s="84" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="R52" s="84"/>
       <c r="S52" s="93"/>
@@ -7574,14 +7628,14 @@
       <c r="F53" s="80" t="s">
         <v>279</v>
       </c>
-      <c r="G53" s="81" t="s">
-        <v>380</v>
+      <c r="G53" s="107" t="s">
+        <v>374</v>
       </c>
       <c r="H53" s="81" t="s">
         <v>190</v>
       </c>
       <c r="I53" s="80" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J53" s="80" t="s">
         <v>280</v>
@@ -7605,7 +7659,7 @@
         <v>284</v>
       </c>
       <c r="Q53" s="80" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="R53" s="80" t="s">
         <v>190</v>
@@ -7616,42 +7670,42 @@
     <row r="54" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="58"/>
       <c r="D54" s="85" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="E54" s="85" t="s">
-        <v>749</v>
+        <v>725</v>
       </c>
       <c r="F54" s="85" t="s">
-        <v>751</v>
+        <v>727</v>
       </c>
       <c r="G54" s="85" t="s">
-        <v>753</v>
+        <v>583</v>
       </c>
       <c r="H54" s="85"/>
       <c r="I54" s="85" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="J54" s="85" t="s">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="K54" s="85" t="s">
-        <v>526</v>
+        <v>767</v>
       </c>
       <c r="L54" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M54" s="85"/>
       <c r="N54" s="85" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="O54" s="85" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="P54" s="85" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="Q54" s="85" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="R54" s="85"/>
       <c r="S54" s="96"/>
@@ -7680,43 +7734,43 @@
     <row r="56" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="56"/>
       <c r="D56" s="84" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="E56" s="84" t="s">
-        <v>756</v>
+        <v>730</v>
       </c>
       <c r="F56" s="84" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G56" s="84" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="H56" s="84" t="s">
-        <v>758</v>
+        <v>380</v>
       </c>
       <c r="I56" s="84"/>
       <c r="J56" s="84" t="s">
-        <v>760</v>
+        <v>732</v>
       </c>
       <c r="K56" s="84" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="L56" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M56" s="84"/>
       <c r="N56" s="84" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="O56" s="84" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P56" s="84" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="Q56" s="84"/>
       <c r="R56" s="84" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="S56" s="93"/>
       <c r="V56" s="60"/>
@@ -7727,28 +7781,28 @@
         <v>14</v>
       </c>
       <c r="D57" s="80" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="E57" s="100" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F57" s="80" t="s">
         <v>256</v>
       </c>
       <c r="G57" s="81" t="s">
-        <v>385</v>
-      </c>
-      <c r="H57" s="81" t="s">
-        <v>712</v>
+        <v>379</v>
+      </c>
+      <c r="H57" s="107" t="s">
+        <v>690</v>
       </c>
       <c r="I57" s="80" t="s">
         <v>228</v>
       </c>
       <c r="J57" s="80" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="K57" s="80" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="L57" s="80" t="s">
         <v>193</v>
@@ -7760,7 +7814,7 @@
         <v>286</v>
       </c>
       <c r="O57" s="80" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="P57" s="80" t="s">
         <v>287</v>
@@ -7769,7 +7823,7 @@
         <v>190</v>
       </c>
       <c r="R57" s="80" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="S57" s="94"/>
       <c r="V57" s="60"/>
@@ -7777,43 +7831,43 @@
     <row r="58" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="58"/>
       <c r="D58" s="85" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="E58" s="85" t="s">
-        <v>757</v>
+        <v>731</v>
       </c>
       <c r="F58" s="85" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G58" s="85" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="H58" s="85" t="s">
-        <v>759</v>
+        <v>478</v>
       </c>
       <c r="I58" s="85"/>
       <c r="J58" s="85" t="s">
-        <v>761</v>
+        <v>733</v>
       </c>
       <c r="K58" s="85" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="L58" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M58" s="85"/>
       <c r="N58" s="85" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="O58" s="85" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="P58" s="85" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q58" s="85"/>
       <c r="R58" s="85" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="S58" s="96"/>
       <c r="V58" s="60"/>
@@ -7841,43 +7895,43 @@
     <row r="60" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="56"/>
       <c r="D60" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="E60" s="84" t="s">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="F60" s="84" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="G60" s="84"/>
       <c r="H60" s="84" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="I60" s="84" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="K60" s="84"/>
       <c r="L60" s="84" t="s">
-        <v>647</v>
+        <v>442</v>
       </c>
       <c r="M60" s="84" t="s">
-        <v>762</v>
+        <v>734</v>
       </c>
       <c r="N60" s="84" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="O60" s="84" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="P60" s="84"/>
       <c r="Q60" s="84" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="R60" s="84" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="S60" s="93"/>
       <c r="V60" s="60"/>
@@ -7911,14 +7965,14 @@
       <c r="K61" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="L61" s="80" t="s">
+      <c r="L61" s="98" t="s">
         <v>235</v>
       </c>
       <c r="M61" s="80" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="N61" s="80" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="O61" s="80" t="s">
         <v>292</v>
@@ -7938,43 +7992,43 @@
     <row r="62" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="58"/>
       <c r="D62" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="E62" s="85" t="s">
-        <v>737</v>
+        <v>713</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G62" s="85"/>
       <c r="H62" s="85" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="I62" s="85" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="J62" s="85" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="K62" s="85"/>
       <c r="L62" s="85" t="s">
-        <v>648</v>
+        <v>443</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>763</v>
+        <v>735</v>
       </c>
       <c r="N62" s="85" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="O62" s="85" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="P62" s="85"/>
       <c r="Q62" s="85" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="R62" s="85" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="S62" s="96"/>
       <c r="V62" s="60"/>
@@ -8003,40 +8057,40 @@
       <c r="B64" s="56"/>
       <c r="D64" s="84"/>
       <c r="E64" s="84" t="s">
-        <v>764</v>
+        <v>586</v>
       </c>
       <c r="F64" s="84" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="G64" s="84"/>
       <c r="H64" s="84" t="s">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="I64" s="84" t="s">
-        <v>442</v>
+        <v>663</v>
       </c>
       <c r="J64" s="84"/>
       <c r="K64" s="84" t="s">
-        <v>703</v>
+        <v>782</v>
       </c>
       <c r="L64" s="84" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="M64" s="84" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="N64" s="84" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="O64" s="84" t="s">
-        <v>673</v>
+        <v>784</v>
       </c>
       <c r="P64" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="Q64" s="84"/>
       <c r="R64" s="84" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="S64" s="93"/>
       <c r="V64" s="60"/>
@@ -8049,8 +8103,8 @@
       <c r="D65" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="E65" s="80" t="s">
-        <v>393</v>
+      <c r="E65" s="98" t="s">
+        <v>387</v>
       </c>
       <c r="F65" s="80" t="s">
         <v>270</v>
@@ -8061,14 +8115,14 @@
       <c r="H65" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="I65" s="80" t="s">
-        <v>395</v>
+      <c r="I65" s="98" t="s">
+        <v>389</v>
       </c>
       <c r="J65" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="K65" s="80" t="s">
-        <v>396</v>
+      <c r="K65" s="100" t="s">
+        <v>390</v>
       </c>
       <c r="L65" s="80" t="s">
         <v>189</v>
@@ -8098,40 +8152,40 @@
       <c r="B66" s="58"/>
       <c r="D66" s="85"/>
       <c r="E66" s="85" t="s">
-        <v>765</v>
+        <v>587</v>
       </c>
       <c r="F66" s="85" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G66" s="85"/>
       <c r="H66" s="85" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="I66" s="85" t="s">
-        <v>443</v>
+        <v>664</v>
       </c>
       <c r="J66" s="85"/>
       <c r="K66" s="85" t="s">
-        <v>704</v>
+        <v>783</v>
       </c>
       <c r="L66" s="85" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="M66" s="85" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="N66" s="85" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="O66" s="85" t="s">
-        <v>674</v>
+        <v>785</v>
       </c>
       <c r="P66" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="Q66" s="85"/>
       <c r="R66" s="85" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="S66" s="96"/>
       <c r="V66" s="60"/>
@@ -8159,40 +8213,40 @@
     <row r="68" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="56"/>
       <c r="D68" s="84" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E68" s="84" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F68" s="84" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G68" s="84"/>
       <c r="H68" s="84" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="I68" s="84" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="J68" s="84"/>
       <c r="K68" s="84"/>
       <c r="L68" s="84" t="s">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="M68" s="84" t="s">
+        <v>493</v>
+      </c>
+      <c r="N68" s="84" t="s">
+        <v>495</v>
+      </c>
+      <c r="O68" s="84" t="s">
+        <v>497</v>
+      </c>
+      <c r="P68" s="84" t="s">
         <v>499</v>
       </c>
-      <c r="N68" s="84" t="s">
+      <c r="Q68" s="84" t="s">
         <v>501</v>
-      </c>
-      <c r="O68" s="84" t="s">
-        <v>503</v>
-      </c>
-      <c r="P68" s="84" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q68" s="84" t="s">
-        <v>507</v>
       </c>
       <c r="R68" s="84"/>
       <c r="S68" s="93"/>
@@ -8234,7 +8288,7 @@
         <v>302</v>
       </c>
       <c r="N69" s="80" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="O69" s="80" t="s">
         <v>303</v>
@@ -8254,40 +8308,40 @@
     <row r="70" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="58"/>
       <c r="D70" s="85" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="E70" s="85" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F70" s="85" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="G70" s="85"/>
       <c r="H70" s="85" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="I70" s="85" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="J70" s="85"/>
       <c r="K70" s="85"/>
       <c r="L70" s="85" t="s">
-        <v>725</v>
+        <v>703</v>
       </c>
       <c r="M70" s="85" t="s">
+        <v>494</v>
+      </c>
+      <c r="N70" s="85" t="s">
+        <v>496</v>
+      </c>
+      <c r="O70" s="85" t="s">
+        <v>498</v>
+      </c>
+      <c r="P70" s="85" t="s">
         <v>500</v>
       </c>
-      <c r="N70" s="85" t="s">
+      <c r="Q70" s="85" t="s">
         <v>502</v>
-      </c>
-      <c r="O70" s="85" t="s">
-        <v>504</v>
-      </c>
-      <c r="P70" s="85" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q70" s="85" t="s">
-        <v>508</v>
       </c>
       <c r="R70" s="85"/>
       <c r="S70" s="96"/>
@@ -8316,44 +8370,44 @@
     <row r="72" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="56"/>
       <c r="D72" s="84" t="s">
-        <v>766</v>
+        <v>736</v>
       </c>
       <c r="E72" s="84" t="s">
-        <v>768</v>
+        <v>786</v>
       </c>
       <c r="F72" s="84" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="G72" s="84" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="H72" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="I72" s="84" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="J72" s="84" t="s">
-        <v>673</v>
+        <v>784</v>
       </c>
       <c r="K72" s="84" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="L72" s="84" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="M72" s="84"/>
       <c r="N72" s="84" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="O72" s="84" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="P72" s="84" t="s">
-        <v>772</v>
+        <v>794</v>
       </c>
       <c r="Q72" s="84" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="R72" s="84"/>
       <c r="S72" s="93"/>
@@ -8400,7 +8454,7 @@
       <c r="O73" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="P73" s="80" t="s">
+      <c r="P73" s="98" t="s">
         <v>313</v>
       </c>
       <c r="Q73" s="80" t="s">
@@ -8415,44 +8469,44 @@
     <row r="74" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="58"/>
       <c r="D74" s="85" t="s">
-        <v>767</v>
+        <v>737</v>
       </c>
       <c r="E74" s="85" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
       <c r="F74" s="85" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="G74" s="85" t="s">
-        <v>705</v>
+        <v>685</v>
       </c>
       <c r="H74" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="I74" s="85" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="J74" s="85" t="s">
-        <v>674</v>
+        <v>785</v>
       </c>
       <c r="K74" s="85" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="L74" s="85" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="M74" s="85"/>
       <c r="N74" s="85" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="O74" s="85" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="P74" s="85" t="s">
-        <v>773</v>
+        <v>795</v>
       </c>
       <c r="Q74" s="85" t="s">
-        <v>775</v>
+        <v>739</v>
       </c>
       <c r="R74" s="85"/>
       <c r="S74" s="96"/>
@@ -8481,19 +8535,19 @@
     <row r="76" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="56"/>
       <c r="D76" s="84" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E76" s="84" t="s">
-        <v>533</v>
+        <v>796</v>
       </c>
       <c r="F76" s="84" t="s">
-        <v>525</v>
+        <v>766</v>
       </c>
       <c r="G76" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="H76" s="84" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="I76" s="84" t="s">
         <v>588</v>
@@ -8501,20 +8555,20 @@
       <c r="J76" s="84"/>
       <c r="K76" s="84"/>
       <c r="L76" s="84" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="M76" s="84"/>
       <c r="N76" s="84" t="s">
         <v>590</v>
       </c>
       <c r="O76" s="84" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="P76" s="84" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="Q76" s="84" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="R76" s="84"/>
       <c r="S76" s="93"/>
@@ -8528,8 +8582,8 @@
       <c r="D77" s="80" t="s">
         <v>315</v>
       </c>
-      <c r="E77" s="80" t="s">
-        <v>316</v>
+      <c r="E77" s="108" t="s">
+        <v>790</v>
       </c>
       <c r="F77" s="80" t="s">
         <v>281</v>
@@ -8538,16 +8592,16 @@
         <v>193</v>
       </c>
       <c r="H77" s="80" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I77" s="80" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="J77" s="80" t="s">
         <v>228</v>
       </c>
       <c r="K77" s="80" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L77" s="80" t="s">
         <v>288</v>
@@ -8556,19 +8610,19 @@
         <v>300</v>
       </c>
       <c r="N77" s="80" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="O77" s="80" t="s">
+        <v>318</v>
+      </c>
+      <c r="P77" s="80" t="s">
         <v>319</v>
-      </c>
-      <c r="P77" s="80" t="s">
-        <v>320</v>
       </c>
       <c r="Q77" s="80" t="s">
         <v>302</v>
       </c>
       <c r="R77" s="80" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S77" s="94"/>
       <c r="V77" s="60"/>
@@ -8576,19 +8630,19 @@
     <row r="78" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="58"/>
       <c r="D78" s="85" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E78" s="85" t="s">
-        <v>534</v>
+        <v>797</v>
       </c>
       <c r="F78" s="85" t="s">
-        <v>526</v>
+        <v>767</v>
       </c>
       <c r="G78" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="H78" s="85" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="I78" s="85" t="s">
         <v>589</v>
@@ -8596,20 +8650,20 @@
       <c r="J78" s="85"/>
       <c r="K78" s="85"/>
       <c r="L78" s="85" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="M78" s="85"/>
       <c r="N78" s="85" t="s">
         <v>591</v>
       </c>
       <c r="O78" s="85" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="P78" s="85" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="Q78" s="85" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="R78" s="85"/>
       <c r="S78" s="96"/>
@@ -8639,40 +8693,40 @@
       <c r="B80" s="56"/>
       <c r="D80" s="84"/>
       <c r="E80" s="84" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="F80" s="84" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="G80" s="84" t="s">
         <v>592</v>
       </c>
       <c r="H80" s="84" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="I80" s="84" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="J80" s="84"/>
       <c r="K80" s="84" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="L80" s="84" t="s">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="M80" s="84" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="N80" s="84"/>
       <c r="O80" s="84" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="P80" s="84"/>
       <c r="Q80" s="84" t="s">
-        <v>673</v>
+        <v>784</v>
       </c>
       <c r="R80" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="S80" s="93"/>
       <c r="V80" s="60"/>
@@ -8683,7 +8737,7 @@
         <v>20</v>
       </c>
       <c r="D81" s="80" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E81" s="80" t="s">
         <v>286</v>
@@ -8692,13 +8746,13 @@
         <v>312</v>
       </c>
       <c r="G81" s="80" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H81" s="80" t="s">
         <v>239</v>
       </c>
       <c r="I81" s="80" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J81" s="80" t="s">
         <v>190</v>
@@ -8707,10 +8761,10 @@
         <v>217</v>
       </c>
       <c r="L81" s="80" t="s">
-        <v>323</v>
+        <v>791</v>
       </c>
       <c r="M81" s="80" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N81" s="80" t="s">
         <v>267</v>
@@ -8719,7 +8773,7 @@
         <v>186</v>
       </c>
       <c r="P81" s="80" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q81" s="80" t="s">
         <v>295</v>
@@ -8734,40 +8788,40 @@
       <c r="B82" s="58"/>
       <c r="D82" s="85"/>
       <c r="E82" s="85" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F82" s="85" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="G82" s="85" t="s">
         <v>593</v>
       </c>
       <c r="H82" s="85" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I82" s="85" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="J82" s="85"/>
       <c r="K82" s="85" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="L82" s="85" t="s">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="M82" s="85" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="N82" s="85"/>
       <c r="O82" s="85" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="P82" s="85"/>
       <c r="Q82" s="85" t="s">
-        <v>674</v>
+        <v>785</v>
       </c>
       <c r="R82" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="S82" s="96"/>
       <c r="V82" s="60"/>
@@ -8795,42 +8849,42 @@
     <row r="84" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="56"/>
       <c r="D84" s="84" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E84" s="84" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F84" s="84" t="s">
-        <v>695</v>
+        <v>754</v>
       </c>
       <c r="G84" s="84" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="H84" s="84" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="I84" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="J84" s="84" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="K84" s="84"/>
       <c r="L84" s="84" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="M84" s="84" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="N84" s="84" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="O84" s="84"/>
       <c r="P84" s="84" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="Q84" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="R84" s="84" t="s">
         <v>594</v>
@@ -8844,7 +8898,7 @@
         <v>21</v>
       </c>
       <c r="D85" s="80" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E85" s="80" t="s">
         <v>237</v>
@@ -8856,7 +8910,7 @@
         <v>290</v>
       </c>
       <c r="H85" s="80" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I85" s="80" t="s">
         <v>289</v>
@@ -8868,25 +8922,25 @@
         <v>190</v>
       </c>
       <c r="L85" s="80" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M85" s="80" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="N85" s="80" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O85" s="80" t="s">
         <v>228</v>
       </c>
       <c r="P85" s="80" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q85" s="80" t="s">
         <v>193</v>
       </c>
       <c r="R85" s="80" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="S85" s="94"/>
       <c r="V85" s="60"/>
@@ -8894,42 +8948,42 @@
     <row r="86" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="58"/>
       <c r="D86" s="85" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E86" s="85" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F86" s="85" t="s">
-        <v>696</v>
+        <v>755</v>
       </c>
       <c r="G86" s="85" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="H86" s="85" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="I86" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="J86" s="85" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="K86" s="85"/>
       <c r="L86" s="85" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="M86" s="85" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="N86" s="85" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="O86" s="85"/>
       <c r="P86" s="85" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="Q86" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="R86" s="85" t="s">
         <v>595</v>
@@ -8960,42 +9014,42 @@
     <row r="88" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B88" s="56"/>
       <c r="D88" s="84" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="E88" s="84" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F88" s="84" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G88" s="84" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H88" s="84" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="I88" s="84"/>
       <c r="J88" s="84" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="K88" s="84" t="s">
-        <v>772</v>
+        <v>794</v>
       </c>
       <c r="L88" s="84" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="M88" s="84" t="s">
-        <v>442</v>
+        <v>663</v>
       </c>
       <c r="N88" s="84"/>
       <c r="O88" s="84" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="P88" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="Q88" s="84" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="R88" s="84"/>
       <c r="S88" s="93"/>
@@ -9010,10 +9064,10 @@
         <v>229</v>
       </c>
       <c r="E89" s="80" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F89" s="80" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G89" s="80" t="s">
         <v>231</v>
@@ -9025,28 +9079,28 @@
         <v>190</v>
       </c>
       <c r="J89" s="80" t="s">
-        <v>327</v>
-      </c>
-      <c r="K89" s="80" t="s">
+        <v>325</v>
+      </c>
+      <c r="K89" s="98" t="s">
         <v>313</v>
       </c>
       <c r="L89" s="80" t="s">
         <v>294</v>
       </c>
-      <c r="M89" s="80" t="s">
-        <v>395</v>
+      <c r="M89" s="98" t="s">
+        <v>389</v>
       </c>
       <c r="N89" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="O89" s="80" t="s">
-        <v>332</v>
+      <c r="O89" s="100" t="s">
+        <v>330</v>
       </c>
       <c r="P89" s="80" t="s">
         <v>214</v>
       </c>
       <c r="Q89" s="80" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="R89" s="80" t="s">
         <v>190</v>
@@ -9057,42 +9111,42 @@
     <row r="90" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="58"/>
       <c r="D90" s="85" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="E90" s="85" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F90" s="85" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G90" s="85" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H90" s="85" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="I90" s="85"/>
       <c r="J90" s="85" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="K90" s="85" t="s">
-        <v>773</v>
+        <v>795</v>
       </c>
       <c r="L90" s="85" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="M90" s="85" t="s">
-        <v>443</v>
+        <v>664</v>
       </c>
       <c r="N90" s="85"/>
       <c r="O90" s="85" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="P90" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="Q90" s="85" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="R90" s="85"/>
       <c r="S90" s="96"/>
@@ -9121,43 +9175,43 @@
     <row r="92" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="56"/>
       <c r="D92" s="84" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E92" s="84" t="s">
-        <v>778</v>
+        <v>742</v>
       </c>
       <c r="F92" s="84"/>
       <c r="G92" s="84" t="s">
-        <v>673</v>
+        <v>784</v>
       </c>
       <c r="H92" s="84" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="I92" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="J92" s="84" t="s">
-        <v>780</v>
+        <v>744</v>
       </c>
       <c r="K92" s="84" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="L92" s="84"/>
       <c r="M92" s="84"/>
       <c r="N92" s="84" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="O92" s="84" t="s">
-        <v>708</v>
+        <v>533</v>
       </c>
       <c r="P92" s="84" t="s">
-        <v>695</v>
+        <v>754</v>
       </c>
       <c r="Q92" s="84" t="s">
-        <v>525</v>
+        <v>766</v>
       </c>
       <c r="R92" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="S92" s="93"/>
       <c r="V92" s="60"/>
@@ -9168,10 +9222,10 @@
         <v>23</v>
       </c>
       <c r="D93" s="80" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E93" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F93" s="80" t="s">
         <v>228</v>
@@ -9186,7 +9240,7 @@
         <v>193</v>
       </c>
       <c r="J93" s="80" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="K93" s="80" t="s">
         <v>298</v>
@@ -9200,8 +9254,8 @@
       <c r="N93" s="80" t="s">
         <v>312</v>
       </c>
-      <c r="O93" s="80" t="s">
-        <v>336</v>
+      <c r="O93" s="108" t="s">
+        <v>143</v>
       </c>
       <c r="P93" s="80" t="s">
         <v>196</v>
@@ -9218,43 +9272,43 @@
     <row r="94" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="58"/>
       <c r="D94" s="85" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E94" s="85" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="F94" s="85"/>
       <c r="G94" s="85" t="s">
-        <v>674</v>
+        <v>785</v>
       </c>
       <c r="H94" s="85" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="I94" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="J94" s="85" t="s">
-        <v>781</v>
+        <v>745</v>
       </c>
       <c r="K94" s="85" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="L94" s="85"/>
       <c r="M94" s="85"/>
       <c r="N94" s="85" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="O94" s="85" t="s">
-        <v>709</v>
+        <v>534</v>
       </c>
       <c r="P94" s="85" t="s">
-        <v>696</v>
+        <v>755</v>
       </c>
       <c r="Q94" s="85" t="s">
-        <v>526</v>
+        <v>767</v>
       </c>
       <c r="R94" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="S94" s="96"/>
       <c r="V94" s="60"/>
@@ -9282,10 +9336,10 @@
     <row r="96" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="56"/>
       <c r="D96" s="84" t="s">
-        <v>678</v>
+        <v>768</v>
       </c>
       <c r="E96" s="84" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="F96" s="84"/>
       <c r="G96" s="84"/>
@@ -9309,16 +9363,16 @@
         <v>24</v>
       </c>
       <c r="D97" s="80" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E97" s="80" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F97" s="80" t="s">
         <v>228</v>
       </c>
       <c r="G97" s="81" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H97" s="80"/>
       <c r="I97" s="80"/>
@@ -9337,10 +9391,10 @@
     <row r="98" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="58"/>
       <c r="D98" s="85" t="s">
-        <v>679</v>
+        <v>769</v>
       </c>
       <c r="E98" s="85" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="F98" s="85"/>
       <c r="G98" s="85"/>
@@ -9466,37 +9520,37 @@
       <c r="D104" s="84"/>
       <c r="E104" s="84"/>
       <c r="F104" s="84" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G104" s="84" t="s">
-        <v>772</v>
+        <v>794</v>
       </c>
       <c r="H104" s="84"/>
       <c r="I104" s="84" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J104" s="84" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="K104" s="84" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="L104" s="84"/>
       <c r="M104" s="84" t="s">
-        <v>647</v>
+        <v>442</v>
       </c>
       <c r="N104" s="84" t="s">
         <v>596</v>
       </c>
       <c r="O104" s="84" t="s">
-        <v>476</v>
+        <v>798</v>
       </c>
       <c r="P104" s="84" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="Q104" s="84"/>
       <c r="R104" s="84" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="S104" s="93"/>
       <c r="V104" s="60"/>
@@ -9513,9 +9567,9 @@
         <v>185</v>
       </c>
       <c r="F105" s="80" t="s">
-        <v>339</v>
-      </c>
-      <c r="G105" s="81" t="s">
+        <v>336</v>
+      </c>
+      <c r="G105" s="107" t="s">
         <v>313</v>
       </c>
       <c r="H105" s="80" t="s">
@@ -9533,14 +9587,14 @@
       <c r="L105" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="M105" s="80" t="s">
-        <v>412</v>
+      <c r="M105" s="98" t="s">
+        <v>406</v>
       </c>
       <c r="N105" s="80" t="s">
-        <v>405</v>
-      </c>
-      <c r="O105" s="80" t="s">
-        <v>406</v>
+        <v>399</v>
+      </c>
+      <c r="O105" s="108" t="s">
+        <v>400</v>
       </c>
       <c r="P105" s="80" t="s">
         <v>202</v>
@@ -9549,7 +9603,7 @@
         <v>190</v>
       </c>
       <c r="R105" s="80" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="S105" s="94"/>
       <c r="V105" s="60"/>
@@ -9559,37 +9613,37 @@
       <c r="D106" s="85"/>
       <c r="E106" s="85"/>
       <c r="F106" s="85" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G106" s="85" t="s">
-        <v>773</v>
+        <v>795</v>
       </c>
       <c r="H106" s="85"/>
       <c r="I106" s="85" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J106" s="85" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="K106" s="85" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="L106" s="85"/>
       <c r="M106" s="85" t="s">
-        <v>648</v>
+        <v>443</v>
       </c>
       <c r="N106" s="85" t="s">
         <v>597</v>
       </c>
       <c r="O106" s="85" t="s">
-        <v>477</v>
+        <v>799</v>
       </c>
       <c r="P106" s="85" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="Q106" s="85"/>
       <c r="R106" s="85" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="S106" s="96"/>
       <c r="V106" s="60"/>
@@ -9617,43 +9671,43 @@
     <row r="108" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B108" s="56"/>
       <c r="D108" s="84" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E108" s="84" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="F108" s="84" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G108" s="84"/>
       <c r="H108" s="84" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I108" s="84" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="J108" s="84" t="s">
-        <v>784</v>
+        <v>746</v>
       </c>
       <c r="K108" s="84"/>
       <c r="L108" s="84" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="M108" s="84" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="N108" s="84" t="s">
-        <v>786</v>
+        <v>748</v>
       </c>
       <c r="O108" s="84"/>
       <c r="P108" s="84" t="s">
-        <v>788</v>
+        <v>750</v>
       </c>
       <c r="Q108" s="84" t="s">
-        <v>754</v>
+        <v>728</v>
       </c>
       <c r="R108" s="84" t="s">
-        <v>673</v>
+        <v>784</v>
       </c>
       <c r="S108" s="93"/>
       <c r="V108" s="60"/>
@@ -9664,10 +9718,10 @@
         <v>27</v>
       </c>
       <c r="D109" s="80" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E109" s="80" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F109" s="80" t="s">
         <v>203</v>
@@ -9676,31 +9730,31 @@
         <v>228</v>
       </c>
       <c r="H109" s="80" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I109" s="80" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="J109" s="80" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="K109" s="80" t="s">
         <v>190</v>
       </c>
       <c r="L109" s="80" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="M109" s="80" t="s">
         <v>187</v>
       </c>
       <c r="N109" s="80" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="O109" s="80" t="s">
         <v>190</v>
       </c>
       <c r="P109" s="80" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="Q109" s="80" t="s">
         <v>280</v>
@@ -9714,43 +9768,43 @@
     <row r="110" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="58"/>
       <c r="D110" s="85" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="E110" s="85" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F110" s="85" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="G110" s="85"/>
       <c r="H110" s="85" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="I110" s="85" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J110" s="85" t="s">
-        <v>785</v>
+        <v>747</v>
       </c>
       <c r="K110" s="85"/>
       <c r="L110" s="85" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="M110" s="85" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="N110" s="85" t="s">
-        <v>787</v>
+        <v>749</v>
       </c>
       <c r="O110" s="85"/>
       <c r="P110" s="85" t="s">
-        <v>789</v>
+        <v>751</v>
       </c>
       <c r="Q110" s="85" t="s">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="R110" s="85" t="s">
-        <v>674</v>
+        <v>785</v>
       </c>
       <c r="S110" s="96"/>
       <c r="V110" s="60"/>
@@ -9779,41 +9833,41 @@
       <c r="B112" s="56"/>
       <c r="D112" s="84"/>
       <c r="E112" s="84" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F112" s="84" t="s">
-        <v>786</v>
+        <v>748</v>
       </c>
       <c r="G112" s="84" t="s">
         <v>598</v>
       </c>
       <c r="H112" s="84" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I112" s="84" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="J112" s="84" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="K112" s="84" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="L112" s="84" t="s">
-        <v>701</v>
+        <v>764</v>
       </c>
       <c r="M112" s="84"/>
       <c r="N112" s="84" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="O112" s="84" t="s">
-        <v>476</v>
+        <v>798</v>
       </c>
       <c r="P112" s="84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="Q112" s="84" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="R112" s="84"/>
       <c r="S112" s="93"/>
@@ -9831,19 +9885,19 @@
         <v>187</v>
       </c>
       <c r="F113" s="80" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G113" s="80" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="H113" s="80" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I113" s="80" t="s">
         <v>193</v>
       </c>
       <c r="J113" s="80" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K113" s="80" t="s">
         <v>231</v>
@@ -9855,16 +9909,16 @@
         <v>190</v>
       </c>
       <c r="N113" s="80" t="s">
-        <v>411</v>
-      </c>
-      <c r="O113" s="80" t="s">
-        <v>340</v>
+        <v>405</v>
+      </c>
+      <c r="O113" s="108" t="s">
+        <v>400</v>
       </c>
       <c r="P113" s="80" t="s">
         <v>289</v>
       </c>
       <c r="Q113" s="80" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="R113" s="80" t="s">
         <v>190</v>
@@ -9876,41 +9930,41 @@
       <c r="B114" s="58"/>
       <c r="D114" s="85"/>
       <c r="E114" s="85" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F114" s="85" t="s">
-        <v>787</v>
+        <v>749</v>
       </c>
       <c r="G114" s="85" t="s">
         <v>599</v>
       </c>
       <c r="H114" s="85" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I114" s="85" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="J114" s="85" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="K114" s="85" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="L114" s="85" t="s">
-        <v>702</v>
+        <v>765</v>
       </c>
       <c r="M114" s="85"/>
       <c r="N114" s="85" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="O114" s="85" t="s">
-        <v>477</v>
+        <v>799</v>
       </c>
       <c r="P114" s="85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="Q114" s="85" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="R114" s="85"/>
       <c r="S114" s="96"/>
@@ -9939,22 +9993,22 @@
     <row r="116" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B116" s="56"/>
       <c r="D116" s="84" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E116" s="84" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F116" s="84" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="G116" s="84" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="H116" s="84" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I116" s="84" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="J116" s="84"/>
       <c r="K116" s="84"/>
@@ -9977,7 +10031,7 @@
         <v>315</v>
       </c>
       <c r="E117" s="80" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F117" s="80" t="s">
         <v>312</v>
@@ -10008,22 +10062,22 @@
     <row r="118" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="58"/>
       <c r="D118" s="85" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E118" s="85" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F118" s="85" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="G118" s="85" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="H118" s="85" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I118" s="85" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J118" s="85"/>
       <c r="K118" s="85"/>
@@ -10145,39 +10199,39 @@
       <c r="D124" s="84"/>
       <c r="E124" s="84"/>
       <c r="F124" s="84" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="G124" s="84" t="s">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="H124" s="84" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I124" s="84" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="J124" s="84" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="K124" s="84"/>
       <c r="L124" s="84" t="s">
-        <v>657</v>
+        <v>770</v>
       </c>
       <c r="M124" s="84" t="s">
-        <v>790</v>
+        <v>544</v>
       </c>
       <c r="N124" s="84" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="O124" s="84" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="P124" s="84"/>
       <c r="Q124" s="84" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="R124" s="84" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="S124" s="93"/>
       <c r="V124" s="60"/>
@@ -10194,34 +10248,34 @@
         <v>185</v>
       </c>
       <c r="F125" s="80" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G125" s="81" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H125" s="80" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I125" s="80" t="s">
         <v>308</v>
       </c>
       <c r="J125" s="80" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K125" s="80" t="s">
         <v>190</v>
       </c>
       <c r="L125" s="80" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M125" s="80" t="s">
-        <v>356</v>
-      </c>
-      <c r="N125" s="80" t="s">
-        <v>357</v>
+        <v>792</v>
+      </c>
+      <c r="N125" s="109" t="s">
+        <v>793</v>
       </c>
       <c r="O125" s="80" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="P125" s="80" t="s">
         <v>190</v>
@@ -10240,39 +10294,39 @@
       <c r="D126" s="85"/>
       <c r="E126" s="85"/>
       <c r="F126" s="85" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G126" s="85" t="s">
-        <v>711</v>
+        <v>689</v>
       </c>
       <c r="H126" s="85" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I126" s="85" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="J126" s="85" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="K126" s="85"/>
       <c r="L126" s="85" t="s">
-        <v>658</v>
+        <v>771</v>
       </c>
       <c r="M126" s="85" t="s">
-        <v>791</v>
+        <v>545</v>
       </c>
       <c r="N126" s="85" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="O126" s="85" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="P126" s="85"/>
       <c r="Q126" s="85" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="R126" s="85" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="S126" s="96"/>
       <c r="V126" s="60"/>
@@ -10301,40 +10355,40 @@
       <c r="B128" s="56"/>
       <c r="D128" s="84"/>
       <c r="E128" s="84" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F128" s="84" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G128" s="84" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H128" s="84" t="s">
-        <v>701</v>
+        <v>764</v>
       </c>
       <c r="I128" s="84"/>
       <c r="J128" s="84" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="K128" s="84" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="L128" s="84"/>
       <c r="M128" s="84" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="N128" s="84" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="O128" s="84" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="P128" s="84"/>
       <c r="Q128" s="84" t="s">
-        <v>792</v>
+        <v>752</v>
       </c>
       <c r="R128" s="84" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S128" s="93"/>
       <c r="V128" s="60"/>
@@ -10354,7 +10408,7 @@
         <v>256</v>
       </c>
       <c r="G129" s="80" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="H129" s="80" t="s">
         <v>274</v>
@@ -10363,28 +10417,28 @@
         <v>190</v>
       </c>
       <c r="J129" s="80" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="K129" s="80" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L129" s="80" t="s">
         <v>190</v>
       </c>
       <c r="M129" s="80" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="N129" s="80" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="O129" s="80" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P129" s="80" t="s">
         <v>228</v>
       </c>
       <c r="Q129" s="80" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="R129" s="80" t="s">
         <v>315</v>
@@ -10396,40 +10450,40 @@
       <c r="B130" s="58"/>
       <c r="D130" s="85"/>
       <c r="E130" s="85" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F130" s="85" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G130" s="85" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H130" s="85" t="s">
-        <v>702</v>
+        <v>765</v>
       </c>
       <c r="I130" s="85"/>
       <c r="J130" s="85" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="K130" s="85" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="L130" s="85"/>
       <c r="M130" s="85" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="N130" s="85" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="O130" s="85" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="P130" s="85"/>
       <c r="Q130" s="85" t="s">
-        <v>793</v>
+        <v>753</v>
       </c>
       <c r="R130" s="85" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="S130" s="96"/>
       <c r="V130" s="60"/>
@@ -10457,16 +10511,16 @@
     <row r="132" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B132" s="56"/>
       <c r="D132" s="84" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E132" s="84" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F132" s="84" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="G132" s="84" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H132" s="84"/>
       <c r="I132" s="84"/>
@@ -10494,10 +10548,10 @@
         <v>288</v>
       </c>
       <c r="F133" s="80" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G133" s="81" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="H133" s="80" t="s">
         <v>228</v>
@@ -10518,16 +10572,16 @@
     <row r="134" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="58"/>
       <c r="D134" s="85" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="E134" s="85" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F134" s="85" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="G134" s="85" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H134" s="85"/>
       <c r="I134" s="85"/>
